--- a/research/traditional_assets/database/data/portugal/portugal_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_restaurant_dining.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtls_ibs" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06059999999999999</v>
+        <v>0.0185</v>
+      </c>
+      <c r="E2">
+        <v>0.199</v>
       </c>
       <c r="G2">
-        <v>-0.05204359673024524</v>
+        <v>0.05174616695059625</v>
       </c>
       <c r="H2">
-        <v>-0.05204359673024524</v>
+        <v>0.05174616695059625</v>
       </c>
       <c r="I2">
-        <v>-0.07738419618528609</v>
+        <v>0.07218909710391821</v>
       </c>
       <c r="J2">
-        <v>-0.07738419618528609</v>
+        <v>0.06187636894621562</v>
       </c>
       <c r="K2">
-        <v>-44.6</v>
+        <v>64.8</v>
       </c>
       <c r="L2">
-        <v>-0.1215258855585831</v>
+        <v>0.1379897785349233</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.543</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.02616153538584566</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.1009722222222222</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02243102758896441</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.08657407407407408</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.9329999999999998</v>
+      </c>
+      <c r="T2">
+        <v>0.1425951398441082</v>
       </c>
       <c r="U2">
-        <v>83.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.3338670936749399</v>
+        <v>0.296281487405038</v>
       </c>
       <c r="W2">
-        <v>-0.2168206125425377</v>
+        <v>0.4093493367024637</v>
       </c>
       <c r="X2">
-        <v>0.1840376746915945</v>
+        <v>0.1880750164015587</v>
       </c>
       <c r="Y2">
-        <v>-0.4008582872341322</v>
+        <v>0.221274320300905</v>
       </c>
       <c r="Z2">
-        <v>0.5291684269567337</v>
+        <v>0.7080820265379976</v>
       </c>
       <c r="AA2">
-        <v>-0.04094927336667912</v>
+        <v>0.04381354471824918</v>
       </c>
       <c r="AB2">
-        <v>0.0796948860332731</v>
+        <v>0.115846115862686</v>
       </c>
       <c r="AC2">
-        <v>-0.1206441593999522</v>
+        <v>-0.07203257114443681</v>
       </c>
       <c r="AD2">
-        <v>581.7</v>
+        <v>300.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>581.7</v>
+        <v>300.7</v>
       </c>
       <c r="AG2">
-        <v>498.3000000000001</v>
+        <v>226.6</v>
       </c>
       <c r="AH2">
-        <v>0.699579073962718</v>
+        <v>0.5459331880900509</v>
       </c>
       <c r="AI2">
-        <v>0.7854442344045369</v>
+        <v>0.555514502124515</v>
       </c>
       <c r="AJ2">
-        <v>0.6660874214677182</v>
+        <v>0.4753513740297881</v>
       </c>
       <c r="AK2">
-        <v>0.7582166768107121</v>
+        <v>0.4850171232876712</v>
       </c>
       <c r="AL2">
-        <v>21.4</v>
+        <v>10.1</v>
       </c>
       <c r="AM2">
-        <v>20.836</v>
+        <v>9.430999999999999</v>
       </c>
       <c r="AN2">
-        <v>-12.01859504132232</v>
+        <v>8.591428571428571</v>
       </c>
       <c r="AO2">
-        <v>-1.327102803738318</v>
+        <v>3.356435643564356</v>
       </c>
       <c r="AP2">
-        <v>-10.29545454545455</v>
+        <v>6.474285714285714</v>
       </c>
       <c r="AQ2">
-        <v>-1.36302553273181</v>
+        <v>3.59452868200615</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +724,8822 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06059999999999999</v>
+        <v>0.0185</v>
+      </c>
+      <c r="E3">
+        <v>0.199</v>
       </c>
       <c r="G3">
-        <v>-0.05204359673024524</v>
+        <v>0.05174616695059625</v>
       </c>
       <c r="H3">
-        <v>-0.05204359673024524</v>
+        <v>0.05174616695059625</v>
       </c>
       <c r="I3">
-        <v>-0.07738419618528609</v>
+        <v>0.07218909710391821</v>
       </c>
       <c r="J3">
-        <v>-0.07738419618528609</v>
+        <v>0.06187636894621562</v>
       </c>
       <c r="K3">
-        <v>-44.6</v>
+        <v>64.8</v>
       </c>
       <c r="L3">
-        <v>-0.1215258855585831</v>
+        <v>0.1379897785349233</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>6.543</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02616153538584566</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.1009722222222222</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>5.61</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02243102758896441</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.08657407407407408</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.9329999999999998</v>
+      </c>
+      <c r="T3">
+        <v>0.1425951398441082</v>
       </c>
       <c r="U3">
-        <v>83.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.3338670936749399</v>
+        <v>0.296281487405038</v>
       </c>
       <c r="W3">
-        <v>-0.2168206125425377</v>
+        <v>0.4093493367024637</v>
       </c>
       <c r="X3">
-        <v>0.1840376746915945</v>
+        <v>0.1880750164015587</v>
       </c>
       <c r="Y3">
-        <v>-0.4008582872341322</v>
+        <v>0.221274320300905</v>
       </c>
       <c r="Z3">
-        <v>0.5291684269567337</v>
+        <v>0.7080820265379976</v>
       </c>
       <c r="AA3">
-        <v>-0.04094927336667912</v>
+        <v>0.04381354471824918</v>
       </c>
       <c r="AB3">
-        <v>0.0796948860332731</v>
+        <v>0.115846115862686</v>
       </c>
       <c r="AC3">
-        <v>-0.1206441593999522</v>
+        <v>-0.07203257114443681</v>
       </c>
       <c r="AD3">
-        <v>581.7</v>
+        <v>300.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>581.7</v>
+        <v>300.7</v>
       </c>
       <c r="AG3">
-        <v>498.3000000000001</v>
+        <v>226.6</v>
       </c>
       <c r="AH3">
-        <v>0.699579073962718</v>
+        <v>0.5459331880900509</v>
       </c>
       <c r="AI3">
-        <v>0.7854442344045369</v>
+        <v>0.555514502124515</v>
       </c>
       <c r="AJ3">
-        <v>0.6660874214677182</v>
+        <v>0.4753513740297881</v>
       </c>
       <c r="AK3">
-        <v>0.7582166768107121</v>
+        <v>0.4850171232876712</v>
       </c>
       <c r="AL3">
-        <v>21.4</v>
+        <v>10.1</v>
       </c>
       <c r="AM3">
-        <v>20.836</v>
+        <v>9.430999999999999</v>
       </c>
       <c r="AN3">
-        <v>-12.01859504132232</v>
+        <v>8.591428571428571</v>
       </c>
       <c r="AO3">
-        <v>-1.327102803738318</v>
+        <v>3.356435643564356</v>
       </c>
       <c r="AP3">
-        <v>-10.29545454545455</v>
+        <v>6.474285714285714</v>
       </c>
       <c r="AQ3">
-        <v>-1.36302553273181</v>
+        <v>3.59452868200615</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ibersol, S.G.P.S., S.A. (ENXTLS:IBS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTLS:IBS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restaurant/Dining</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.545933188090051</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>250.1</v>
+      </c>
+      <c r="H2">
+        <v>488.001625608415</v>
+      </c>
+      <c r="I2">
+        <v>476.7</v>
+      </c>
+      <c r="J2">
+        <v>419.409625608415</v>
+      </c>
+      <c r="K2">
+        <v>300.7</v>
+      </c>
+      <c r="L2">
+        <v>5.508</v>
+      </c>
+      <c r="M2">
+        <v>0.115846115862686</v>
+      </c>
+      <c r="N2">
+        <v>0.126370435176501</v>
+      </c>
+      <c r="O2">
+        <v>0.0557714633027523</v>
+      </c>
+      <c r="P2">
+        <v>0.921261873638344</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.188075016401559</v>
+      </c>
+      <c r="T2">
+        <v>0.118341228727392</v>
+      </c>
+      <c r="U2">
+        <v>1.6224588232213</v>
+      </c>
+      <c r="V2">
+        <v>0.864527577819601</v>
+      </c>
+      <c r="W2">
+        <v>-13.60895496606732</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>250.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.07059678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.21</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>35</v>
+      </c>
+      <c r="AH2">
+        <v>52.9</v>
+      </c>
+      <c r="AI2">
+        <v>44.7</v>
+      </c>
+      <c r="AJ2">
+        <v>300.7</v>
+      </c>
+      <c r="AK2">
+        <v>300.7</v>
+      </c>
+      <c r="AL2">
+        <v>10.1</v>
+      </c>
+      <c r="AM2">
+        <v>300.7</v>
+      </c>
+      <c r="AN2">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-300.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>250.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>35</v>
+      </c>
+      <c r="K2">
+        <v>52.9</v>
+      </c>
+      <c r="L2">
+        <v>-17.9</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-17.9</v>
+      </c>
+      <c r="O2">
+        <v>-3.758999999999999</v>
+      </c>
+      <c r="P2">
+        <v>-14.141</v>
+      </c>
+      <c r="Q2">
+        <v>38.759</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1263704351765013</v>
+      </c>
+      <c r="C3">
+        <v>488.0016256084151</v>
+      </c>
+      <c r="D3">
+        <v>419.4096256084151</v>
+      </c>
+      <c r="E3">
+        <v>-295.192</v>
+      </c>
+      <c r="F3">
+        <v>5.508</v>
+      </c>
+      <c r="G3">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>250.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>35</v>
+      </c>
+      <c r="K3">
+        <v>52.9</v>
+      </c>
+      <c r="L3">
+        <v>-17.9</v>
+      </c>
+      <c r="M3">
+        <v>1.3153104</v>
+      </c>
+      <c r="N3">
+        <v>-19.2153104</v>
+      </c>
+      <c r="O3">
+        <v>-4.035215183999999</v>
+      </c>
+      <c r="P3">
+        <v>-15.180095216</v>
+      </c>
+      <c r="Q3">
+        <v>37.71990478399999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1183412287273918</v>
+      </c>
+      <c r="T3">
+        <v>0.864527577819601</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-2.857880542874138</v>
+      </c>
+      <c r="W3">
+        <v>0.9212618736383441</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-13.60895496606732</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1283704351765013</v>
+      </c>
+      <c r="C4">
+        <v>473.1287135192428</v>
+      </c>
+      <c r="D4">
+        <v>410.0447135192429</v>
+      </c>
+      <c r="E4">
+        <v>-289.684</v>
+      </c>
+      <c r="F4">
+        <v>11.016</v>
+      </c>
+      <c r="G4">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H4">
+        <v>250.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>35</v>
+      </c>
+      <c r="K4">
+        <v>52.9</v>
+      </c>
+      <c r="L4">
+        <v>-17.9</v>
+      </c>
+      <c r="M4">
+        <v>2.6306208</v>
+      </c>
+      <c r="N4">
+        <v>-20.5306208</v>
+      </c>
+      <c r="O4">
+        <v>-4.311430367999999</v>
+      </c>
+      <c r="P4">
+        <v>-16.219190432</v>
+      </c>
+      <c r="Q4">
+        <v>36.680809568</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1191528739184877</v>
+      </c>
+      <c r="T4">
+        <v>0.8733492877973521</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-1.428940271437069</v>
+      </c>
+      <c r="W4">
+        <v>0.5800309368191722</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-6.804477483033661</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1303704351765013</v>
+      </c>
+      <c r="C5">
+        <v>458.6648815909816</v>
+      </c>
+      <c r="D5">
+        <v>401.0888815909816</v>
+      </c>
+      <c r="E5">
+        <v>-284.176</v>
+      </c>
+      <c r="F5">
+        <v>16.524</v>
+      </c>
+      <c r="G5">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H5">
+        <v>250.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>35</v>
+      </c>
+      <c r="K5">
+        <v>52.9</v>
+      </c>
+      <c r="L5">
+        <v>-17.9</v>
+      </c>
+      <c r="M5">
+        <v>3.9459312</v>
+      </c>
+      <c r="N5">
+        <v>-21.8459312</v>
+      </c>
+      <c r="O5">
+        <v>-4.587645551999999</v>
+      </c>
+      <c r="P5">
+        <v>-17.258285648</v>
+      </c>
+      <c r="Q5">
+        <v>35.64171435199999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1199812540619772</v>
+      </c>
+      <c r="T5">
+        <v>0.8823528887024794</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.9526268476247127</v>
+      </c>
+      <c r="W5">
+        <v>0.4662872912127814</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-4.536318322022442</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1323704351765013</v>
+      </c>
+      <c r="C6">
+        <v>444.5838984508603</v>
+      </c>
+      <c r="D6">
+        <v>392.5158984508603</v>
+      </c>
+      <c r="E6">
+        <v>-278.668</v>
+      </c>
+      <c r="F6">
+        <v>22.032</v>
+      </c>
+      <c r="G6">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H6">
+        <v>250.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>35</v>
+      </c>
+      <c r="K6">
+        <v>52.9</v>
+      </c>
+      <c r="L6">
+        <v>-17.9</v>
+      </c>
+      <c r="M6">
+        <v>5.2612416</v>
+      </c>
+      <c r="N6">
+        <v>-23.1612416</v>
+      </c>
+      <c r="O6">
+        <v>-4.863860735999999</v>
+      </c>
+      <c r="P6">
+        <v>-18.297380864</v>
+      </c>
+      <c r="Q6">
+        <v>34.602619136</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1208268921251228</v>
+      </c>
+      <c r="T6">
+        <v>0.8915440646264636</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.7144701357185345</v>
+      </c>
+      <c r="W6">
+        <v>0.4094154684095861</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-3.402238741516831</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1343704351765014</v>
+      </c>
+      <c r="C7">
+        <v>430.8617284991182</v>
+      </c>
+      <c r="D7">
+        <v>384.3017284991183</v>
+      </c>
+      <c r="E7">
+        <v>-273.16</v>
+      </c>
+      <c r="F7">
+        <v>27.54</v>
+      </c>
+      <c r="G7">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H7">
+        <v>250.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>52.9</v>
+      </c>
+      <c r="L7">
+        <v>-17.9</v>
+      </c>
+      <c r="M7">
+        <v>6.576552</v>
+      </c>
+      <c r="N7">
+        <v>-24.476552</v>
+      </c>
+      <c r="O7">
+        <v>-5.140075919999998</v>
+      </c>
+      <c r="P7">
+        <v>-19.33647608</v>
+      </c>
+      <c r="Q7">
+        <v>33.56352391999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.121690333094861</v>
+      </c>
+      <c r="T7">
+        <v>0.9009287389909526</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.5715761085748275</v>
+      </c>
+      <c r="W7">
+        <v>0.3752923747276689</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-2.721790993213465</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1363704351765013</v>
+      </c>
+      <c r="C8">
+        <v>417.4763068640927</v>
+      </c>
+      <c r="D8">
+        <v>376.4243068640928</v>
+      </c>
+      <c r="E8">
+        <v>-267.652</v>
+      </c>
+      <c r="F8">
+        <v>33.04799999999999</v>
+      </c>
+      <c r="G8">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H8">
+        <v>250.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>35</v>
+      </c>
+      <c r="K8">
+        <v>52.9</v>
+      </c>
+      <c r="L8">
+        <v>-17.9</v>
+      </c>
+      <c r="M8">
+        <v>7.891862399999999</v>
+      </c>
+      <c r="N8">
+        <v>-25.7918624</v>
+      </c>
+      <c r="O8">
+        <v>-5.416291103999999</v>
+      </c>
+      <c r="P8">
+        <v>-20.375571296</v>
+      </c>
+      <c r="Q8">
+        <v>32.524428704</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1225721451490616</v>
+      </c>
+      <c r="T8">
+        <v>0.9105130872780904</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.4763134238123564</v>
+      </c>
+      <c r="W8">
+        <v>0.3525436456063907</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-2.268159161011221</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1383704351765014</v>
+      </c>
+      <c r="C9">
+        <v>404.4073414792004</v>
+      </c>
+      <c r="D9">
+        <v>368.8633414792004</v>
+      </c>
+      <c r="E9">
+        <v>-262.144</v>
+      </c>
+      <c r="F9">
+        <v>38.556</v>
+      </c>
+      <c r="G9">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H9">
+        <v>250.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>35</v>
+      </c>
+      <c r="K9">
+        <v>52.9</v>
+      </c>
+      <c r="L9">
+        <v>-17.9</v>
+      </c>
+      <c r="M9">
+        <v>9.2071728</v>
+      </c>
+      <c r="N9">
+        <v>-27.1071728</v>
+      </c>
+      <c r="O9">
+        <v>-5.692506287999999</v>
+      </c>
+      <c r="P9">
+        <v>-21.414666512</v>
+      </c>
+      <c r="Q9">
+        <v>31.48533348799999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1234729209033526</v>
+      </c>
+      <c r="T9">
+        <v>0.920303550582156</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.4082686489820196</v>
+      </c>
+      <c r="W9">
+        <v>0.3362945533769063</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-1.944136423723903</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1403704351765014</v>
+      </c>
+      <c r="C10">
+        <v>391.6361385434599</v>
+      </c>
+      <c r="D10">
+        <v>361.6001385434599</v>
+      </c>
+      <c r="E10">
+        <v>-256.636</v>
+      </c>
+      <c r="F10">
+        <v>44.064</v>
+      </c>
+      <c r="G10">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H10">
+        <v>250.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>35</v>
+      </c>
+      <c r="K10">
+        <v>52.9</v>
+      </c>
+      <c r="L10">
+        <v>-17.9</v>
+      </c>
+      <c r="M10">
+        <v>10.5224832</v>
+      </c>
+      <c r="N10">
+        <v>-28.4224832</v>
+      </c>
+      <c r="O10">
+        <v>-5.968721471999999</v>
+      </c>
+      <c r="P10">
+        <v>-22.453761728</v>
+      </c>
+      <c r="Q10">
+        <v>30.446238272</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1243932787392586</v>
+      </c>
+      <c r="T10">
+        <v>0.9303068500450054</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.3572350678592672</v>
+      </c>
+      <c r="W10">
+        <v>0.3241077342047931</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-1.701119370758415</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1423704351765013</v>
+      </c>
+      <c r="C11">
+        <v>379.1454482047116</v>
+      </c>
+      <c r="D11">
+        <v>354.6174482047116</v>
+      </c>
+      <c r="E11">
+        <v>-251.128</v>
+      </c>
+      <c r="F11">
+        <v>49.572</v>
+      </c>
+      <c r="G11">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H11">
+        <v>250.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>35</v>
+      </c>
+      <c r="K11">
+        <v>52.9</v>
+      </c>
+      <c r="L11">
+        <v>-17.9</v>
+      </c>
+      <c r="M11">
+        <v>11.8377936</v>
+      </c>
+      <c r="N11">
+        <v>-29.7377936</v>
+      </c>
+      <c r="O11">
+        <v>-6.244936655999998</v>
+      </c>
+      <c r="P11">
+        <v>-23.492856944</v>
+      </c>
+      <c r="Q11">
+        <v>29.407143056</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1253338642199098</v>
+      </c>
+      <c r="T11">
+        <v>0.9405300022433021</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.3175422825415709</v>
+      </c>
+      <c r="W11">
+        <v>0.3146290970709271</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-1.512106107340814</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1443704351765013</v>
+      </c>
+      <c r="C12">
+        <v>366.9193277837466</v>
+      </c>
+      <c r="D12">
+        <v>347.8993277837466</v>
+      </c>
+      <c r="E12">
+        <v>-245.62</v>
+      </c>
+      <c r="F12">
+        <v>55.08</v>
+      </c>
+      <c r="G12">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H12">
+        <v>250.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>35</v>
+      </c>
+      <c r="K12">
+        <v>52.9</v>
+      </c>
+      <c r="L12">
+        <v>-17.9</v>
+      </c>
+      <c r="M12">
+        <v>13.153104</v>
+      </c>
+      <c r="N12">
+        <v>-31.053104</v>
+      </c>
+      <c r="O12">
+        <v>-6.521151839999998</v>
+      </c>
+      <c r="P12">
+        <v>-24.53195216</v>
+      </c>
+      <c r="Q12">
+        <v>28.36804784</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.126295351600131</v>
+      </c>
+      <c r="T12">
+        <v>0.950980335601561</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.2857880542874138</v>
+      </c>
+      <c r="W12">
+        <v>0.3070461873638344</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-1.360895496606732</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1463704351765013</v>
+      </c>
+      <c r="C13">
+        <v>354.9430202564429</v>
+      </c>
+      <c r="D13">
+        <v>341.4310202564429</v>
+      </c>
+      <c r="E13">
+        <v>-240.112</v>
+      </c>
+      <c r="F13">
+        <v>60.58799999999999</v>
+      </c>
+      <c r="G13">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H13">
+        <v>250.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>35</v>
+      </c>
+      <c r="K13">
+        <v>52.9</v>
+      </c>
+      <c r="L13">
+        <v>-17.9</v>
+      </c>
+      <c r="M13">
+        <v>14.4684144</v>
+      </c>
+      <c r="N13">
+        <v>-32.3684144</v>
+      </c>
+      <c r="O13">
+        <v>-6.797367023999999</v>
+      </c>
+      <c r="P13">
+        <v>-25.571047376</v>
+      </c>
+      <c r="Q13">
+        <v>27.328952624</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1272784454383347</v>
+      </c>
+      <c r="T13">
+        <v>0.961665507911691</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.2598073220794671</v>
+      </c>
+      <c r="W13">
+        <v>0.3008419885125767</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-1.237177724187939</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1483704351765013</v>
+      </c>
+      <c r="C14">
+        <v>343.2028460443673</v>
+      </c>
+      <c r="D14">
+        <v>335.1988460443674</v>
+      </c>
+      <c r="E14">
+        <v>-234.604</v>
+      </c>
+      <c r="F14">
+        <v>66.09599999999999</v>
+      </c>
+      <c r="G14">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H14">
+        <v>250.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>35</v>
+      </c>
+      <c r="K14">
+        <v>52.9</v>
+      </c>
+      <c r="L14">
+        <v>-17.9</v>
+      </c>
+      <c r="M14">
+        <v>15.7837248</v>
+      </c>
+      <c r="N14">
+        <v>-33.68372479999999</v>
+      </c>
+      <c r="O14">
+        <v>-7.073582207999998</v>
+      </c>
+      <c r="P14">
+        <v>-26.610142592</v>
+      </c>
+      <c r="Q14">
+        <v>26.289857408</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1282838823183158</v>
+      </c>
+      <c r="T14">
+        <v>0.9725935250470511</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.2381567119061782</v>
+      </c>
+      <c r="W14">
+        <v>0.2956718228031954</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-1.13407958050561</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1503704351765013</v>
+      </c>
+      <c r="C15">
+        <v>331.6861064438793</v>
+      </c>
+      <c r="D15">
+        <v>329.1901064438792</v>
+      </c>
+      <c r="E15">
+        <v>-229.096</v>
+      </c>
+      <c r="F15">
+        <v>71.604</v>
+      </c>
+      <c r="G15">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H15">
+        <v>250.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>35</v>
+      </c>
+      <c r="K15">
+        <v>52.9</v>
+      </c>
+      <c r="L15">
+        <v>-17.9</v>
+      </c>
+      <c r="M15">
+        <v>17.0990352</v>
+      </c>
+      <c r="N15">
+        <v>-34.99903519999999</v>
+      </c>
+      <c r="O15">
+        <v>-7.349797391999997</v>
+      </c>
+      <c r="P15">
+        <v>-27.649237808</v>
+      </c>
+      <c r="Q15">
+        <v>25.250762192</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1293124326897907</v>
+      </c>
+      <c r="T15">
+        <v>0.9837727609671322</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.2198369648364721</v>
+      </c>
+      <c r="W15">
+        <v>0.2912970672029496</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-1.046842689697487</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1523704351765014</v>
+      </c>
+      <c r="C16">
+        <v>320.3809972590411</v>
+      </c>
+      <c r="D16">
+        <v>323.3929972590411</v>
+      </c>
+      <c r="E16">
+        <v>-223.588</v>
+      </c>
+      <c r="F16">
+        <v>77.11199999999999</v>
+      </c>
+      <c r="G16">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H16">
+        <v>250.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>35</v>
+      </c>
+      <c r="K16">
+        <v>52.9</v>
+      </c>
+      <c r="L16">
+        <v>-17.9</v>
+      </c>
+      <c r="M16">
+        <v>18.4143456</v>
+      </c>
+      <c r="N16">
+        <v>-36.3143456</v>
+      </c>
+      <c r="O16">
+        <v>-7.626012575999998</v>
+      </c>
+      <c r="P16">
+        <v>-28.688333024</v>
+      </c>
+      <c r="Q16">
+        <v>24.211666976</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1303649028373464</v>
+      </c>
+      <c r="T16">
+        <v>0.9952119791179129</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.2041343244910098</v>
+      </c>
+      <c r="W16">
+        <v>0.2875472766884531</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.9720682118619515</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1543704351765013</v>
+      </c>
+      <c r="C17">
+        <v>309.2765314022647</v>
+      </c>
+      <c r="D17">
+        <v>317.7965314022647</v>
+      </c>
+      <c r="E17">
+        <v>-218.08</v>
+      </c>
+      <c r="F17">
+        <v>82.61999999999999</v>
+      </c>
+      <c r="G17">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H17">
+        <v>250.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>35</v>
+      </c>
+      <c r="K17">
+        <v>52.9</v>
+      </c>
+      <c r="L17">
+        <v>-17.9</v>
+      </c>
+      <c r="M17">
+        <v>19.729656</v>
+      </c>
+      <c r="N17">
+        <v>-37.629656</v>
+      </c>
+      <c r="O17">
+        <v>-7.902227759999998</v>
+      </c>
+      <c r="P17">
+        <v>-29.72742824</v>
+      </c>
+      <c r="Q17">
+        <v>23.17257176</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.131442136988374</v>
+      </c>
+      <c r="T17">
+        <v>1.006920355342829</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.1905253695249425</v>
+      </c>
+      <c r="W17">
+        <v>0.2842974582425563</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.9072636644044882</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1563704351765013</v>
+      </c>
+      <c r="C18">
+        <v>298.3624693948361</v>
+      </c>
+      <c r="D18">
+        <v>312.3904693948361</v>
+      </c>
+      <c r="E18">
+        <v>-212.572</v>
+      </c>
+      <c r="F18">
+        <v>88.128</v>
+      </c>
+      <c r="G18">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H18">
+        <v>250.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>35</v>
+      </c>
+      <c r="K18">
+        <v>52.9</v>
+      </c>
+      <c r="L18">
+        <v>-17.9</v>
+      </c>
+      <c r="M18">
+        <v>21.0449664</v>
+      </c>
+      <c r="N18">
+        <v>-38.9449664</v>
+      </c>
+      <c r="O18">
+        <v>-8.178442943999999</v>
+      </c>
+      <c r="P18">
+        <v>-30.766523456</v>
+      </c>
+      <c r="Q18">
+        <v>22.133476544</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1325450195715689</v>
+      </c>
+      <c r="T18">
+        <v>1.018907502430244</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.1786175339296336</v>
+      </c>
+      <c r="W18">
+        <v>0.2814538671023965</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.8505596853792077</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1583704351765013</v>
+      </c>
+      <c r="C19">
+        <v>287.6292568423568</v>
+      </c>
+      <c r="D19">
+        <v>307.1652568423568</v>
+      </c>
+      <c r="E19">
+        <v>-207.064</v>
+      </c>
+      <c r="F19">
+        <v>93.636</v>
+      </c>
+      <c r="G19">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H19">
+        <v>250.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>35</v>
+      </c>
+      <c r="K19">
+        <v>52.9</v>
+      </c>
+      <c r="L19">
+        <v>-17.9</v>
+      </c>
+      <c r="M19">
+        <v>22.3602768</v>
+      </c>
+      <c r="N19">
+        <v>-40.2602768</v>
+      </c>
+      <c r="O19">
+        <v>-8.454658127999998</v>
+      </c>
+      <c r="P19">
+        <v>-31.805618672</v>
+      </c>
+      <c r="Q19">
+        <v>21.094381328</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1336744776386963</v>
+      </c>
+      <c r="T19">
+        <v>1.031183496435428</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.1681106201690669</v>
+      </c>
+      <c r="W19">
+        <v>0.2789448160963732</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.8005267627098425</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1603704351765014</v>
+      </c>
+      <c r="C20">
+        <v>277.0679680818714</v>
+      </c>
+      <c r="D20">
+        <v>302.1119680818715</v>
+      </c>
+      <c r="E20">
+        <v>-201.556</v>
+      </c>
+      <c r="F20">
+        <v>99.14399999999999</v>
+      </c>
+      <c r="G20">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H20">
+        <v>250.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>35</v>
+      </c>
+      <c r="K20">
+        <v>52.9</v>
+      </c>
+      <c r="L20">
+        <v>-17.9</v>
+      </c>
+      <c r="M20">
+        <v>23.6755872</v>
+      </c>
+      <c r="N20">
+        <v>-41.5755872</v>
+      </c>
+      <c r="O20">
+        <v>-8.730873311999998</v>
+      </c>
+      <c r="P20">
+        <v>-32.844713888</v>
+      </c>
+      <c r="Q20">
+        <v>20.055286112</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1348314834635584</v>
+      </c>
+      <c r="T20">
+        <v>1.043758904928543</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.1587711412707854</v>
+      </c>
+      <c r="W20">
+        <v>0.2767145485354636</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.7560530536704071</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1623704351765014</v>
+      </c>
+      <c r="C21">
+        <v>266.6702553014584</v>
+      </c>
+      <c r="D21">
+        <v>297.2222553014584</v>
+      </c>
+      <c r="E21">
+        <v>-196.048</v>
+      </c>
+      <c r="F21">
+        <v>104.652</v>
+      </c>
+      <c r="G21">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H21">
+        <v>250.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>35</v>
+      </c>
+      <c r="K21">
+        <v>52.9</v>
+      </c>
+      <c r="L21">
+        <v>-17.9</v>
+      </c>
+      <c r="M21">
+        <v>24.9908976</v>
+      </c>
+      <c r="N21">
+        <v>-42.8908976</v>
+      </c>
+      <c r="O21">
+        <v>-9.007088495999998</v>
+      </c>
+      <c r="P21">
+        <v>-33.88380910399999</v>
+      </c>
+      <c r="Q21">
+        <v>19.016190896</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1360170573334789</v>
+      </c>
+      <c r="T21">
+        <v>1.056644817335068</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.1504147654144283</v>
+      </c>
+      <c r="W21">
+        <v>0.2747190459809655</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.716260787687754</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1643704351765014</v>
+      </c>
+      <c r="C22">
+        <v>256.4283025221489</v>
+      </c>
+      <c r="D22">
+        <v>292.4883025221488</v>
+      </c>
+      <c r="E22">
+        <v>-190.54</v>
+      </c>
+      <c r="F22">
+        <v>110.16</v>
+      </c>
+      <c r="G22">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H22">
+        <v>250.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>35</v>
+      </c>
+      <c r="K22">
+        <v>52.9</v>
+      </c>
+      <c r="L22">
+        <v>-17.9</v>
+      </c>
+      <c r="M22">
+        <v>26.306208</v>
+      </c>
+      <c r="N22">
+        <v>-44.206208</v>
+      </c>
+      <c r="O22">
+        <v>-9.28330368</v>
+      </c>
+      <c r="P22">
+        <v>-34.92290432</v>
+      </c>
+      <c r="Q22">
+        <v>17.97709568</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1372322705501474</v>
+      </c>
+      <c r="T22">
+        <v>1.069852877551756</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.1428940271437069</v>
+      </c>
+      <c r="W22">
+        <v>0.2729230936819173</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.6804477483033664</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1663704351765014</v>
+      </c>
+      <c r="C23">
+        <v>246.3347839085692</v>
+      </c>
+      <c r="D23">
+        <v>287.9027839085692</v>
+      </c>
+      <c r="E23">
+        <v>-185.032</v>
+      </c>
+      <c r="F23">
+        <v>115.668</v>
+      </c>
+      <c r="G23">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H23">
+        <v>250.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>35</v>
+      </c>
+      <c r="K23">
+        <v>52.9</v>
+      </c>
+      <c r="L23">
+        <v>-17.9</v>
+      </c>
+      <c r="M23">
+        <v>27.6215184</v>
+      </c>
+      <c r="N23">
+        <v>-45.5215184</v>
+      </c>
+      <c r="O23">
+        <v>-9.559518863999998</v>
+      </c>
+      <c r="P23">
+        <v>-35.961999536</v>
+      </c>
+      <c r="Q23">
+        <v>16.938000464</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1384782486583771</v>
+      </c>
+      <c r="T23">
+        <v>1.083395319039753</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.1360895496606732</v>
+      </c>
+      <c r="W23">
+        <v>0.2712981844589687</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.6480454745746345</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1683704351765014</v>
+      </c>
+      <c r="C24">
+        <v>236.3828259405901</v>
+      </c>
+      <c r="D24">
+        <v>283.45882594059</v>
+      </c>
+      <c r="E24">
+        <v>-179.524</v>
+      </c>
+      <c r="F24">
+        <v>121.176</v>
+      </c>
+      <c r="G24">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H24">
+        <v>250.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>35</v>
+      </c>
+      <c r="K24">
+        <v>52.9</v>
+      </c>
+      <c r="L24">
+        <v>-17.9</v>
+      </c>
+      <c r="M24">
+        <v>28.9368288</v>
+      </c>
+      <c r="N24">
+        <v>-46.83682879999999</v>
+      </c>
+      <c r="O24">
+        <v>-9.835734047999997</v>
+      </c>
+      <c r="P24">
+        <v>-37.00109475199999</v>
+      </c>
+      <c r="Q24">
+        <v>15.89890524800001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1397561749232281</v>
+      </c>
+      <c r="T24">
+        <v>1.097285002617186</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.1299036610397336</v>
+      </c>
+      <c r="W24">
+        <v>0.2698209942562884</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.6185888620939692</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1703704351765014</v>
+      </c>
+      <c r="C25">
+        <v>226.5659730351432</v>
+      </c>
+      <c r="D25">
+        <v>279.1499730351431</v>
+      </c>
+      <c r="E25">
+        <v>-174.016</v>
+      </c>
+      <c r="F25">
+        <v>126.684</v>
+      </c>
+      <c r="G25">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H25">
+        <v>250.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>35</v>
+      </c>
+      <c r="K25">
+        <v>52.9</v>
+      </c>
+      <c r="L25">
+        <v>-17.9</v>
+      </c>
+      <c r="M25">
+        <v>30.2521392</v>
+      </c>
+      <c r="N25">
+        <v>-48.1521392</v>
+      </c>
+      <c r="O25">
+        <v>-10.111949232</v>
+      </c>
+      <c r="P25">
+        <v>-38.040189968</v>
+      </c>
+      <c r="Q25">
+        <v>14.859810032</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1410672940780752</v>
+      </c>
+      <c r="T25">
+        <v>1.11153545719663</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.1242556757771364</v>
+      </c>
+      <c r="W25">
+        <v>0.2684722553755802</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.59169369417684</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1723704351765014</v>
+      </c>
+      <c r="C26">
+        <v>216.8781562565833</v>
+      </c>
+      <c r="D26">
+        <v>274.9701562565833</v>
+      </c>
+      <c r="E26">
+        <v>-168.508</v>
+      </c>
+      <c r="F26">
+        <v>132.192</v>
+      </c>
+      <c r="G26">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H26">
+        <v>250.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>35</v>
+      </c>
+      <c r="K26">
+        <v>52.9</v>
+      </c>
+      <c r="L26">
+        <v>-17.9</v>
+      </c>
+      <c r="M26">
+        <v>31.5674496</v>
+      </c>
+      <c r="N26">
+        <v>-49.46744959999999</v>
+      </c>
+      <c r="O26">
+        <v>-10.388164416</v>
+      </c>
+      <c r="P26">
+        <v>-39.079285184</v>
+      </c>
+      <c r="Q26">
+        <v>13.820714816</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1424129163685762</v>
+      </c>
+      <c r="T26">
+        <v>1.126160923738691</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.1190783559530891</v>
+      </c>
+      <c r="W26">
+        <v>0.2672359114015977</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.5670397902528053</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1743704351765013</v>
+      </c>
+      <c r="C27">
+        <v>207.3136647966483</v>
+      </c>
+      <c r="D27">
+        <v>270.9136647966483</v>
+      </c>
+      <c r="E27">
+        <v>-163</v>
+      </c>
+      <c r="F27">
+        <v>137.7</v>
+      </c>
+      <c r="G27">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H27">
+        <v>250.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>35</v>
+      </c>
+      <c r="K27">
+        <v>52.9</v>
+      </c>
+      <c r="L27">
+        <v>-17.9</v>
+      </c>
+      <c r="M27">
+        <v>32.88276</v>
+      </c>
+      <c r="N27">
+        <v>-50.78276</v>
+      </c>
+      <c r="O27">
+        <v>-10.6643796</v>
+      </c>
+      <c r="P27">
+        <v>-40.1183804</v>
+      </c>
+      <c r="Q27">
+        <v>12.7816196</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1437944219201572</v>
+      </c>
+      <c r="T27">
+        <v>1.141176402721873</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.1143152217149655</v>
+      </c>
+      <c r="W27">
+        <v>0.2660984749455337</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.5443581986426931</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1763704351765014</v>
+      </c>
+      <c r="C28">
+        <v>197.8671199421659</v>
+      </c>
+      <c r="D28">
+        <v>266.9751199421659</v>
+      </c>
+      <c r="E28">
+        <v>-157.492</v>
+      </c>
+      <c r="F28">
+        <v>143.208</v>
+      </c>
+      <c r="G28">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H28">
+        <v>250.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>35</v>
+      </c>
+      <c r="K28">
+        <v>52.9</v>
+      </c>
+      <c r="L28">
+        <v>-17.9</v>
+      </c>
+      <c r="M28">
+        <v>34.1980704</v>
+      </c>
+      <c r="N28">
+        <v>-52.0980704</v>
+      </c>
+      <c r="O28">
+        <v>-10.940594784</v>
+      </c>
+      <c r="P28">
+        <v>-41.157475616</v>
+      </c>
+      <c r="Q28">
+        <v>11.742524384</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1452132654596188</v>
+      </c>
+      <c r="T28">
+        <v>1.156597705461358</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.1099184824182361</v>
+      </c>
+      <c r="W28">
+        <v>0.2650485336014748</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.5234213448487433</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1783704351765014</v>
+      </c>
+      <c r="C29">
+        <v>188.5334512809692</v>
+      </c>
+      <c r="D29">
+        <v>263.1494512809692</v>
+      </c>
+      <c r="E29">
+        <v>-151.984</v>
+      </c>
+      <c r="F29">
+        <v>148.716</v>
+      </c>
+      <c r="G29">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H29">
+        <v>250.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>35</v>
+      </c>
+      <c r="K29">
+        <v>52.9</v>
+      </c>
+      <c r="L29">
+        <v>-17.9</v>
+      </c>
+      <c r="M29">
+        <v>35.51338080000001</v>
+      </c>
+      <c r="N29">
+        <v>-53.41338080000001</v>
+      </c>
+      <c r="O29">
+        <v>-11.216809968</v>
+      </c>
+      <c r="P29">
+        <v>-42.19657083200001</v>
+      </c>
+      <c r="Q29">
+        <v>10.70342916799999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.146670981424819</v>
+      </c>
+      <c r="T29">
+        <v>1.17244150964576</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.1058474275138569</v>
+      </c>
+      <c r="W29">
+        <v>0.2640763656903091</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.5040353691136046</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1803704351765014</v>
+      </c>
+      <c r="C30">
+        <v>179.3078749246785</v>
+      </c>
+      <c r="D30">
+        <v>259.4318749246785</v>
+      </c>
+      <c r="E30">
+        <v>-146.476</v>
+      </c>
+      <c r="F30">
+        <v>154.224</v>
+      </c>
+      <c r="G30">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H30">
+        <v>250.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>35</v>
+      </c>
+      <c r="K30">
+        <v>52.9</v>
+      </c>
+      <c r="L30">
+        <v>-17.9</v>
+      </c>
+      <c r="M30">
+        <v>36.8286912</v>
+      </c>
+      <c r="N30">
+        <v>-54.7286912</v>
+      </c>
+      <c r="O30">
+        <v>-11.493025152</v>
+      </c>
+      <c r="P30">
+        <v>-43.235666048</v>
+      </c>
+      <c r="Q30">
+        <v>9.664333952</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1481691895001638</v>
+      </c>
+      <c r="T30">
+        <v>1.188725419501951</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.1020671622455049</v>
+      </c>
+      <c r="W30">
+        <v>0.2631736383442266</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.4860341059309758</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1823704351765014</v>
+      </c>
+      <c r="C31">
+        <v>170.1858735516836</v>
+      </c>
+      <c r="D31">
+        <v>255.8178735516836</v>
+      </c>
+      <c r="E31">
+        <v>-140.968</v>
+      </c>
+      <c r="F31">
+        <v>159.732</v>
+      </c>
+      <c r="G31">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H31">
+        <v>250.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>35</v>
+      </c>
+      <c r="K31">
+        <v>52.9</v>
+      </c>
+      <c r="L31">
+        <v>-17.9</v>
+      </c>
+      <c r="M31">
+        <v>38.1440016</v>
+      </c>
+      <c r="N31">
+        <v>-56.04400159999999</v>
+      </c>
+      <c r="O31">
+        <v>-11.769240336</v>
+      </c>
+      <c r="P31">
+        <v>-44.274761264</v>
+      </c>
+      <c r="Q31">
+        <v>8.625238736</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1497096006198844</v>
+      </c>
+      <c r="T31">
+        <v>1.205468031044233</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.09854760492669441</v>
+      </c>
+      <c r="W31">
+        <v>0.2623331680564946</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.4692743091747353</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1843704351765014</v>
+      </c>
+      <c r="C32">
+        <v>161.1631780952674</v>
+      </c>
+      <c r="D32">
+        <v>252.3031780952674</v>
+      </c>
+      <c r="E32">
+        <v>-135.46</v>
+      </c>
+      <c r="F32">
+        <v>165.24</v>
+      </c>
+      <c r="G32">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H32">
+        <v>250.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>35</v>
+      </c>
+      <c r="K32">
+        <v>52.9</v>
+      </c>
+      <c r="L32">
+        <v>-17.9</v>
+      </c>
+      <c r="M32">
+        <v>39.459312</v>
+      </c>
+      <c r="N32">
+        <v>-57.359312</v>
+      </c>
+      <c r="O32">
+        <v>-12.04545552</v>
+      </c>
+      <c r="P32">
+        <v>-45.31385648</v>
+      </c>
+      <c r="Q32">
+        <v>7.58614352</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1512940234858827</v>
+      </c>
+      <c r="T32">
+        <v>1.222689002916293</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.09526268476247127</v>
+      </c>
+      <c r="W32">
+        <v>0.2615487291212782</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.4536318322022441</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1863704351765013</v>
+      </c>
+      <c r="C33">
+        <v>152.2357509207999</v>
+      </c>
+      <c r="D33">
+        <v>248.8837509207999</v>
+      </c>
+      <c r="E33">
+        <v>-129.952</v>
+      </c>
+      <c r="F33">
+        <v>170.748</v>
+      </c>
+      <c r="G33">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H33">
+        <v>250.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>35</v>
+      </c>
+      <c r="K33">
+        <v>52.9</v>
+      </c>
+      <c r="L33">
+        <v>-17.9</v>
+      </c>
+      <c r="M33">
+        <v>40.7746224</v>
+      </c>
+      <c r="N33">
+        <v>-58.6746224</v>
+      </c>
+      <c r="O33">
+        <v>-12.321670704</v>
+      </c>
+      <c r="P33">
+        <v>-46.352951696</v>
+      </c>
+      <c r="Q33">
+        <v>6.547048304</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1529243716523448</v>
+      </c>
+      <c r="T33">
+        <v>1.240409133393341</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.09218969493142379</v>
+      </c>
+      <c r="W33">
+        <v>0.260814899149624</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.4389985472924944</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1883704351765013</v>
+      </c>
+      <c r="C34">
+        <v>143.3997703526201</v>
+      </c>
+      <c r="D34">
+        <v>245.5557703526201</v>
+      </c>
+      <c r="E34">
+        <v>-124.444</v>
+      </c>
+      <c r="F34">
+        <v>176.256</v>
+      </c>
+      <c r="G34">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H34">
+        <v>250.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>35</v>
+      </c>
+      <c r="K34">
+        <v>52.9</v>
+      </c>
+      <c r="L34">
+        <v>-17.9</v>
+      </c>
+      <c r="M34">
+        <v>42.0899328</v>
+      </c>
+      <c r="N34">
+        <v>-59.9899328</v>
+      </c>
+      <c r="O34">
+        <v>-12.597885888</v>
+      </c>
+      <c r="P34">
+        <v>-47.392046912</v>
+      </c>
+      <c r="Q34">
+        <v>5.507953088000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1546026712354675</v>
+      </c>
+      <c r="T34">
+        <v>1.258650444178537</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.08930876696481681</v>
+      </c>
+      <c r="W34">
+        <v>0.2601269335511983</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.4252798426896038</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1903704351765013</v>
+      </c>
+      <c r="C35">
+        <v>134.6516164259433</v>
+      </c>
+      <c r="D35">
+        <v>242.3156164259433</v>
+      </c>
+      <c r="E35">
+        <v>-118.936</v>
+      </c>
+      <c r="F35">
+        <v>181.764</v>
+      </c>
+      <c r="G35">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H35">
+        <v>250.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>35</v>
+      </c>
+      <c r="K35">
+        <v>52.9</v>
+      </c>
+      <c r="L35">
+        <v>-17.9</v>
+      </c>
+      <c r="M35">
+        <v>43.4052432</v>
+      </c>
+      <c r="N35">
+        <v>-61.3052432</v>
+      </c>
+      <c r="O35">
+        <v>-12.874101072</v>
+      </c>
+      <c r="P35">
+        <v>-48.431142128</v>
+      </c>
+      <c r="Q35">
+        <v>4.468857871999994</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1563310693136088</v>
+      </c>
+      <c r="T35">
+        <v>1.27743627170359</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.08660244069315569</v>
+      </c>
+      <c r="W35">
+        <v>0.2594806628375256</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.4123925747293129</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1923704351765013</v>
+      </c>
+      <c r="C36">
+        <v>125.9878577521147</v>
+      </c>
+      <c r="D36">
+        <v>239.1598577521147</v>
+      </c>
+      <c r="E36">
+        <v>-113.428</v>
+      </c>
+      <c r="F36">
+        <v>187.272</v>
+      </c>
+      <c r="G36">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H36">
+        <v>250.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>35</v>
+      </c>
+      <c r="K36">
+        <v>52.9</v>
+      </c>
+      <c r="L36">
+        <v>-17.9</v>
+      </c>
+      <c r="M36">
+        <v>44.7205536</v>
+      </c>
+      <c r="N36">
+        <v>-62.6205536</v>
+      </c>
+      <c r="O36">
+        <v>-13.150316256</v>
+      </c>
+      <c r="P36">
+        <v>-49.470237344</v>
+      </c>
+      <c r="Q36">
+        <v>3.429762655999994</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1581118430910877</v>
+      </c>
+      <c r="T36">
+        <v>1.296791366729402</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.08405531008453346</v>
+      </c>
+      <c r="W36">
+        <v>0.2588724080481866</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.4002633813549212</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1943704351765013</v>
+      </c>
+      <c r="C37">
+        <v>117.4052393970169</v>
+      </c>
+      <c r="D37">
+        <v>236.0852393970168</v>
+      </c>
+      <c r="E37">
+        <v>-107.92</v>
+      </c>
+      <c r="F37">
+        <v>192.78</v>
+      </c>
+      <c r="G37">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H37">
+        <v>250.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>35</v>
+      </c>
+      <c r="K37">
+        <v>52.9</v>
+      </c>
+      <c r="L37">
+        <v>-17.9</v>
+      </c>
+      <c r="M37">
+        <v>46.035864</v>
+      </c>
+      <c r="N37">
+        <v>-63.935864</v>
+      </c>
+      <c r="O37">
+        <v>-13.42653144</v>
+      </c>
+      <c r="P37">
+        <v>-50.50933256</v>
+      </c>
+      <c r="Q37">
+        <v>2.390667439999994</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1599474099078737</v>
+      </c>
+      <c r="T37">
+        <v>1.316742003140623</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.08165372979640392</v>
+      </c>
+      <c r="W37">
+        <v>0.2582989106753813</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.3888272847447807</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1963704351765014</v>
+      </c>
+      <c r="C38">
+        <v>108.9006716826158</v>
+      </c>
+      <c r="D38">
+        <v>233.0886716826157</v>
+      </c>
+      <c r="E38">
+        <v>-102.412</v>
+      </c>
+      <c r="F38">
+        <v>198.288</v>
+      </c>
+      <c r="G38">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H38">
+        <v>250.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>35</v>
+      </c>
+      <c r="K38">
+        <v>52.9</v>
+      </c>
+      <c r="L38">
+        <v>-17.9</v>
+      </c>
+      <c r="M38">
+        <v>47.3511744</v>
+      </c>
+      <c r="N38">
+        <v>-65.2511744</v>
+      </c>
+      <c r="O38">
+        <v>-13.702746624</v>
+      </c>
+      <c r="P38">
+        <v>-51.548427776</v>
+      </c>
+      <c r="Q38">
+        <v>1.351572224000002</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1618403381876842</v>
+      </c>
+      <c r="T38">
+        <v>1.337316096939695</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.07938557063539271</v>
+      </c>
+      <c r="W38">
+        <v>0.2577572742677318</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.3780265268352034</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1983704351765014</v>
+      </c>
+      <c r="C39">
+        <v>100.4712198306509</v>
+      </c>
+      <c r="D39">
+        <v>230.1672198306509</v>
+      </c>
+      <c r="E39">
+        <v>-96.904</v>
+      </c>
+      <c r="F39">
+        <v>203.796</v>
+      </c>
+      <c r="G39">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H39">
+        <v>250.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>35</v>
+      </c>
+      <c r="K39">
+        <v>52.9</v>
+      </c>
+      <c r="L39">
+        <v>-17.9</v>
+      </c>
+      <c r="M39">
+        <v>48.6664848</v>
+      </c>
+      <c r="N39">
+        <v>-66.5664848</v>
+      </c>
+      <c r="O39">
+        <v>-13.978961808</v>
+      </c>
+      <c r="P39">
+        <v>-52.587522992</v>
+      </c>
+      <c r="Q39">
+        <v>0.3124770079999948</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1637933594287586</v>
+      </c>
+      <c r="T39">
+        <v>1.358543336573659</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.077240014672274</v>
+      </c>
+      <c r="W39">
+        <v>0.2572449155037391</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.3678095936774952</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2003704351765014</v>
+      </c>
+      <c r="C40">
+        <v>92.11409437549918</v>
+      </c>
+      <c r="D40">
+        <v>227.3180943754992</v>
+      </c>
+      <c r="E40">
+        <v>-91.39600000000002</v>
+      </c>
+      <c r="F40">
+        <v>209.304</v>
+      </c>
+      <c r="G40">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H40">
+        <v>250.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>35</v>
+      </c>
+      <c r="K40">
+        <v>52.9</v>
+      </c>
+      <c r="L40">
+        <v>-17.9</v>
+      </c>
+      <c r="M40">
+        <v>49.98179519999999</v>
+      </c>
+      <c r="N40">
+        <v>-67.8817952</v>
+      </c>
+      <c r="O40">
+        <v>-14.255176992</v>
+      </c>
+      <c r="P40">
+        <v>-53.626618208</v>
+      </c>
+      <c r="Q40">
+        <v>-0.726618208000005</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1658093813550289</v>
+      </c>
+      <c r="T40">
+        <v>1.380455325873234</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.07520738270721417</v>
+      </c>
+      <c r="W40">
+        <v>0.2567595229904828</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.3581303938438771</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2023704351765014</v>
+      </c>
+      <c r="C41">
+        <v>83.82664228037928</v>
+      </c>
+      <c r="D41">
+        <v>224.5386422803793</v>
+      </c>
+      <c r="E41">
+        <v>-85.88800000000001</v>
+      </c>
+      <c r="F41">
+        <v>214.812</v>
+      </c>
+      <c r="G41">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H41">
+        <v>250.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>35</v>
+      </c>
+      <c r="K41">
+        <v>52.9</v>
+      </c>
+      <c r="L41">
+        <v>-17.9</v>
+      </c>
+      <c r="M41">
+        <v>51.2971056</v>
+      </c>
+      <c r="N41">
+        <v>-69.1971056</v>
+      </c>
+      <c r="O41">
+        <v>-14.531392176</v>
+      </c>
+      <c r="P41">
+        <v>-54.665713424</v>
+      </c>
+      <c r="Q41">
+        <v>-1.765713424000005</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.167891502360849</v>
+      </c>
+      <c r="T41">
+        <v>1.403085741051484</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.07327898827882404</v>
+      </c>
+      <c r="W41">
+        <v>0.2562990224009832</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.3489475632324954</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2043704351765014</v>
+      </c>
+      <c r="C42">
+        <v>75.60633869742355</v>
+      </c>
+      <c r="D42">
+        <v>221.8263386974236</v>
+      </c>
+      <c r="E42">
+        <v>-80.38</v>
+      </c>
+      <c r="F42">
+        <v>220.32</v>
+      </c>
+      <c r="G42">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H42">
+        <v>250.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>35</v>
+      </c>
+      <c r="K42">
+        <v>52.9</v>
+      </c>
+      <c r="L42">
+        <v>-17.9</v>
+      </c>
+      <c r="M42">
+        <v>52.612416</v>
+      </c>
+      <c r="N42">
+        <v>-70.512416</v>
+      </c>
+      <c r="O42">
+        <v>-14.80760736</v>
+      </c>
+      <c r="P42">
+        <v>-55.70480864</v>
+      </c>
+      <c r="Q42">
+        <v>-2.804808640000005</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1700430274001965</v>
+      </c>
+      <c r="T42">
+        <v>1.426470503402342</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.07144701357185344</v>
+      </c>
+      <c r="W42">
+        <v>0.2558615468409586</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.340223874151683</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2063704351765014</v>
+      </c>
+      <c r="C43">
+        <v>67.45077931782563</v>
+      </c>
+      <c r="D43">
+        <v>219.1787793178256</v>
+      </c>
+      <c r="E43">
+        <v>-74.87199999999999</v>
+      </c>
+      <c r="F43">
+        <v>225.828</v>
+      </c>
+      <c r="G43">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H43">
+        <v>250.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>35</v>
+      </c>
+      <c r="K43">
+        <v>52.9</v>
+      </c>
+      <c r="L43">
+        <v>-17.9</v>
+      </c>
+      <c r="M43">
+        <v>53.9277264</v>
+      </c>
+      <c r="N43">
+        <v>-71.8277264</v>
+      </c>
+      <c r="O43">
+        <v>-15.083822544</v>
+      </c>
+      <c r="P43">
+        <v>-56.743903856</v>
+      </c>
+      <c r="Q43">
+        <v>-3.843903856000004</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1722674854917253</v>
+      </c>
+      <c r="T43">
+        <v>1.450647969561704</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.06970440348473506</v>
+      </c>
+      <c r="W43">
+        <v>0.2554454115521548</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.3319257308796908</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2083704351765014</v>
+      </c>
+      <c r="C44">
+        <v>59.35767326334528</v>
+      </c>
+      <c r="D44">
+        <v>216.5936732633453</v>
+      </c>
+      <c r="E44">
+        <v>-69.364</v>
+      </c>
+      <c r="F44">
+        <v>231.336</v>
+      </c>
+      <c r="G44">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H44">
+        <v>250.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>35</v>
+      </c>
+      <c r="K44">
+        <v>52.9</v>
+      </c>
+      <c r="L44">
+        <v>-17.9</v>
+      </c>
+      <c r="M44">
+        <v>55.2430368</v>
+      </c>
+      <c r="N44">
+        <v>-73.1430368</v>
+      </c>
+      <c r="O44">
+        <v>-15.360037728</v>
+      </c>
+      <c r="P44">
+        <v>-57.78299907200001</v>
+      </c>
+      <c r="Q44">
+        <v>-4.882999072000011</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1745686490346861</v>
+      </c>
+      <c r="T44">
+        <v>1.475659141450698</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.06804477483033661</v>
+      </c>
+      <c r="W44">
+        <v>0.2550490922294844</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.3240227372873175</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2103704351765014</v>
+      </c>
+      <c r="C45">
+        <v>51.3248364749962</v>
+      </c>
+      <c r="D45">
+        <v>214.0688364749961</v>
+      </c>
+      <c r="E45">
+        <v>-63.85600000000002</v>
+      </c>
+      <c r="F45">
+        <v>236.844</v>
+      </c>
+      <c r="G45">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H45">
+        <v>250.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>35</v>
+      </c>
+      <c r="K45">
+        <v>52.9</v>
+      </c>
+      <c r="L45">
+        <v>-17.9</v>
+      </c>
+      <c r="M45">
+        <v>56.55834719999999</v>
+      </c>
+      <c r="N45">
+        <v>-74.45834719999999</v>
+      </c>
+      <c r="O45">
+        <v>-15.636252912</v>
+      </c>
+      <c r="P45">
+        <v>-58.822094288</v>
+      </c>
+      <c r="Q45">
+        <v>-5.922094287999997</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1769505551581016</v>
+      </c>
+      <c r="T45">
+        <v>1.501547898318254</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.0664623382063753</v>
+      </c>
+      <c r="W45">
+        <v>0.2546712063636825</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.3164873247922635</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2123704351765014</v>
+      </c>
+      <c r="C46">
+        <v>43.35018555881555</v>
+      </c>
+      <c r="D46">
+        <v>211.6021855588155</v>
+      </c>
+      <c r="E46">
+        <v>-58.34800000000001</v>
+      </c>
+      <c r="F46">
+        <v>242.352</v>
+      </c>
+      <c r="G46">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H46">
+        <v>250.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>35</v>
+      </c>
+      <c r="K46">
+        <v>52.9</v>
+      </c>
+      <c r="L46">
+        <v>-17.9</v>
+      </c>
+      <c r="M46">
+        <v>57.87365759999999</v>
+      </c>
+      <c r="N46">
+        <v>-75.77365759999999</v>
+      </c>
+      <c r="O46">
+        <v>-15.912468096</v>
+      </c>
+      <c r="P46">
+        <v>-59.861189504</v>
+      </c>
+      <c r="Q46">
+        <v>-6.961189503999996</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1794175293573534</v>
+      </c>
+      <c r="T46">
+        <v>1.528361253645366</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.06495183051986678</v>
+      </c>
+      <c r="W46">
+        <v>0.2543104971281442</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.3092944310469847</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2143704351765014</v>
+      </c>
+      <c r="C47">
+        <v>35.43173205226597</v>
+      </c>
+      <c r="D47">
+        <v>209.191732052266</v>
+      </c>
+      <c r="E47">
+        <v>-52.84</v>
+      </c>
+      <c r="F47">
+        <v>247.86</v>
+      </c>
+      <c r="G47">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H47">
+        <v>250.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>35</v>
+      </c>
+      <c r="K47">
+        <v>52.9</v>
+      </c>
+      <c r="L47">
+        <v>-17.9</v>
+      </c>
+      <c r="M47">
+        <v>59.188968</v>
+      </c>
+      <c r="N47">
+        <v>-77.08896799999999</v>
+      </c>
+      <c r="O47">
+        <v>-16.18868328</v>
+      </c>
+      <c r="P47">
+        <v>-60.90028472</v>
+      </c>
+      <c r="Q47">
+        <v>-8.000284720000003</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1819742117093053</v>
+      </c>
+      <c r="T47">
+        <v>1.556149640075282</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.06350845650831417</v>
+      </c>
+      <c r="W47">
+        <v>0.2539658194141854</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.3024212214681625</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2163704351765013</v>
+      </c>
+      <c r="C48">
+        <v>27.56757707810789</v>
+      </c>
+      <c r="D48">
+        <v>206.8355770781079</v>
+      </c>
+      <c r="E48">
+        <v>-47.33199999999999</v>
+      </c>
+      <c r="F48">
+        <v>253.368</v>
+      </c>
+      <c r="G48">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H48">
+        <v>250.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>35</v>
+      </c>
+      <c r="K48">
+        <v>52.9</v>
+      </c>
+      <c r="L48">
+        <v>-17.9</v>
+      </c>
+      <c r="M48">
+        <v>60.5042784</v>
+      </c>
+      <c r="N48">
+        <v>-78.40427840000001</v>
+      </c>
+      <c r="O48">
+        <v>-16.464898464</v>
+      </c>
+      <c r="P48">
+        <v>-61.93937993600001</v>
+      </c>
+      <c r="Q48">
+        <v>-9.03937993600001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1846255860002183</v>
+      </c>
+      <c r="T48">
+        <v>1.584967226002602</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.0621278378885682</v>
+      </c>
+      <c r="W48">
+        <v>0.2536361276877901</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.2958468470884201</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2183704351765014</v>
+      </c>
+      <c r="C49">
+        <v>19.75590635553255</v>
+      </c>
+      <c r="D49">
+        <v>204.5319063555325</v>
+      </c>
+      <c r="E49">
+        <v>-41.82400000000001</v>
+      </c>
+      <c r="F49">
+        <v>258.876</v>
+      </c>
+      <c r="G49">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H49">
+        <v>250.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>35</v>
+      </c>
+      <c r="K49">
+        <v>52.9</v>
+      </c>
+      <c r="L49">
+        <v>-17.9</v>
+      </c>
+      <c r="M49">
+        <v>61.8195888</v>
+      </c>
+      <c r="N49">
+        <v>-79.7195888</v>
+      </c>
+      <c r="O49">
+        <v>-16.741113648</v>
+      </c>
+      <c r="P49">
+        <v>-62.978475152</v>
+      </c>
+      <c r="Q49">
+        <v>-10.078475152</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1873770121511659</v>
+      </c>
+      <c r="T49">
+        <v>1.614872268002651</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.06080596899732208</v>
+      </c>
+      <c r="W49">
+        <v>0.2533204653965606</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.2895522333205813</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2203704351765014</v>
+      </c>
+      <c r="C50">
+        <v>11.99498554101001</v>
+      </c>
+      <c r="D50">
+        <v>202.27898554101</v>
+      </c>
+      <c r="E50">
+        <v>-36.31600000000003</v>
+      </c>
+      <c r="F50">
+        <v>264.384</v>
+      </c>
+      <c r="G50">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H50">
+        <v>250.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>35</v>
+      </c>
+      <c r="K50">
+        <v>52.9</v>
+      </c>
+      <c r="L50">
+        <v>-17.9</v>
+      </c>
+      <c r="M50">
+        <v>63.13489919999999</v>
+      </c>
+      <c r="N50">
+        <v>-81.03489919999998</v>
+      </c>
+      <c r="O50">
+        <v>-17.01732883199999</v>
+      </c>
+      <c r="P50">
+        <v>-64.01757036799999</v>
+      </c>
+      <c r="Q50">
+        <v>-11.117570368</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1902342623848421</v>
+      </c>
+      <c r="T50">
+        <v>1.645927503925779</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.05953917797654455</v>
+      </c>
+      <c r="W50">
+        <v>0.2530179557007989</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.2835198951264024</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2223704351765013</v>
+      </c>
+      <c r="C51">
+        <v>4.283155873705198</v>
+      </c>
+      <c r="D51">
+        <v>200.0751558737052</v>
+      </c>
+      <c r="E51">
+        <v>-30.80799999999999</v>
+      </c>
+      <c r="F51">
+        <v>269.892</v>
+      </c>
+      <c r="G51">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H51">
+        <v>250.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>35</v>
+      </c>
+      <c r="K51">
+        <v>52.9</v>
+      </c>
+      <c r="L51">
+        <v>-17.9</v>
+      </c>
+      <c r="M51">
+        <v>64.45020960000001</v>
+      </c>
+      <c r="N51">
+        <v>-82.3502096</v>
+      </c>
+      <c r="O51">
+        <v>-17.293544016</v>
+      </c>
+      <c r="P51">
+        <v>-65.056665584</v>
+      </c>
+      <c r="Q51">
+        <v>-12.156665584</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.19320356164729</v>
+      </c>
+      <c r="T51">
+        <v>1.678200592238049</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.05832409271171708</v>
+      </c>
+      <c r="W51">
+        <v>0.252727793339558</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.2777337748177005</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2243704351765013</v>
+      </c>
+      <c r="C52">
+        <v>-3.381169897513701</v>
+      </c>
+      <c r="D52">
+        <v>197.9188301024863</v>
+      </c>
+      <c r="E52">
+        <v>-25.30000000000001</v>
+      </c>
+      <c r="F52">
+        <v>275.4</v>
+      </c>
+      <c r="G52">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H52">
+        <v>250.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>35</v>
+      </c>
+      <c r="K52">
+        <v>52.9</v>
+      </c>
+      <c r="L52">
+        <v>-17.9</v>
+      </c>
+      <c r="M52">
+        <v>65.76552</v>
+      </c>
+      <c r="N52">
+        <v>-83.66551999999999</v>
+      </c>
+      <c r="O52">
+        <v>-17.56975919999999</v>
+      </c>
+      <c r="P52">
+        <v>-66.09576079999999</v>
+      </c>
+      <c r="Q52">
+        <v>-13.1957608</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1962916328802359</v>
+      </c>
+      <c r="T52">
+        <v>1.71176460408281</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.05715761085748275</v>
+      </c>
+      <c r="W52">
+        <v>0.2524492374727669</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.2721790993213464</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2263704351765014</v>
+      </c>
+      <c r="C53">
+        <v>-10.99951132649477</v>
+      </c>
+      <c r="D53">
+        <v>195.8084886735052</v>
+      </c>
+      <c r="E53">
+        <v>-19.79200000000003</v>
+      </c>
+      <c r="F53">
+        <v>280.908</v>
+      </c>
+      <c r="G53">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H53">
+        <v>250.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>35</v>
+      </c>
+      <c r="K53">
+        <v>52.9</v>
+      </c>
+      <c r="L53">
+        <v>-17.9</v>
+      </c>
+      <c r="M53">
+        <v>67.0808304</v>
+      </c>
+      <c r="N53">
+        <v>-84.9808304</v>
+      </c>
+      <c r="O53">
+        <v>-17.845974384</v>
+      </c>
+      <c r="P53">
+        <v>-67.134856016</v>
+      </c>
+      <c r="Q53">
+        <v>-14.234856016</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1995057478369753</v>
+      </c>
+      <c r="T53">
+        <v>1.746698575594704</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.05603687338968898</v>
+      </c>
+      <c r="W53">
+        <v>0.2521816053654578</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.2668422542366142</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2283704351765014</v>
+      </c>
+      <c r="C54">
+        <v>-18.57332384089028</v>
+      </c>
+      <c r="D54">
+        <v>193.7426761591097</v>
+      </c>
+      <c r="E54">
+        <v>-14.28399999999999</v>
+      </c>
+      <c r="F54">
+        <v>286.416</v>
+      </c>
+      <c r="G54">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H54">
+        <v>250.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>35</v>
+      </c>
+      <c r="K54">
+        <v>52.9</v>
+      </c>
+      <c r="L54">
+        <v>-17.9</v>
+      </c>
+      <c r="M54">
+        <v>68.3961408</v>
+      </c>
+      <c r="N54">
+        <v>-86.29614079999999</v>
+      </c>
+      <c r="O54">
+        <v>-18.122189568</v>
+      </c>
+      <c r="P54">
+        <v>-68.17395123199999</v>
+      </c>
+      <c r="Q54">
+        <v>-15.27395123199999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2028537842502456</v>
+      </c>
+      <c r="T54">
+        <v>1.783088129252927</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.05495924120911803</v>
+      </c>
+      <c r="W54">
+        <v>0.2519242668007374</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.2617106724243716</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2303704351765014</v>
+      </c>
+      <c r="C55">
+        <v>-26.1040020895523</v>
+      </c>
+      <c r="D55">
+        <v>191.7199979104477</v>
+      </c>
+      <c r="E55">
+        <v>-8.77600000000001</v>
+      </c>
+      <c r="F55">
+        <v>291.924</v>
+      </c>
+      <c r="G55">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H55">
+        <v>250.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>35</v>
+      </c>
+      <c r="K55">
+        <v>52.9</v>
+      </c>
+      <c r="L55">
+        <v>-17.9</v>
+      </c>
+      <c r="M55">
+        <v>69.7114512</v>
+      </c>
+      <c r="N55">
+        <v>-87.6114512</v>
+      </c>
+      <c r="O55">
+        <v>-18.398404752</v>
+      </c>
+      <c r="P55">
+        <v>-69.213046448</v>
+      </c>
+      <c r="Q55">
+        <v>-16.313046448</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2063442902981233</v>
+      </c>
+      <c r="T55">
+        <v>1.821026174556181</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.05392227439385165</v>
+      </c>
+      <c r="W55">
+        <v>0.2516766391252518</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.2567727352088176</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2323704351765014</v>
+      </c>
+      <c r="C56">
+        <v>-33.59288308241287</v>
+      </c>
+      <c r="D56">
+        <v>189.7391169175871</v>
+      </c>
+      <c r="E56">
+        <v>-3.267999999999972</v>
+      </c>
+      <c r="F56">
+        <v>297.432</v>
+      </c>
+      <c r="G56">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H56">
+        <v>250.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>35</v>
+      </c>
+      <c r="K56">
+        <v>52.9</v>
+      </c>
+      <c r="L56">
+        <v>-17.9</v>
+      </c>
+      <c r="M56">
+        <v>71.02676160000001</v>
+      </c>
+      <c r="N56">
+        <v>-88.92676160000002</v>
+      </c>
+      <c r="O56">
+        <v>-18.674619936</v>
+      </c>
+      <c r="P56">
+        <v>-70.25214166400002</v>
+      </c>
+      <c r="Q56">
+        <v>-17.35214166400002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2099865574785172</v>
+      </c>
+      <c r="T56">
+        <v>1.860613700090011</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.05292371375692846</v>
+      </c>
+      <c r="W56">
+        <v>0.2514381828451545</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.2520176845568023</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2343704351765014</v>
+      </c>
+      <c r="C57">
+        <v>-41.04124913770494</v>
+      </c>
+      <c r="D57">
+        <v>187.7987508622951</v>
+      </c>
+      <c r="E57">
+        <v>2.240000000000009</v>
+      </c>
+      <c r="F57">
+        <v>302.94</v>
+      </c>
+      <c r="G57">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H57">
+        <v>250.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>35</v>
+      </c>
+      <c r="K57">
+        <v>52.9</v>
+      </c>
+      <c r="L57">
+        <v>-17.9</v>
+      </c>
+      <c r="M57">
+        <v>72.342072</v>
+      </c>
+      <c r="N57">
+        <v>-90.24207200000001</v>
+      </c>
+      <c r="O57">
+        <v>-18.95083512</v>
+      </c>
+      <c r="P57">
+        <v>-71.29123688000001</v>
+      </c>
+      <c r="Q57">
+        <v>-18.39123688000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2137907032002621</v>
+      </c>
+      <c r="T57">
+        <v>1.901960671203123</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.05196146441589341</v>
+      </c>
+      <c r="W57">
+        <v>0.2512083977025154</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.2474355448375878</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2363704351765014</v>
+      </c>
+      <c r="C58">
+        <v>-48.45033065017441</v>
+      </c>
+      <c r="D58">
+        <v>185.8976693498256</v>
+      </c>
+      <c r="E58">
+        <v>7.74799999999999</v>
+      </c>
+      <c r="F58">
+        <v>308.448</v>
+      </c>
+      <c r="G58">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H58">
+        <v>250.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>35</v>
+      </c>
+      <c r="K58">
+        <v>52.9</v>
+      </c>
+      <c r="L58">
+        <v>-17.9</v>
+      </c>
+      <c r="M58">
+        <v>73.6573824</v>
+      </c>
+      <c r="N58">
+        <v>-91.55738239999999</v>
+      </c>
+      <c r="O58">
+        <v>-19.227050304</v>
+      </c>
+      <c r="P58">
+        <v>-72.33033209600001</v>
+      </c>
+      <c r="Q58">
+        <v>-19.43033209600001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2177677646366316</v>
+      </c>
+      <c r="T58">
+        <v>1.945187050094103</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.05103358112275246</v>
+      </c>
+      <c r="W58">
+        <v>0.2509868191721133</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.2430170529654878</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2383704351765014</v>
+      </c>
+      <c r="C59">
+        <v>-55.8213086928431</v>
+      </c>
+      <c r="D59">
+        <v>184.0346913071569</v>
+      </c>
+      <c r="E59">
+        <v>13.25600000000003</v>
+      </c>
+      <c r="F59">
+        <v>313.956</v>
+      </c>
+      <c r="G59">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H59">
+        <v>250.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>35</v>
+      </c>
+      <c r="K59">
+        <v>52.9</v>
+      </c>
+      <c r="L59">
+        <v>-17.9</v>
+      </c>
+      <c r="M59">
+        <v>74.9726928</v>
+      </c>
+      <c r="N59">
+        <v>-92.87269280000001</v>
+      </c>
+      <c r="O59">
+        <v>-19.503265488</v>
+      </c>
+      <c r="P59">
+        <v>-73.36942731200001</v>
+      </c>
+      <c r="Q59">
+        <v>-20.46942731200001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2219298056746929</v>
+      </c>
+      <c r="T59">
+        <v>1.990423958235826</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.05013825513814276</v>
+      </c>
+      <c r="W59">
+        <v>0.2507730153269885</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.2387535958959182</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2403704351765014</v>
+      </c>
+      <c r="C60">
+        <v>-63.15531746388137</v>
+      </c>
+      <c r="D60">
+        <v>182.2086825361185</v>
+      </c>
+      <c r="E60">
+        <v>18.76399999999995</v>
+      </c>
+      <c r="F60">
+        <v>319.4639999999999</v>
+      </c>
+      <c r="G60">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H60">
+        <v>250.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>35</v>
+      </c>
+      <c r="K60">
+        <v>52.9</v>
+      </c>
+      <c r="L60">
+        <v>-17.9</v>
+      </c>
+      <c r="M60">
+        <v>76.28800319999999</v>
+      </c>
+      <c r="N60">
+        <v>-94.1880032</v>
+      </c>
+      <c r="O60">
+        <v>-19.77948067199999</v>
+      </c>
+      <c r="P60">
+        <v>-74.40852252800001</v>
+      </c>
+      <c r="Q60">
+        <v>-21.50852252800001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2262900391431378</v>
+      </c>
+      <c r="T60">
+        <v>2.037815004860488</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.04927380246334721</v>
+      </c>
+      <c r="W60">
+        <v>0.2505665840282473</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.2346371545873678</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2423704351765014</v>
+      </c>
+      <c r="C61">
+        <v>-70.45344658924421</v>
+      </c>
+      <c r="D61">
+        <v>180.4185534107558</v>
+      </c>
+      <c r="E61">
+        <v>24.27199999999999</v>
+      </c>
+      <c r="F61">
+        <v>324.972</v>
+      </c>
+      <c r="G61">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H61">
+        <v>250.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>35</v>
+      </c>
+      <c r="K61">
+        <v>52.9</v>
+      </c>
+      <c r="L61">
+        <v>-17.9</v>
+      </c>
+      <c r="M61">
+        <v>77.60331359999999</v>
+      </c>
+      <c r="N61">
+        <v>-95.50331359999998</v>
+      </c>
+      <c r="O61">
+        <v>-20.05569585599999</v>
+      </c>
+      <c r="P61">
+        <v>-75.44761774399998</v>
+      </c>
+      <c r="Q61">
+        <v>-22.54761774399999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2308629669271168</v>
+      </c>
+      <c r="T61">
+        <v>2.087517809857085</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.04843865326905319</v>
+      </c>
+      <c r="W61">
+        <v>0.2503671504006499</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.230660253662158</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2443704351765014</v>
+      </c>
+      <c r="C62">
+        <v>-77.71674329089146</v>
+      </c>
+      <c r="D62">
+        <v>178.6632567091085</v>
+      </c>
+      <c r="E62">
+        <v>29.77999999999997</v>
+      </c>
+      <c r="F62">
+        <v>330.48</v>
+      </c>
+      <c r="G62">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H62">
+        <v>250.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>35</v>
+      </c>
+      <c r="K62">
+        <v>52.9</v>
+      </c>
+      <c r="L62">
+        <v>-17.9</v>
+      </c>
+      <c r="M62">
+        <v>78.91862399999999</v>
+      </c>
+      <c r="N62">
+        <v>-96.818624</v>
+      </c>
+      <c r="O62">
+        <v>-20.33191104</v>
+      </c>
+      <c r="P62">
+        <v>-76.48671296000001</v>
+      </c>
+      <c r="Q62">
+        <v>-23.58671296000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2356645411002947</v>
+      </c>
+      <c r="T62">
+        <v>2.139705755103512</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.04763134238123563</v>
+      </c>
+      <c r="W62">
+        <v>0.2501743645606391</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.2268159161011223</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2463704351765014</v>
+      </c>
+      <c r="C63">
+        <v>-84.94621442966118</v>
+      </c>
+      <c r="D63">
+        <v>176.9417855703388</v>
+      </c>
+      <c r="E63">
+        <v>35.28799999999995</v>
+      </c>
+      <c r="F63">
+        <v>335.9879999999999</v>
+      </c>
+      <c r="G63">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H63">
+        <v>250.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>35</v>
+      </c>
+      <c r="K63">
+        <v>52.9</v>
+      </c>
+      <c r="L63">
+        <v>-17.9</v>
+      </c>
+      <c r="M63">
+        <v>80.2339344</v>
+      </c>
+      <c r="N63">
+        <v>-98.13393439999999</v>
+      </c>
+      <c r="O63">
+        <v>-20.60812622399999</v>
+      </c>
+      <c r="P63">
+        <v>-77.525808176</v>
+      </c>
+      <c r="Q63">
+        <v>-24.625808176</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2407123498464562</v>
+      </c>
+      <c r="T63">
+        <v>2.194570005234372</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.04685050070285472</v>
+      </c>
+      <c r="W63">
+        <v>0.2499878995678417</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.2230976223945462</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2483704351765014</v>
+      </c>
+      <c r="C64">
+        <v>-92.14282843116689</v>
+      </c>
+      <c r="D64">
+        <v>175.2531715688331</v>
+      </c>
+      <c r="E64">
+        <v>40.79599999999999</v>
+      </c>
+      <c r="F64">
+        <v>341.496</v>
+      </c>
+      <c r="G64">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H64">
+        <v>250.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>35</v>
+      </c>
+      <c r="K64">
+        <v>52.9</v>
+      </c>
+      <c r="L64">
+        <v>-17.9</v>
+      </c>
+      <c r="M64">
+        <v>81.5492448</v>
+      </c>
+      <c r="N64">
+        <v>-99.4492448</v>
+      </c>
+      <c r="O64">
+        <v>-20.884341408</v>
+      </c>
+      <c r="P64">
+        <v>-78.56490339200001</v>
+      </c>
+      <c r="Q64">
+        <v>-25.66490339200001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2460258327371524</v>
+      </c>
+      <c r="T64">
+        <v>2.252321847477382</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.04609484746571189</v>
+      </c>
+      <c r="W64">
+        <v>0.249807449574812</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.2194992736462473</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2503704351765014</v>
+      </c>
+      <c r="C65">
+        <v>-99.30751710246091</v>
+      </c>
+      <c r="D65">
+        <v>173.5964828975391</v>
+      </c>
+      <c r="E65">
+        <v>46.30399999999997</v>
+      </c>
+      <c r="F65">
+        <v>347.004</v>
+      </c>
+      <c r="G65">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H65">
+        <v>250.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>35</v>
+      </c>
+      <c r="K65">
+        <v>52.9</v>
+      </c>
+      <c r="L65">
+        <v>-17.9</v>
+      </c>
+      <c r="M65">
+        <v>82.8645552</v>
+      </c>
+      <c r="N65">
+        <v>-100.7645552</v>
+      </c>
+      <c r="O65">
+        <v>-21.160556592</v>
+      </c>
+      <c r="P65">
+        <v>-79.603998608</v>
+      </c>
+      <c r="Q65">
+        <v>-26.703998608</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2516265309192376</v>
+      </c>
+      <c r="T65">
+        <v>2.313195410922716</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.0453631832202244</v>
+      </c>
+      <c r="W65">
+        <v>0.2496327281529896</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.2160151581915448</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2523704351765014</v>
+      </c>
+      <c r="C66">
+        <v>-106.4411773466242</v>
+      </c>
+      <c r="D66">
+        <v>171.9708226533758</v>
+      </c>
+      <c r="E66">
+        <v>51.81200000000001</v>
+      </c>
+      <c r="F66">
+        <v>352.512</v>
+      </c>
+      <c r="G66">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H66">
+        <v>250.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>35</v>
+      </c>
+      <c r="K66">
+        <v>52.9</v>
+      </c>
+      <c r="L66">
+        <v>-17.9</v>
+      </c>
+      <c r="M66">
+        <v>84.1798656</v>
+      </c>
+      <c r="N66">
+        <v>-102.0798656</v>
+      </c>
+      <c r="O66">
+        <v>-21.436771776</v>
+      </c>
+      <c r="P66">
+        <v>-80.643093824</v>
+      </c>
+      <c r="Q66">
+        <v>-27.74309382400001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2575383790003275</v>
+      </c>
+      <c r="T66">
+        <v>2.377450839003903</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.0446543834824084</v>
+      </c>
+      <c r="W66">
+        <v>0.2494634667755992</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.212639921344802</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2543704351765013</v>
+      </c>
+      <c r="C67">
+        <v>-113.5446727819103</v>
+      </c>
+      <c r="D67">
+        <v>170.3753272180897</v>
+      </c>
+      <c r="E67">
+        <v>57.31999999999999</v>
+      </c>
+      <c r="F67">
+        <v>358.02</v>
+      </c>
+      <c r="G67">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H67">
+        <v>250.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>35</v>
+      </c>
+      <c r="K67">
+        <v>52.9</v>
+      </c>
+      <c r="L67">
+        <v>-17.9</v>
+      </c>
+      <c r="M67">
+        <v>85.495176</v>
+      </c>
+      <c r="N67">
+        <v>-103.395176</v>
+      </c>
+      <c r="O67">
+        <v>-21.71298695999999</v>
+      </c>
+      <c r="P67">
+        <v>-81.68218904</v>
+      </c>
+      <c r="Q67">
+        <v>-28.78218904</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2637880469717654</v>
+      </c>
+      <c r="T67">
+        <v>2.445378005832586</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.04396739296729443</v>
+      </c>
+      <c r="W67">
+        <v>0.2492994134405899</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.2093685379394972</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2563704351765014</v>
+      </c>
+      <c r="C68">
+        <v>-120.6188352715875</v>
+      </c>
+      <c r="D68">
+        <v>168.8091647284125</v>
+      </c>
+      <c r="E68">
+        <v>62.82799999999997</v>
+      </c>
+      <c r="F68">
+        <v>363.528</v>
+      </c>
+      <c r="G68">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H68">
+        <v>250.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>35</v>
+      </c>
+      <c r="K68">
+        <v>52.9</v>
+      </c>
+      <c r="L68">
+        <v>-17.9</v>
+      </c>
+      <c r="M68">
+        <v>86.8104864</v>
+      </c>
+      <c r="N68">
+        <v>-104.7104864</v>
+      </c>
+      <c r="O68">
+        <v>-21.989202144</v>
+      </c>
+      <c r="P68">
+        <v>-82.72128425600002</v>
+      </c>
+      <c r="Q68">
+        <v>-29.82128425600002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2704053424709351</v>
+      </c>
+      <c r="T68">
+        <v>2.517300888357074</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.04330122034657784</v>
+      </c>
+      <c r="W68">
+        <v>0.2491403314187628</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.2061962873646566</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2583704351765013</v>
+      </c>
+      <c r="C69">
+        <v>-127.6644663701707</v>
+      </c>
+      <c r="D69">
+        <v>167.2715336298293</v>
+      </c>
+      <c r="E69">
+        <v>68.33600000000001</v>
+      </c>
+      <c r="F69">
+        <v>369.036</v>
+      </c>
+      <c r="G69">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H69">
+        <v>250.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>35</v>
+      </c>
+      <c r="K69">
+        <v>52.9</v>
+      </c>
+      <c r="L69">
+        <v>-17.9</v>
+      </c>
+      <c r="M69">
+        <v>88.1257968</v>
+      </c>
+      <c r="N69">
+        <v>-106.0257968</v>
+      </c>
+      <c r="O69">
+        <v>-22.26541732799999</v>
+      </c>
+      <c r="P69">
+        <v>-83.760379472</v>
+      </c>
+      <c r="Q69">
+        <v>-30.860379472</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2774236861821755</v>
+      </c>
+      <c r="T69">
+        <v>2.593582733458804</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.0426549334757334</v>
+      </c>
+      <c r="W69">
+        <v>0.2489859981140051</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.2031187308368256</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2603704351765014</v>
+      </c>
+      <c r="C70">
+        <v>-134.6823386913274</v>
+      </c>
+      <c r="D70">
+        <v>165.7616613086726</v>
+      </c>
+      <c r="E70">
+        <v>73.84399999999999</v>
+      </c>
+      <c r="F70">
+        <v>374.544</v>
+      </c>
+      <c r="G70">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H70">
+        <v>250.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>35</v>
+      </c>
+      <c r="K70">
+        <v>52.9</v>
+      </c>
+      <c r="L70">
+        <v>-17.9</v>
+      </c>
+      <c r="M70">
+        <v>89.4411072</v>
+      </c>
+      <c r="N70">
+        <v>-107.3411072</v>
+      </c>
+      <c r="O70">
+        <v>-22.541632512</v>
+      </c>
+      <c r="P70">
+        <v>-84.799474688</v>
+      </c>
+      <c r="Q70">
+        <v>-31.89947468800001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2848806763753685</v>
+      </c>
+      <c r="T70">
+        <v>2.674632193879391</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.04202765504226673</v>
+      </c>
+      <c r="W70">
+        <v>0.2488362040240933</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.2001316906774606</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2623704351765014</v>
+      </c>
+      <c r="C71">
+        <v>-141.6731972023628</v>
+      </c>
+      <c r="D71">
+        <v>164.2788027976372</v>
+      </c>
+      <c r="E71">
+        <v>79.35200000000003</v>
+      </c>
+      <c r="F71">
+        <v>380.052</v>
+      </c>
+      <c r="G71">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H71">
+        <v>250.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>35</v>
+      </c>
+      <c r="K71">
+        <v>52.9</v>
+      </c>
+      <c r="L71">
+        <v>-17.9</v>
+      </c>
+      <c r="M71">
+        <v>90.75641760000001</v>
+      </c>
+      <c r="N71">
+        <v>-108.6564176</v>
+      </c>
+      <c r="O71">
+        <v>-22.81784769599999</v>
+      </c>
+      <c r="P71">
+        <v>-85.838569904</v>
+      </c>
+      <c r="Q71">
+        <v>-32.938569904</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2928187627100578</v>
+      </c>
+      <c r="T71">
+        <v>2.760910651746468</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.0414185585923788</v>
+      </c>
+      <c r="W71">
+        <v>0.2486907517918601</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.1972312313922799</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2643704351765014</v>
+      </c>
+      <c r="C72">
+        <v>-148.6377604498388</v>
+      </c>
+      <c r="D72">
+        <v>162.8222395501612</v>
+      </c>
+      <c r="E72">
+        <v>84.86000000000001</v>
+      </c>
+      <c r="F72">
+        <v>385.56</v>
+      </c>
+      <c r="G72">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H72">
+        <v>250.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>35</v>
+      </c>
+      <c r="K72">
+        <v>52.9</v>
+      </c>
+      <c r="L72">
+        <v>-17.9</v>
+      </c>
+      <c r="M72">
+        <v>92.07172800000001</v>
+      </c>
+      <c r="N72">
+        <v>-109.971728</v>
+      </c>
+      <c r="O72">
+        <v>-23.09406288</v>
+      </c>
+      <c r="P72">
+        <v>-86.87766512000002</v>
+      </c>
+      <c r="Q72">
+        <v>-33.97766512000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3012860548003931</v>
+      </c>
+      <c r="T72">
+        <v>2.852941006804684</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.04082686489820196</v>
+      </c>
+      <c r="W72">
+        <v>0.2485494553376907</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.1944136423723903</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2663704351765014</v>
+      </c>
+      <c r="C73">
+        <v>-155.5767217205669</v>
+      </c>
+      <c r="D73">
+        <v>161.391278279433</v>
+      </c>
+      <c r="E73">
+        <v>90.36799999999994</v>
+      </c>
+      <c r="F73">
+        <v>391.0679999999999</v>
+      </c>
+      <c r="G73">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H73">
+        <v>250.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>35</v>
+      </c>
+      <c r="K73">
+        <v>52.9</v>
+      </c>
+      <c r="L73">
+        <v>-17.9</v>
+      </c>
+      <c r="M73">
+        <v>93.38703839999998</v>
+      </c>
+      <c r="N73">
+        <v>-111.2870384</v>
+      </c>
+      <c r="O73">
+        <v>-23.37027806399999</v>
+      </c>
+      <c r="P73">
+        <v>-87.91676033599998</v>
+      </c>
+      <c r="Q73">
+        <v>-35.01676033599998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3103372980693721</v>
+      </c>
+      <c r="T73">
+        <v>2.951318282901397</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.04025183863203011</v>
+      </c>
+      <c r="W73">
+        <v>0.2484121390653288</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.1916754220572863</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2683704351765013</v>
+      </c>
+      <c r="C74">
+        <v>-162.4907501419126</v>
+      </c>
+      <c r="D74">
+        <v>159.9852498580874</v>
+      </c>
+      <c r="E74">
+        <v>95.87599999999998</v>
+      </c>
+      <c r="F74">
+        <v>396.576</v>
+      </c>
+      <c r="G74">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H74">
+        <v>250.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>35</v>
+      </c>
+      <c r="K74">
+        <v>52.9</v>
+      </c>
+      <c r="L74">
+        <v>-17.9</v>
+      </c>
+      <c r="M74">
+        <v>94.7023488</v>
+      </c>
+      <c r="N74">
+        <v>-112.6023488</v>
+      </c>
+      <c r="O74">
+        <v>-23.64649324799999</v>
+      </c>
+      <c r="P74">
+        <v>-88.955855552</v>
+      </c>
+      <c r="Q74">
+        <v>-36.055855552</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3200350587147068</v>
+      </c>
+      <c r="T74">
+        <v>3.056722507290732</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.03969278531769636</v>
+      </c>
+      <c r="W74">
+        <v>0.2482786371338659</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.1890132634176016</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2703704351765014</v>
+      </c>
+      <c r="C75">
+        <v>-169.3804917250827</v>
+      </c>
+      <c r="D75">
+        <v>158.6035082749172</v>
+      </c>
+      <c r="E75">
+        <v>101.384</v>
+      </c>
+      <c r="F75">
+        <v>402.0839999999999</v>
+      </c>
+      <c r="G75">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H75">
+        <v>250.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>35</v>
+      </c>
+      <c r="K75">
+        <v>52.9</v>
+      </c>
+      <c r="L75">
+        <v>-17.9</v>
+      </c>
+      <c r="M75">
+        <v>96.0176592</v>
+      </c>
+      <c r="N75">
+        <v>-113.9176592</v>
+      </c>
+      <c r="O75">
+        <v>-23.922708432</v>
+      </c>
+      <c r="P75">
+        <v>-89.99495076800001</v>
+      </c>
+      <c r="Q75">
+        <v>-37.09495076800001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3304511720004367</v>
+      </c>
+      <c r="T75">
+        <v>3.169934452005204</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.03914904853252243</v>
+      </c>
+      <c r="W75">
+        <v>0.2481487927895664</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.1864240406310593</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2723704351765013</v>
+      </c>
+      <c r="C76">
+        <v>-176.2465703548123</v>
+      </c>
+      <c r="D76">
+        <v>157.2454296451877</v>
+      </c>
+      <c r="E76">
+        <v>106.892</v>
+      </c>
+      <c r="F76">
+        <v>407.592</v>
+      </c>
+      <c r="G76">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H76">
+        <v>250.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>35</v>
+      </c>
+      <c r="K76">
+        <v>52.9</v>
+      </c>
+      <c r="L76">
+        <v>-17.9</v>
+      </c>
+      <c r="M76">
+        <v>97.3329696</v>
+      </c>
+      <c r="N76">
+        <v>-115.2329696</v>
+      </c>
+      <c r="O76">
+        <v>-24.19892361599999</v>
+      </c>
+      <c r="P76">
+        <v>-91.03404598399999</v>
+      </c>
+      <c r="Q76">
+        <v>-38.13404598399999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3416685247696842</v>
+      </c>
+      <c r="T76">
+        <v>3.291855007851557</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.038620007336137</v>
+      </c>
+      <c r="W76">
+        <v>0.2480224577518695</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.1839047968387475</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2743704351765013</v>
+      </c>
+      <c r="C77">
+        <v>-183.0895887286364</v>
+      </c>
+      <c r="D77">
+        <v>155.9104112713636</v>
+      </c>
+      <c r="E77">
+        <v>112.4</v>
+      </c>
+      <c r="F77">
+        <v>413.1</v>
+      </c>
+      <c r="G77">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H77">
+        <v>250.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>35</v>
+      </c>
+      <c r="K77">
+        <v>52.9</v>
+      </c>
+      <c r="L77">
+        <v>-17.9</v>
+      </c>
+      <c r="M77">
+        <v>98.64828</v>
+      </c>
+      <c r="N77">
+        <v>-116.54828</v>
+      </c>
+      <c r="O77">
+        <v>-24.4751388</v>
+      </c>
+      <c r="P77">
+        <v>-92.07314120000001</v>
+      </c>
+      <c r="Q77">
+        <v>-39.17314120000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3537832657604716</v>
+      </c>
+      <c r="T77">
+        <v>3.42352920816562</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.0381050739049885</v>
+      </c>
+      <c r="W77">
+        <v>0.2478994916485112</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.1814527328808977</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2763704351765014</v>
+      </c>
+      <c r="C78">
+        <v>-189.9101292487187</v>
+      </c>
+      <c r="D78">
+        <v>154.5978707512813</v>
+      </c>
+      <c r="E78">
+        <v>117.908</v>
+      </c>
+      <c r="F78">
+        <v>418.6079999999999</v>
+      </c>
+      <c r="G78">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H78">
+        <v>250.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>35</v>
+      </c>
+      <c r="K78">
+        <v>52.9</v>
+      </c>
+      <c r="L78">
+        <v>-17.9</v>
+      </c>
+      <c r="M78">
+        <v>99.96359039999999</v>
+      </c>
+      <c r="N78">
+        <v>-117.8635904</v>
+      </c>
+      <c r="O78">
+        <v>-24.75135398399999</v>
+      </c>
+      <c r="P78">
+        <v>-93.112236416</v>
+      </c>
+      <c r="Q78">
+        <v>-40.212236416</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3669075685004913</v>
+      </c>
+      <c r="T78">
+        <v>3.566176258505855</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.03760369135360708</v>
+      </c>
+      <c r="W78">
+        <v>0.2477797614952414</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.1790651969219386</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2783704351765013</v>
+      </c>
+      <c r="C79">
+        <v>-196.7087548690076</v>
+      </c>
+      <c r="D79">
+        <v>153.3072451309924</v>
+      </c>
+      <c r="E79">
+        <v>123.416</v>
+      </c>
+      <c r="F79">
+        <v>424.116</v>
+      </c>
+      <c r="G79">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H79">
+        <v>250.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>35</v>
+      </c>
+      <c r="K79">
+        <v>52.9</v>
+      </c>
+      <c r="L79">
+        <v>-17.9</v>
+      </c>
+      <c r="M79">
+        <v>101.2789008</v>
+      </c>
+      <c r="N79">
+        <v>-119.1789008</v>
+      </c>
+      <c r="O79">
+        <v>-25.027569168</v>
+      </c>
+      <c r="P79">
+        <v>-94.15133163200001</v>
+      </c>
+      <c r="Q79">
+        <v>-41.25133163200001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3811731149570344</v>
+      </c>
+      <c r="T79">
+        <v>3.721227400180022</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.03711533172563815</v>
+      </c>
+      <c r="W79">
+        <v>0.2476631412160824</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.1767396748839913</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2803704351765013</v>
+      </c>
+      <c r="C80">
+        <v>-203.4860099003112</v>
+      </c>
+      <c r="D80">
+        <v>152.0379900996888</v>
+      </c>
+      <c r="E80">
+        <v>128.924</v>
+      </c>
+      <c r="F80">
+        <v>429.624</v>
+      </c>
+      <c r="G80">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H80">
+        <v>250.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>35</v>
+      </c>
+      <c r="K80">
+        <v>52.9</v>
+      </c>
+      <c r="L80">
+        <v>-17.9</v>
+      </c>
+      <c r="M80">
+        <v>102.5942112</v>
+      </c>
+      <c r="N80">
+        <v>-120.4942112</v>
+      </c>
+      <c r="O80">
+        <v>-25.30378435199999</v>
+      </c>
+      <c r="P80">
+        <v>-95.190426848</v>
+      </c>
+      <c r="Q80">
+        <v>-42.290426848</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3967355292732632</v>
+      </c>
+      <c r="T80">
+        <v>3.890374100188204</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.03663949413941202</v>
+      </c>
+      <c r="W80">
+        <v>0.2475495112004916</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.1744737816162476</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2823704351765013</v>
+      </c>
+      <c r="C81">
+        <v>-210.2424207757076</v>
+      </c>
+      <c r="D81">
+        <v>150.7895792242924</v>
+      </c>
+      <c r="E81">
+        <v>134.432</v>
+      </c>
+      <c r="F81">
+        <v>435.132</v>
+      </c>
+      <c r="G81">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H81">
+        <v>250.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>35</v>
+      </c>
+      <c r="K81">
+        <v>52.9</v>
+      </c>
+      <c r="L81">
+        <v>-17.9</v>
+      </c>
+      <c r="M81">
+        <v>103.9095216</v>
+      </c>
+      <c r="N81">
+        <v>-121.8095216</v>
+      </c>
+      <c r="O81">
+        <v>-25.579999536</v>
+      </c>
+      <c r="P81">
+        <v>-96.22952206400001</v>
+      </c>
+      <c r="Q81">
+        <v>-43.32952206400001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4137800782862758</v>
+      </c>
+      <c r="T81">
+        <v>4.075630009720976</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.03617570307435617</v>
+      </c>
+      <c r="W81">
+        <v>0.2474387578941563</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.1722652527350295</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2843704351765014</v>
+      </c>
+      <c r="C82">
+        <v>-216.9784967785532</v>
+      </c>
+      <c r="D82">
+        <v>149.5615032214468</v>
+      </c>
+      <c r="E82">
+        <v>139.94</v>
+      </c>
+      <c r="F82">
+        <v>440.64</v>
+      </c>
+      <c r="G82">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H82">
+        <v>250.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>35</v>
+      </c>
+      <c r="K82">
+        <v>52.9</v>
+      </c>
+      <c r="L82">
+        <v>-17.9</v>
+      </c>
+      <c r="M82">
+        <v>105.224832</v>
+      </c>
+      <c r="N82">
+        <v>-123.124832</v>
+      </c>
+      <c r="O82">
+        <v>-25.85621471999999</v>
+      </c>
+      <c r="P82">
+        <v>-97.26861728</v>
+      </c>
+      <c r="Q82">
+        <v>-44.36861728</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4325290822005896</v>
+      </c>
+      <c r="T82">
+        <v>4.279411510207026</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.03572350678592672</v>
+      </c>
+      <c r="W82">
+        <v>0.2473307734204793</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.1701119370758415</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2863704351765014</v>
+      </c>
+      <c r="C83">
+        <v>-223.6947307352033</v>
+      </c>
+      <c r="D83">
+        <v>148.3532692647967</v>
+      </c>
+      <c r="E83">
+        <v>145.448</v>
+      </c>
+      <c r="F83">
+        <v>446.148</v>
+      </c>
+      <c r="G83">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H83">
+        <v>250.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>35</v>
+      </c>
+      <c r="K83">
+        <v>52.9</v>
+      </c>
+      <c r="L83">
+        <v>-17.9</v>
+      </c>
+      <c r="M83">
+        <v>106.5401424</v>
+      </c>
+      <c r="N83">
+        <v>-124.4401424</v>
+      </c>
+      <c r="O83">
+        <v>-26.13242990399999</v>
+      </c>
+      <c r="P83">
+        <v>-98.30771249599999</v>
+      </c>
+      <c r="Q83">
+        <v>-45.40771249599999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4532516654743049</v>
+      </c>
+      <c r="T83">
+        <v>4.504643694954765</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.03528247583795232</v>
+      </c>
+      <c r="W83">
+        <v>0.2472254552301031</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.1680117897045348</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2883704351765014</v>
+      </c>
+      <c r="C84">
+        <v>-230.3915996744258</v>
+      </c>
+      <c r="D84">
+        <v>147.1644003255742</v>
+      </c>
+      <c r="E84">
+        <v>150.956</v>
+      </c>
+      <c r="F84">
+        <v>451.656</v>
+      </c>
+      <c r="G84">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H84">
+        <v>250.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>35</v>
+      </c>
+      <c r="K84">
+        <v>52.9</v>
+      </c>
+      <c r="L84">
+        <v>-17.9</v>
+      </c>
+      <c r="M84">
+        <v>107.8554528</v>
+      </c>
+      <c r="N84">
+        <v>-125.7554528</v>
+      </c>
+      <c r="O84">
+        <v>-26.408645088</v>
+      </c>
+      <c r="P84">
+        <v>-99.346807712</v>
+      </c>
+      <c r="Q84">
+        <v>-46.446807712</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4762767580006552</v>
+      </c>
+      <c r="T84">
+        <v>4.754901678007807</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.03485220174236753</v>
+      </c>
+      <c r="W84">
+        <v>0.2471227057760774</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.1659628654398453</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2903704351765014</v>
+      </c>
+      <c r="C85">
+        <v>-237.0695654553597</v>
+      </c>
+      <c r="D85">
+        <v>145.9944345446403</v>
+      </c>
+      <c r="E85">
+        <v>156.464</v>
+      </c>
+      <c r="F85">
+        <v>457.164</v>
+      </c>
+      <c r="G85">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H85">
+        <v>250.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>35</v>
+      </c>
+      <c r="K85">
+        <v>52.9</v>
+      </c>
+      <c r="L85">
+        <v>-17.9</v>
+      </c>
+      <c r="M85">
+        <v>109.1707632</v>
+      </c>
+      <c r="N85">
+        <v>-127.0707632</v>
+      </c>
+      <c r="O85">
+        <v>-26.68486027199999</v>
+      </c>
+      <c r="P85">
+        <v>-100.385902928</v>
+      </c>
+      <c r="Q85">
+        <v>-47.48590292799999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5020106849418702</v>
+      </c>
+      <c r="T85">
+        <v>5.034601776714148</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.03443229569727877</v>
+      </c>
+      <c r="W85">
+        <v>0.2470224322125102</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.1639633128441846</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2923704351765014</v>
+      </c>
+      <c r="C86">
+        <v>-243.7290753657561</v>
+      </c>
+      <c r="D86">
+        <v>144.8429246342439</v>
+      </c>
+      <c r="E86">
+        <v>161.972</v>
+      </c>
+      <c r="F86">
+        <v>462.672</v>
+      </c>
+      <c r="G86">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H86">
+        <v>250.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>35</v>
+      </c>
+      <c r="K86">
+        <v>52.9</v>
+      </c>
+      <c r="L86">
+        <v>-17.9</v>
+      </c>
+      <c r="M86">
+        <v>110.4860736</v>
+      </c>
+      <c r="N86">
+        <v>-128.3860736</v>
+      </c>
+      <c r="O86">
+        <v>-26.961075456</v>
+      </c>
+      <c r="P86">
+        <v>-101.424998144</v>
+      </c>
+      <c r="Q86">
+        <v>-48.524998144</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5309613527507369</v>
+      </c>
+      <c r="T86">
+        <v>5.34926438775878</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.0340223874151683</v>
+      </c>
+      <c r="W86">
+        <v>0.2469245461147422</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.1620113686436586</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2943704351765014</v>
+      </c>
+      <c r="C87">
+        <v>-250.3705626921302</v>
+      </c>
+      <c r="D87">
+        <v>143.7094373078697</v>
+      </c>
+      <c r="E87">
+        <v>167.48</v>
+      </c>
+      <c r="F87">
+        <v>468.1799999999999</v>
+      </c>
+      <c r="G87">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H87">
+        <v>250.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>35</v>
+      </c>
+      <c r="K87">
+        <v>52.9</v>
+      </c>
+      <c r="L87">
+        <v>-17.9</v>
+      </c>
+      <c r="M87">
+        <v>111.801384</v>
+      </c>
+      <c r="N87">
+        <v>-129.701384</v>
+      </c>
+      <c r="O87">
+        <v>-27.23729063999999</v>
+      </c>
+      <c r="P87">
+        <v>-102.46409336</v>
+      </c>
+      <c r="Q87">
+        <v>-49.56409335999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5637721096007862</v>
+      </c>
+      <c r="T87">
+        <v>5.705882013609367</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.03362212403381339</v>
+      </c>
+      <c r="W87">
+        <v>0.2468289632192747</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.1601053525419684</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2963704351765014</v>
+      </c>
+      <c r="C88">
+        <v>-256.9944472633497</v>
+      </c>
+      <c r="D88">
+        <v>142.5935527366503</v>
+      </c>
+      <c r="E88">
+        <v>172.9879999999999</v>
+      </c>
+      <c r="F88">
+        <v>473.6879999999999</v>
+      </c>
+      <c r="G88">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H88">
+        <v>250.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>35</v>
+      </c>
+      <c r="K88">
+        <v>52.9</v>
+      </c>
+      <c r="L88">
+        <v>-17.9</v>
+      </c>
+      <c r="M88">
+        <v>113.1166944</v>
+      </c>
+      <c r="N88">
+        <v>-131.0166944</v>
+      </c>
+      <c r="O88">
+        <v>-27.51350582399999</v>
+      </c>
+      <c r="P88">
+        <v>-103.503188576</v>
+      </c>
+      <c r="Q88">
+        <v>-50.60318857599999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6012701174294135</v>
+      </c>
+      <c r="T88">
+        <v>6.113445014581464</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.03323116910318765</v>
+      </c>
+      <c r="W88">
+        <v>0.2467356031818412</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.1582436623961316</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2983704351765014</v>
+      </c>
+      <c r="C89">
+        <v>-263.601135969093</v>
+      </c>
+      <c r="D89">
+        <v>141.494864030907</v>
+      </c>
+      <c r="E89">
+        <v>178.496</v>
+      </c>
+      <c r="F89">
+        <v>479.196</v>
+      </c>
+      <c r="G89">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H89">
+        <v>250.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>35</v>
+      </c>
+      <c r="K89">
+        <v>52.9</v>
+      </c>
+      <c r="L89">
+        <v>-17.9</v>
+      </c>
+      <c r="M89">
+        <v>114.4320048</v>
+      </c>
+      <c r="N89">
+        <v>-132.3320048</v>
+      </c>
+      <c r="O89">
+        <v>-27.78972100799999</v>
+      </c>
+      <c r="P89">
+        <v>-104.542283792</v>
+      </c>
+      <c r="Q89">
+        <v>-51.64228379200001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6445370495393685</v>
+      </c>
+      <c r="T89">
+        <v>6.583710015703114</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.03284920164223146</v>
+      </c>
+      <c r="W89">
+        <v>0.2466443893521649</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.1564247697249117</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3003704351765014</v>
+      </c>
+      <c r="C90">
+        <v>-270.1910232545229</v>
+      </c>
+      <c r="D90">
+        <v>140.4129767454771</v>
+      </c>
+      <c r="E90">
+        <v>184.004</v>
+      </c>
+      <c r="F90">
+        <v>484.704</v>
+      </c>
+      <c r="G90">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H90">
+        <v>250.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>35</v>
+      </c>
+      <c r="K90">
+        <v>52.9</v>
+      </c>
+      <c r="L90">
+        <v>-17.9</v>
+      </c>
+      <c r="M90">
+        <v>115.7473152</v>
+      </c>
+      <c r="N90">
+        <v>-133.6473152</v>
+      </c>
+      <c r="O90">
+        <v>-28.06593619199999</v>
+      </c>
+      <c r="P90">
+        <v>-105.581379008</v>
+      </c>
+      <c r="Q90">
+        <v>-52.68137900799999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6950151370009827</v>
+      </c>
+      <c r="T90">
+        <v>7.132352517011709</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.03247591525993339</v>
+      </c>
+      <c r="W90">
+        <v>0.2465552485640721</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.1546472155234924</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3023704351765014</v>
+      </c>
+      <c r="C91">
+        <v>-276.7644915924376</v>
+      </c>
+      <c r="D91">
+        <v>139.3475084075624</v>
+      </c>
+      <c r="E91">
+        <v>189.512</v>
+      </c>
+      <c r="F91">
+        <v>490.212</v>
+      </c>
+      <c r="G91">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H91">
+        <v>250.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>35</v>
+      </c>
+      <c r="K91">
+        <v>52.9</v>
+      </c>
+      <c r="L91">
+        <v>-17.9</v>
+      </c>
+      <c r="M91">
+        <v>117.0626256</v>
+      </c>
+      <c r="N91">
+        <v>-134.9626256</v>
+      </c>
+      <c r="O91">
+        <v>-28.34215137599999</v>
+      </c>
+      <c r="P91">
+        <v>-106.620474224</v>
+      </c>
+      <c r="Q91">
+        <v>-53.72047422400001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7546710585465266</v>
+      </c>
+      <c r="T91">
+        <v>7.780748200376411</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.03211101733566447</v>
+      </c>
+      <c r="W91">
+        <v>0.2464681109397567</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.152909606360307</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3043704351765014</v>
+      </c>
+      <c r="C92">
+        <v>-283.3219119340878</v>
+      </c>
+      <c r="D92">
+        <v>138.2980880659122</v>
+      </c>
+      <c r="E92">
+        <v>195.02</v>
+      </c>
+      <c r="F92">
+        <v>495.72</v>
+      </c>
+      <c r="G92">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H92">
+        <v>250.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>35</v>
+      </c>
+      <c r="K92">
+        <v>52.9</v>
+      </c>
+      <c r="L92">
+        <v>-17.9</v>
+      </c>
+      <c r="M92">
+        <v>118.377936</v>
+      </c>
+      <c r="N92">
+        <v>-136.277936</v>
+      </c>
+      <c r="O92">
+        <v>-28.61836656</v>
+      </c>
+      <c r="P92">
+        <v>-107.65956944</v>
+      </c>
+      <c r="Q92">
+        <v>-54.75956944000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8262581644011793</v>
+      </c>
+      <c r="T92">
+        <v>8.558823020414053</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.03175422825415709</v>
+      </c>
+      <c r="W92">
+        <v>0.2463829097070928</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.1512106107340814</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3063704351765014</v>
+      </c>
+      <c r="C93">
+        <v>-289.8636441397755</v>
+      </c>
+      <c r="D93">
+        <v>137.2643558602245</v>
+      </c>
+      <c r="E93">
+        <v>200.528</v>
+      </c>
+      <c r="F93">
+        <v>501.228</v>
+      </c>
+      <c r="G93">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H93">
+        <v>250.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>35</v>
+      </c>
+      <c r="K93">
+        <v>52.9</v>
+      </c>
+      <c r="L93">
+        <v>-17.9</v>
+      </c>
+      <c r="M93">
+        <v>119.6932464</v>
+      </c>
+      <c r="N93">
+        <v>-137.5932464</v>
+      </c>
+      <c r="O93">
+        <v>-28.894581744</v>
+      </c>
+      <c r="P93">
+        <v>-108.698664656</v>
+      </c>
+      <c r="Q93">
+        <v>-55.79866465600001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9137535160013104</v>
+      </c>
+      <c r="T93">
+        <v>9.509803356015615</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.0314052806909246</v>
+      </c>
+      <c r="W93">
+        <v>0.2462995810289928</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.1495489556710696</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3083704351765014</v>
+      </c>
+      <c r="C94">
+        <v>-296.3900373902842</v>
+      </c>
+      <c r="D94">
+        <v>136.2459626097158</v>
+      </c>
+      <c r="E94">
+        <v>206.036</v>
+      </c>
+      <c r="F94">
+        <v>506.736</v>
+      </c>
+      <c r="G94">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H94">
+        <v>250.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>35</v>
+      </c>
+      <c r="K94">
+        <v>52.9</v>
+      </c>
+      <c r="L94">
+        <v>-17.9</v>
+      </c>
+      <c r="M94">
+        <v>121.0085568</v>
+      </c>
+      <c r="N94">
+        <v>-138.9085568</v>
+      </c>
+      <c r="O94">
+        <v>-29.170796928</v>
+      </c>
+      <c r="P94">
+        <v>-109.737759872</v>
+      </c>
+      <c r="Q94">
+        <v>-56.83775987200001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.023122705501474</v>
+      </c>
+      <c r="T94">
+        <v>10.69852877551757</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.0310639189442841</v>
+      </c>
+      <c r="W94">
+        <v>0.2462180638438951</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.1479234235442102</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3103704351765014</v>
+      </c>
+      <c r="C95">
+        <v>-302.9014305801296</v>
+      </c>
+      <c r="D95">
+        <v>135.2425694198704</v>
+      </c>
+      <c r="E95">
+        <v>211.544</v>
+      </c>
+      <c r="F95">
+        <v>512.244</v>
+      </c>
+      <c r="G95">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H95">
+        <v>250.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>35</v>
+      </c>
+      <c r="K95">
+        <v>52.9</v>
+      </c>
+      <c r="L95">
+        <v>-17.9</v>
+      </c>
+      <c r="M95">
+        <v>122.3238672</v>
+      </c>
+      <c r="N95">
+        <v>-140.2238672</v>
+      </c>
+      <c r="O95">
+        <v>-29.447012112</v>
+      </c>
+      <c r="P95">
+        <v>-110.776855088</v>
+      </c>
+      <c r="Q95">
+        <v>-57.87685508800001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.163740234858828</v>
+      </c>
+      <c r="T95">
+        <v>12.22689002916294</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.0307298983104746</v>
+      </c>
+      <c r="W95">
+        <v>0.2461382997165414</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.146332849097498</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3123704351765014</v>
+      </c>
+      <c r="C96">
+        <v>-309.3981526935597</v>
+      </c>
+      <c r="D96">
+        <v>134.2538473064402</v>
+      </c>
+      <c r="E96">
+        <v>217.052</v>
+      </c>
+      <c r="F96">
+        <v>517.752</v>
+      </c>
+      <c r="G96">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H96">
+        <v>250.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>35</v>
+      </c>
+      <c r="K96">
+        <v>52.9</v>
+      </c>
+      <c r="L96">
+        <v>-17.9</v>
+      </c>
+      <c r="M96">
+        <v>123.6391776</v>
+      </c>
+      <c r="N96">
+        <v>-141.5391776</v>
+      </c>
+      <c r="O96">
+        <v>-29.72322729599999</v>
+      </c>
+      <c r="P96">
+        <v>-111.815950304</v>
+      </c>
+      <c r="Q96">
+        <v>-58.915950304</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.351230274001966</v>
+      </c>
+      <c r="T96">
+        <v>14.26470503402343</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.03040298449866104</v>
+      </c>
+      <c r="W96">
+        <v>0.2460602326982803</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.1447761166602906</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3143704351765014</v>
+      </c>
+      <c r="C97">
+        <v>-315.8805231641834</v>
+      </c>
+      <c r="D97">
+        <v>133.2794768358166</v>
+      </c>
+      <c r="E97">
+        <v>222.56</v>
+      </c>
+      <c r="F97">
+        <v>523.26</v>
+      </c>
+      <c r="G97">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H97">
+        <v>250.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>35</v>
+      </c>
+      <c r="K97">
+        <v>52.9</v>
+      </c>
+      <c r="L97">
+        <v>-17.9</v>
+      </c>
+      <c r="M97">
+        <v>124.954488</v>
+      </c>
+      <c r="N97">
+        <v>-142.854488</v>
+      </c>
+      <c r="O97">
+        <v>-29.99944248</v>
+      </c>
+      <c r="P97">
+        <v>-112.85504552</v>
+      </c>
+      <c r="Q97">
+        <v>-59.95504552000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.61371632880236</v>
+      </c>
+      <c r="T97">
+        <v>17.11764604082812</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.03008295308288566</v>
+      </c>
+      <c r="W97">
+        <v>0.2459838091961931</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.1432521575375509</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3163704351765014</v>
+      </c>
+      <c r="C98">
+        <v>-322.3488522190488</v>
+      </c>
+      <c r="D98">
+        <v>132.3191477809512</v>
+      </c>
+      <c r="E98">
+        <v>228.0679999999999</v>
+      </c>
+      <c r="F98">
+        <v>528.7679999999999</v>
+      </c>
+      <c r="G98">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H98">
+        <v>250.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>35</v>
+      </c>
+      <c r="K98">
+        <v>52.9</v>
+      </c>
+      <c r="L98">
+        <v>-17.9</v>
+      </c>
+      <c r="M98">
+        <v>126.2697984</v>
+      </c>
+      <c r="N98">
+        <v>-144.1697984</v>
+      </c>
+      <c r="O98">
+        <v>-30.27565766399999</v>
+      </c>
+      <c r="P98">
+        <v>-113.894140736</v>
+      </c>
+      <c r="Q98">
+        <v>-60.994140736</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.007445411002946</v>
+      </c>
+      <c r="T98">
+        <v>21.39705755103511</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.02976958898827227</v>
+      </c>
+      <c r="W98">
+        <v>0.2459089778503994</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.1417599475632014</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3183704351765014</v>
+      </c>
+      <c r="C99">
+        <v>-328.8034412079554</v>
+      </c>
+      <c r="D99">
+        <v>131.3725587920445</v>
+      </c>
+      <c r="E99">
+        <v>233.576</v>
+      </c>
+      <c r="F99">
+        <v>534.276</v>
+      </c>
+      <c r="G99">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H99">
+        <v>250.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>35</v>
+      </c>
+      <c r="K99">
+        <v>52.9</v>
+      </c>
+      <c r="L99">
+        <v>-17.9</v>
+      </c>
+      <c r="M99">
+        <v>127.5851088</v>
+      </c>
+      <c r="N99">
+        <v>-145.4851088</v>
+      </c>
+      <c r="O99">
+        <v>-30.551872848</v>
+      </c>
+      <c r="P99">
+        <v>-114.933235952</v>
+      </c>
+      <c r="Q99">
+        <v>-62.03323595200002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.663660548003929</v>
+      </c>
+      <c r="T99">
+        <v>28.52941006804681</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.02946268600901173</v>
+      </c>
+      <c r="W99">
+        <v>0.245835689418952</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.1402985048048178</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3203704351765014</v>
+      </c>
+      <c r="C100">
+        <v>-335.2445829187297</v>
+      </c>
+      <c r="D100">
+        <v>130.4394170812702</v>
+      </c>
+      <c r="E100">
+        <v>239.084</v>
+      </c>
+      <c r="F100">
+        <v>539.784</v>
+      </c>
+      <c r="G100">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H100">
+        <v>250.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>35</v>
+      </c>
+      <c r="K100">
+        <v>52.9</v>
+      </c>
+      <c r="L100">
+        <v>-17.9</v>
+      </c>
+      <c r="M100">
+        <v>128.9004192</v>
+      </c>
+      <c r="N100">
+        <v>-146.8004192</v>
+      </c>
+      <c r="O100">
+        <v>-30.828088032</v>
+      </c>
+      <c r="P100">
+        <v>-115.972331168</v>
+      </c>
+      <c r="Q100">
+        <v>-63.07233116800003</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.976090822005892</v>
+      </c>
+      <c r="T100">
+        <v>42.79411510207022</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.02916204635585854</v>
+      </c>
+      <c r="W100">
+        <v>0.245763896669779</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.1388668874088503</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3223704351765013</v>
+      </c>
+      <c r="C101">
+        <v>-341.6725618791604</v>
+      </c>
+      <c r="D101">
+        <v>129.5194381208395</v>
+      </c>
+      <c r="E101">
+        <v>244.5919999999999</v>
+      </c>
+      <c r="F101">
+        <v>545.2919999999999</v>
+      </c>
+      <c r="G101">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="H101">
+        <v>250.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>35</v>
+      </c>
+      <c r="K101">
+        <v>52.9</v>
+      </c>
+      <c r="L101">
+        <v>-17.9</v>
+      </c>
+      <c r="M101">
+        <v>130.2157296</v>
+      </c>
+      <c r="N101">
+        <v>-148.1157296</v>
+      </c>
+      <c r="O101">
+        <v>-31.10430321599999</v>
+      </c>
+      <c r="P101">
+        <v>-117.011426384</v>
+      </c>
+      <c r="Q101">
+        <v>-64.111426384</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.913381644011783</v>
+      </c>
+      <c r="T101">
+        <v>85.58823020414042</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.0288674802310519</v>
+      </c>
+      <c r="W101">
+        <v>0.2456935542791752</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.1374641915764376</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/portugal/portugal_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_restaurant_dining.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,13 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1015274550683562</v>
+      </c>
+      <c r="C2">
+        <v>535.8201765772752</v>
+      </c>
+      <c r="D2">
+        <v>541.4131765772752</v>
       </c>
       <c r="E2">
-        <v>-322.4</v>
+        <v>-315.981</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.419</v>
       </c>
       <c r="G2">
         <v>0.826</v>
@@ -1448,43 +1457,45 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.5136002</v>
       </c>
       <c r="N2">
-        <v>-9.43333333333333</v>
+        <v>-10.94693353333333</v>
       </c>
       <c r="O2">
-        <v>-1.980999999999999</v>
+        <v>-2.298856041999999</v>
       </c>
       <c r="P2">
-        <v>-7.452333333333331</v>
+        <v>-8.64807749133333</v>
       </c>
       <c r="Q2">
-        <v>65.84766666666667</v>
+        <v>64.65192250866667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.09705384300770262</v>
+      </c>
+      <c r="T2">
+        <v>0.8642134254882696</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-1.308800038477796</v>
+      </c>
+      <c r="W2">
+        <v>0.5444150490730643</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-6.23238113560855</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1492,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1015274550683562</v>
+        <v>0.1034274550683562</v>
       </c>
       <c r="C3">
-        <v>535.8201765772752</v>
+        <v>511.5505698781487</v>
       </c>
       <c r="D3">
-        <v>541.4131765772752</v>
+        <v>523.5625698781487</v>
       </c>
       <c r="E3">
-        <v>-315.981</v>
+        <v>-309.562</v>
       </c>
       <c r="F3">
-        <v>6.419</v>
+        <v>12.838</v>
       </c>
       <c r="G3">
         <v>0.826</v>
@@ -1528,37 +1539,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M3">
-        <v>1.5136002</v>
+        <v>3.0272004</v>
       </c>
       <c r="N3">
-        <v>-10.94693353333333</v>
+        <v>-12.46053373333333</v>
       </c>
       <c r="O3">
-        <v>-2.298856041999999</v>
+        <v>-2.616712083999999</v>
       </c>
       <c r="P3">
-        <v>-8.64807749133333</v>
+        <v>-9.84382164933333</v>
       </c>
       <c r="Q3">
-        <v>64.65192250866667</v>
+        <v>63.45617835066667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09705384300770262</v>
+        <v>0.09757684140574038</v>
       </c>
       <c r="T3">
-        <v>0.8642134254882696</v>
+        <v>0.8730319298299866</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-1.308800038477796</v>
+        <v>-0.6544000192388979</v>
       </c>
       <c r="W3">
-        <v>0.5444150490730643</v>
+        <v>0.3901075245365321</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1566,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-6.23238113560855</v>
+        <v>-3.116190567804276</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1574,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1034274550683562</v>
+        <v>0.1053274550683562</v>
       </c>
       <c r="C4">
-        <v>511.5505698781487</v>
+        <v>488.420476121055</v>
       </c>
       <c r="D4">
-        <v>523.5625698781487</v>
+        <v>506.851476121055</v>
       </c>
       <c r="E4">
-        <v>-309.562</v>
+        <v>-303.143</v>
       </c>
       <c r="F4">
-        <v>12.838</v>
+        <v>19.257</v>
       </c>
       <c r="G4">
         <v>0.826</v>
@@ -1610,37 +1621,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M4">
-        <v>3.0272004</v>
+        <v>4.5408006</v>
       </c>
       <c r="N4">
-        <v>-12.46053373333333</v>
+        <v>-13.97413393333333</v>
       </c>
       <c r="O4">
-        <v>-2.616712083999999</v>
+        <v>-2.934568125999999</v>
       </c>
       <c r="P4">
-        <v>-9.84382164933333</v>
+        <v>-11.03956580733333</v>
       </c>
       <c r="Q4">
-        <v>63.45617835066667</v>
+        <v>62.26043419266666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09757684140574038</v>
+        <v>0.09811062327590267</v>
       </c>
       <c r="T4">
-        <v>0.8730319298299866</v>
+        <v>0.8820322590034917</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-0.6544000192388979</v>
+        <v>-0.4362666794925986</v>
       </c>
       <c r="W4">
-        <v>0.3901075245365321</v>
+        <v>0.3386716830243547</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1648,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-3.116190567804276</v>
+        <v>-2.077460378536184</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1656,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1053274550683562</v>
+        <v>0.1072274550683562</v>
       </c>
       <c r="C5">
-        <v>488.420476121055</v>
+        <v>466.3241571834829</v>
       </c>
       <c r="D5">
-        <v>506.851476121055</v>
+        <v>491.1741571834829</v>
       </c>
       <c r="E5">
-        <v>-303.143</v>
+        <v>-296.724</v>
       </c>
       <c r="F5">
-        <v>19.257</v>
+        <v>25.676</v>
       </c>
       <c r="G5">
         <v>0.826</v>
@@ -1692,37 +1703,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M5">
-        <v>4.5408006</v>
+        <v>6.0544008</v>
       </c>
       <c r="N5">
-        <v>-13.97413393333333</v>
+        <v>-15.48773413333333</v>
       </c>
       <c r="O5">
-        <v>-2.934568125999999</v>
+        <v>-3.252424167999999</v>
       </c>
       <c r="P5">
-        <v>-11.03956580733333</v>
+        <v>-12.23530996533333</v>
       </c>
       <c r="Q5">
-        <v>62.26043419266666</v>
+        <v>61.06469003466667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09811062327590267</v>
+        <v>0.09865552560169331</v>
       </c>
       <c r="T5">
-        <v>0.8820322590034917</v>
+        <v>0.8912200950347781</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.4362666794925986</v>
+        <v>-0.327200009619449</v>
       </c>
       <c r="W5">
-        <v>0.3386716830243547</v>
+        <v>0.3129537622682661</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1730,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-2.077460378536184</v>
+        <v>-1.558095283902138</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1738,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1072274550683562</v>
+        <v>0.1091274550683562</v>
       </c>
       <c r="C6">
-        <v>466.3241571834829</v>
+        <v>445.1685646954178</v>
       </c>
       <c r="D6">
-        <v>491.1741571834829</v>
+        <v>476.4375646954177</v>
       </c>
       <c r="E6">
-        <v>-296.724</v>
+        <v>-290.3049999999999</v>
       </c>
       <c r="F6">
-        <v>25.676</v>
+        <v>32.095</v>
       </c>
       <c r="G6">
         <v>0.826</v>
@@ -1774,37 +1785,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M6">
-        <v>6.0544008</v>
+        <v>7.568001</v>
       </c>
       <c r="N6">
-        <v>-15.48773413333333</v>
+        <v>-17.00133433333333</v>
       </c>
       <c r="O6">
-        <v>-3.252424167999999</v>
+        <v>-3.570280209999999</v>
       </c>
       <c r="P6">
-        <v>-12.23530996533333</v>
+        <v>-13.43105412333333</v>
       </c>
       <c r="Q6">
-        <v>61.06469003466667</v>
+        <v>59.86894587666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09865552560169331</v>
+        <v>0.09921189955539535</v>
       </c>
       <c r="T6">
-        <v>0.8912200950347781</v>
+        <v>0.9006013591930389</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.327200009619449</v>
+        <v>-0.2617600076955591</v>
       </c>
       <c r="W6">
-        <v>0.3129537622682661</v>
+        <v>0.2975230098146128</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1812,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-1.558095283902138</v>
+        <v>-1.24647622712171</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1820,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1091274550683562</v>
+        <v>0.1110274550683562</v>
       </c>
       <c r="C7">
-        <v>445.1685646954178</v>
+        <v>424.8714918505913</v>
       </c>
       <c r="D7">
-        <v>476.4375646954177</v>
+        <v>462.5594918505913</v>
       </c>
       <c r="E7">
-        <v>-290.3049999999999</v>
+        <v>-283.886</v>
       </c>
       <c r="F7">
-        <v>32.095</v>
+        <v>38.514</v>
       </c>
       <c r="G7">
         <v>0.826</v>
@@ -1856,37 +1867,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M7">
-        <v>7.568001</v>
+        <v>9.081601200000001</v>
       </c>
       <c r="N7">
-        <v>-17.00133433333333</v>
+        <v>-18.51493453333333</v>
       </c>
       <c r="O7">
-        <v>-3.570280209999999</v>
+        <v>-3.888136251999999</v>
       </c>
       <c r="P7">
-        <v>-13.43105412333333</v>
+        <v>-14.62679828133333</v>
       </c>
       <c r="Q7">
-        <v>59.86894587666667</v>
+        <v>58.67320171866666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09921189955539535</v>
+        <v>0.09978011125279318</v>
       </c>
       <c r="T7">
-        <v>0.9006013591930389</v>
+        <v>0.9101822247163691</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.2617600076955591</v>
+        <v>-0.2181333397462992</v>
       </c>
       <c r="W7">
-        <v>0.2975230098146128</v>
+        <v>0.2872358415121773</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1894,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-1.24647622712171</v>
+        <v>-1.038730189268092</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1902,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1110274550683562</v>
+        <v>0.1129274550683562</v>
       </c>
       <c r="C8">
-        <v>424.8714918505913</v>
+        <v>405.3600390885855</v>
       </c>
       <c r="D8">
-        <v>462.5594918505913</v>
+        <v>449.4670390885855</v>
       </c>
       <c r="E8">
-        <v>-283.886</v>
+        <v>-277.467</v>
       </c>
       <c r="F8">
-        <v>38.514</v>
+        <v>44.93299999999999</v>
       </c>
       <c r="G8">
         <v>0.826</v>
@@ -1938,37 +1949,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M8">
-        <v>9.0816012</v>
+        <v>10.5952014</v>
       </c>
       <c r="N8">
-        <v>-18.51493453333333</v>
+        <v>-20.02853473333333</v>
       </c>
       <c r="O8">
-        <v>-3.888136251999999</v>
+        <v>-4.205992294</v>
       </c>
       <c r="P8">
-        <v>-14.62679828133333</v>
+        <v>-15.82254243933333</v>
       </c>
       <c r="Q8">
-        <v>58.67320171866666</v>
+        <v>57.47745756066666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09978011125279318</v>
+        <v>0.1003605425565866</v>
       </c>
       <c r="T8">
-        <v>0.9101822247163691</v>
+        <v>0.9199691303584805</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.2181333397462993</v>
+        <v>-0.1869714340682565</v>
       </c>
       <c r="W8">
-        <v>0.2872358415121773</v>
+        <v>0.2798878641532949</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1976,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-1.038730189268092</v>
+        <v>-0.8903401622297933</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1984,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1129274550683562</v>
+        <v>0.1148274550683562</v>
       </c>
       <c r="C9">
-        <v>405.3600390885856</v>
+        <v>386.5693331721117</v>
       </c>
       <c r="D9">
-        <v>449.4670390885856</v>
+        <v>437.0953331721117</v>
       </c>
       <c r="E9">
-        <v>-277.467</v>
+        <v>-271.048</v>
       </c>
       <c r="F9">
-        <v>44.933</v>
+        <v>51.352</v>
       </c>
       <c r="G9">
         <v>0.826</v>
@@ -2020,37 +2031,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M9">
-        <v>10.5952014</v>
+        <v>12.1088016</v>
       </c>
       <c r="N9">
-        <v>-20.02853473333333</v>
+        <v>-21.54213493333333</v>
       </c>
       <c r="O9">
-        <v>-4.205992294</v>
+        <v>-4.523848335999999</v>
       </c>
       <c r="P9">
-        <v>-15.82254243933333</v>
+        <v>-17.01828659733333</v>
       </c>
       <c r="Q9">
-        <v>57.47745756066666</v>
+        <v>56.28171340266667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1003605425565866</v>
+        <v>0.1009535919322017</v>
       </c>
       <c r="T9">
-        <v>0.9199691303584805</v>
+        <v>0.9299687948188987</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.1869714340682565</v>
+        <v>-0.1636000048097245</v>
       </c>
       <c r="W9">
-        <v>0.2798878641532949</v>
+        <v>0.274376881134133</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2058,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.8903401622297931</v>
+        <v>-0.779047641951069</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2066,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1148274550683562</v>
+        <v>0.1167274550683562</v>
       </c>
       <c r="C10">
-        <v>386.5693331721117</v>
+        <v>368.441452143931</v>
       </c>
       <c r="D10">
-        <v>437.0953331721117</v>
+        <v>425.386452143931</v>
       </c>
       <c r="E10">
-        <v>-271.048</v>
+        <v>-264.629</v>
       </c>
       <c r="F10">
-        <v>51.352</v>
+        <v>57.77099999999999</v>
       </c>
       <c r="G10">
         <v>0.826</v>
@@ -2102,37 +2113,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M10">
-        <v>12.1088016</v>
+        <v>13.6224018</v>
       </c>
       <c r="N10">
-        <v>-21.54213493333333</v>
+        <v>-23.05573513333333</v>
       </c>
       <c r="O10">
-        <v>-4.523848335999999</v>
+        <v>-4.841704377999998</v>
       </c>
       <c r="P10">
-        <v>-17.01828659733333</v>
+        <v>-18.21403075533333</v>
       </c>
       <c r="Q10">
-        <v>56.28171340266667</v>
+        <v>55.08596924466667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1009535919322017</v>
+        <v>0.1015596753600281</v>
       </c>
       <c r="T10">
-        <v>0.9299687948188987</v>
+        <v>0.9401882321246009</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.1636000048097245</v>
+        <v>-0.1454222264975329</v>
       </c>
       <c r="W10">
-        <v>0.274376881134133</v>
+        <v>0.2700905610081183</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2140,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.779047641951069</v>
+        <v>-0.6924867928453946</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2148,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1167274550683562</v>
+        <v>0.1186274550683562</v>
       </c>
       <c r="C11">
-        <v>368.441452143931</v>
+        <v>350.9245185649688</v>
       </c>
       <c r="D11">
-        <v>425.386452143931</v>
+        <v>414.2885185649688</v>
       </c>
       <c r="E11">
-        <v>-264.629</v>
+        <v>-258.21</v>
       </c>
       <c r="F11">
-        <v>57.77099999999999</v>
+        <v>64.19</v>
       </c>
       <c r="G11">
         <v>0.826</v>
@@ -2184,37 +2195,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M11">
-        <v>13.6224018</v>
+        <v>15.136002</v>
       </c>
       <c r="N11">
-        <v>-23.05573513333333</v>
+        <v>-24.56933533333333</v>
       </c>
       <c r="O11">
-        <v>-4.841704377999998</v>
+        <v>-5.159560419999998</v>
       </c>
       <c r="P11">
-        <v>-18.21403075533333</v>
+        <v>-19.40977491333333</v>
       </c>
       <c r="Q11">
-        <v>55.08596924466667</v>
+        <v>53.89022508666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1015596753600281</v>
+        <v>0.1021792273084729</v>
       </c>
       <c r="T11">
-        <v>0.9401882321246009</v>
+        <v>0.9506347680370965</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.1454222264975329</v>
+        <v>-0.1308800038477796</v>
       </c>
       <c r="W11">
-        <v>0.2700905610081183</v>
+        <v>0.2666615049073064</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2222,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.6924867928453946</v>
+        <v>-0.6232381135608549</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2230,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1186274550683562</v>
+        <v>0.1205274550683562</v>
       </c>
       <c r="C12">
-        <v>350.9245185649688</v>
+        <v>333.9719310829194</v>
       </c>
       <c r="D12">
-        <v>414.2885185649688</v>
+        <v>403.7549310829193</v>
       </c>
       <c r="E12">
-        <v>-258.21</v>
+        <v>-251.791</v>
       </c>
       <c r="F12">
-        <v>64.19</v>
+        <v>70.60899999999999</v>
       </c>
       <c r="G12">
         <v>0.826</v>
@@ -2266,37 +2277,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M12">
-        <v>15.136002</v>
+        <v>16.6496022</v>
       </c>
       <c r="N12">
-        <v>-24.56933533333333</v>
+        <v>-26.08293553333333</v>
       </c>
       <c r="O12">
-        <v>-5.159560419999998</v>
+        <v>-5.477416461999999</v>
       </c>
       <c r="P12">
-        <v>-19.40977491333333</v>
+        <v>-20.60551907133333</v>
       </c>
       <c r="Q12">
-        <v>53.89022508666667</v>
+        <v>52.69448092866666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1021792273084729</v>
+        <v>0.102812701772613</v>
       </c>
       <c r="T12">
-        <v>0.9506347680370967</v>
+        <v>0.9613160575656033</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.1308800038477796</v>
+        <v>-0.1189818216797996</v>
       </c>
       <c r="W12">
-        <v>0.2666615049073064</v>
+        <v>0.2638559135520968</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2304,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.6232381135608549</v>
+        <v>-0.5665801032371409</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2312,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1205274550683562</v>
+        <v>0.1224274550683562</v>
       </c>
       <c r="C13">
-        <v>333.9719310829194</v>
+        <v>317.5417103217286</v>
       </c>
       <c r="D13">
-        <v>403.7549310829193</v>
+        <v>393.7437103217286</v>
       </c>
       <c r="E13">
-        <v>-251.791</v>
+        <v>-245.372</v>
       </c>
       <c r="F13">
-        <v>70.60899999999999</v>
+        <v>77.02799999999999</v>
       </c>
       <c r="G13">
         <v>0.826</v>
@@ -2348,37 +2359,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M13">
-        <v>16.6496022</v>
+        <v>18.1632024</v>
       </c>
       <c r="N13">
-        <v>-26.08293553333333</v>
+        <v>-27.59653573333333</v>
       </c>
       <c r="O13">
-        <v>-5.477416461999999</v>
+        <v>-5.795272503999999</v>
       </c>
       <c r="P13">
-        <v>-20.60551907133333</v>
+        <v>-21.80126322933333</v>
       </c>
       <c r="Q13">
-        <v>52.69448092866666</v>
+        <v>51.49873677066667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.102812701772613</v>
+        <v>0.1034605733836654</v>
       </c>
       <c r="T13">
-        <v>0.9613160575656033</v>
+        <v>0.9722401036743034</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.1189818216797996</v>
+        <v>-0.1090666698731496</v>
       </c>
       <c r="W13">
-        <v>0.2638559135520968</v>
+        <v>0.2615179207560887</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2386,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.5665801032371409</v>
+        <v>-0.519365094634046</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2394,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1224274550683562</v>
+        <v>0.1243274550683562</v>
       </c>
       <c r="C14">
-        <v>317.5417103217286</v>
+        <v>301.5959397297099</v>
       </c>
       <c r="D14">
-        <v>393.7437103217286</v>
+        <v>384.2169397297098</v>
       </c>
       <c r="E14">
-        <v>-245.372</v>
+        <v>-238.953</v>
       </c>
       <c r="F14">
-        <v>77.02799999999999</v>
+        <v>83.447</v>
       </c>
       <c r="G14">
         <v>0.826</v>
@@ -2430,37 +2441,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M14">
-        <v>18.1632024</v>
+        <v>19.6768026</v>
       </c>
       <c r="N14">
-        <v>-27.59653573333333</v>
+        <v>-29.11013593333333</v>
       </c>
       <c r="O14">
-        <v>-5.795272503999999</v>
+        <v>-6.113128546</v>
       </c>
       <c r="P14">
-        <v>-21.80126322933333</v>
+        <v>-22.99700738733333</v>
       </c>
       <c r="Q14">
-        <v>51.49873677066667</v>
+        <v>50.30299261266666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1034605733836654</v>
+        <v>0.1041233385949719</v>
       </c>
       <c r="T14">
-        <v>0.9722401036743034</v>
+        <v>0.9834152772797551</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.1090666698731496</v>
+        <v>-0.1006769260367535</v>
       </c>
       <c r="W14">
-        <v>0.2615179207560887</v>
+        <v>0.2595396191594665</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2468,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.519365094634046</v>
+        <v>-0.47941393350835</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2476,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1243274550683562</v>
+        <v>0.1262274550683562</v>
       </c>
       <c r="C15">
-        <v>301.5959397297099</v>
+        <v>286.1002856833273</v>
       </c>
       <c r="D15">
-        <v>384.2169397297098</v>
+        <v>375.1402856833273</v>
       </c>
       <c r="E15">
-        <v>-238.953</v>
+        <v>-232.534</v>
       </c>
       <c r="F15">
-        <v>83.447</v>
+        <v>89.866</v>
       </c>
       <c r="G15">
         <v>0.826</v>
@@ -2512,37 +2523,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M15">
-        <v>19.6768026</v>
+        <v>21.1904028</v>
       </c>
       <c r="N15">
-        <v>-29.11013593333333</v>
+        <v>-30.62373613333333</v>
       </c>
       <c r="O15">
-        <v>-6.113128546</v>
+        <v>-6.430984587999999</v>
       </c>
       <c r="P15">
-        <v>-22.99700738733333</v>
+        <v>-24.19275154533333</v>
       </c>
       <c r="Q15">
-        <v>50.30299261266666</v>
+        <v>49.10724845466667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1041233385949719</v>
+        <v>0.1048015169507274</v>
       </c>
       <c r="T15">
-        <v>0.9834152772797551</v>
+        <v>0.9948503386434732</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.1006769260367535</v>
+        <v>-0.09348571703412825</v>
       </c>
       <c r="W15">
-        <v>0.2595396191594665</v>
+        <v>0.2578439320766475</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2550,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.47941393350835</v>
+        <v>-0.4451700811148964</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2558,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1262274550683562</v>
+        <v>0.1281274550683562</v>
       </c>
       <c r="C16">
-        <v>286.1002856833273</v>
+        <v>271.0235840428902</v>
       </c>
       <c r="D16">
-        <v>375.1402856833273</v>
+        <v>366.4825840428902</v>
       </c>
       <c r="E16">
-        <v>-232.534</v>
+        <v>-226.115</v>
       </c>
       <c r="F16">
-        <v>89.866</v>
+        <v>96.28500000000001</v>
       </c>
       <c r="G16">
         <v>0.826</v>
@@ -2594,37 +2605,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M16">
-        <v>21.1904028</v>
+        <v>22.704003</v>
       </c>
       <c r="N16">
-        <v>-30.62373613333333</v>
+        <v>-32.13733633333334</v>
       </c>
       <c r="O16">
-        <v>-6.430984587999999</v>
+        <v>-6.748840630000001</v>
       </c>
       <c r="P16">
-        <v>-24.19275154533333</v>
+        <v>-25.38849570333334</v>
       </c>
       <c r="Q16">
-        <v>49.10724845466667</v>
+        <v>47.91150429666666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1048015169507274</v>
+        <v>0.1054956524442654</v>
       </c>
       <c r="T16">
-        <v>0.9948503386434732</v>
+        <v>1.006554460274573</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.09348571703412825</v>
+        <v>-0.0872533358985197</v>
       </c>
       <c r="W16">
-        <v>0.2578439320766475</v>
+        <v>0.256374336604871</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2632,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.4451700811148964</v>
+        <v>-0.4154920757072369</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2640,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1281274550683562</v>
+        <v>0.1300274550683562</v>
       </c>
       <c r="C17">
-        <v>271.0235840428903</v>
+        <v>256.337482667022</v>
       </c>
       <c r="D17">
-        <v>366.4825840428903</v>
+        <v>358.2154826670219</v>
       </c>
       <c r="E17">
-        <v>-226.115</v>
+        <v>-219.696</v>
       </c>
       <c r="F17">
-        <v>96.285</v>
+        <v>102.704</v>
       </c>
       <c r="G17">
         <v>0.826</v>
@@ -2676,37 +2687,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M17">
-        <v>22.704003</v>
+        <v>24.2176032</v>
       </c>
       <c r="N17">
-        <v>-32.13733633333333</v>
+        <v>-33.65093653333333</v>
       </c>
       <c r="O17">
-        <v>-6.748840629999999</v>
+        <v>-7.066696671999999</v>
       </c>
       <c r="P17">
-        <v>-25.38849570333333</v>
+        <v>-26.58423986133333</v>
       </c>
       <c r="Q17">
-        <v>47.91150429666666</v>
+        <v>46.71576013866667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1054956524442654</v>
+        <v>0.1062063149733638</v>
       </c>
       <c r="T17">
-        <v>1.006554460274573</v>
+        <v>1.018537251468318</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.0872533358985197</v>
+        <v>-0.08180000240486224</v>
       </c>
       <c r="W17">
-        <v>0.256374336604871</v>
+        <v>0.2550884405670665</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2714,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.4154920757072367</v>
+        <v>-0.3895238209755345</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2722,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1300274550683562</v>
+        <v>0.1319274550683562</v>
       </c>
       <c r="C18">
-        <v>256.337482667022</v>
+        <v>242.0161312446194</v>
       </c>
       <c r="D18">
-        <v>358.2154826670219</v>
+        <v>350.3131312446194</v>
       </c>
       <c r="E18">
-        <v>-219.696</v>
+        <v>-213.277</v>
       </c>
       <c r="F18">
-        <v>102.704</v>
+        <v>109.123</v>
       </c>
       <c r="G18">
         <v>0.826</v>
@@ -2758,37 +2769,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M18">
-        <v>24.2176032</v>
+        <v>25.7312034</v>
       </c>
       <c r="N18">
-        <v>-33.65093653333333</v>
+        <v>-35.16453673333334</v>
       </c>
       <c r="O18">
-        <v>-7.066696671999999</v>
+        <v>-7.384552714</v>
       </c>
       <c r="P18">
-        <v>-26.58423986133333</v>
+        <v>-27.77998401933333</v>
       </c>
       <c r="Q18">
-        <v>46.71576013866667</v>
+        <v>45.52001598066666</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1062063149733638</v>
+        <v>0.1069341019007537</v>
       </c>
       <c r="T18">
-        <v>1.018537251468318</v>
+        <v>1.030808784618538</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.08180000240486224</v>
+        <v>-0.07698823755751738</v>
       </c>
       <c r="W18">
-        <v>0.2550884405670665</v>
+        <v>0.2539538264160626</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2796,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.3895238209755345</v>
+        <v>-0.3666106550357973</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2804,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1319274550683562</v>
+        <v>0.1338274550683562</v>
       </c>
       <c r="C19">
-        <v>242.0161312446194</v>
+        <v>228.0359112951397</v>
       </c>
       <c r="D19">
-        <v>350.3131312446194</v>
+        <v>342.7519112951397</v>
       </c>
       <c r="E19">
-        <v>-213.277</v>
+        <v>-206.8579999999999</v>
       </c>
       <c r="F19">
-        <v>109.123</v>
+        <v>115.542</v>
       </c>
       <c r="G19">
         <v>0.826</v>
@@ -2840,37 +2851,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M19">
-        <v>25.7312034</v>
+        <v>27.2448036</v>
       </c>
       <c r="N19">
-        <v>-35.16453673333334</v>
+        <v>-36.67813693333333</v>
       </c>
       <c r="O19">
-        <v>-7.384552714</v>
+        <v>-7.702408756</v>
       </c>
       <c r="P19">
-        <v>-27.77998401933333</v>
+        <v>-28.97572817733333</v>
       </c>
       <c r="Q19">
-        <v>45.52001598066666</v>
+        <v>44.32427182266666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1069341019007537</v>
+        <v>0.1076796397288117</v>
       </c>
       <c r="T19">
-        <v>1.030808784618538</v>
+        <v>1.04337962345535</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.07698823755751738</v>
+        <v>-0.07271111324876642</v>
       </c>
       <c r="W19">
-        <v>0.2539538264160626</v>
+        <v>0.2529452805040591</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2878,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.3666106550357973</v>
+        <v>-0.3462433964226972</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2886,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1338274550683562</v>
+        <v>0.1357274550683562</v>
       </c>
       <c r="C20">
-        <v>228.0359112951397</v>
+        <v>214.3752003964408</v>
       </c>
       <c r="D20">
-        <v>342.7519112951396</v>
+        <v>335.5102003964408</v>
       </c>
       <c r="E20">
-        <v>-206.858</v>
+        <v>-200.439</v>
       </c>
       <c r="F20">
-        <v>115.542</v>
+        <v>121.961</v>
       </c>
       <c r="G20">
         <v>0.826</v>
@@ -2922,37 +2933,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M20">
-        <v>27.2448036</v>
+        <v>28.7584038</v>
       </c>
       <c r="N20">
-        <v>-36.67813693333333</v>
+        <v>-38.19173713333333</v>
       </c>
       <c r="O20">
-        <v>-7.702408755999999</v>
+        <v>-8.020264797999999</v>
       </c>
       <c r="P20">
-        <v>-28.97572817733333</v>
+        <v>-30.17147233533333</v>
       </c>
       <c r="Q20">
-        <v>44.32427182266667</v>
+        <v>43.12852766466666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1076796397288117</v>
+        <v>0.1084435858983032</v>
       </c>
       <c r="T20">
-        <v>1.04337962345535</v>
+        <v>1.056260853374552</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.07271111324876643</v>
+        <v>-0.06888421255146293</v>
       </c>
       <c r="W20">
-        <v>0.2529452805040591</v>
+        <v>0.2520428973196349</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2960,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.3462433964226974</v>
+        <v>-0.3280200597688712</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2968,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1357274550683562</v>
+        <v>0.1376274550683562</v>
       </c>
       <c r="C21">
-        <v>214.3752003964408</v>
+        <v>201.0141656827628</v>
       </c>
       <c r="D21">
-        <v>335.5102003964408</v>
+        <v>328.5681656827628</v>
       </c>
       <c r="E21">
-        <v>-200.439</v>
+        <v>-194.02</v>
       </c>
       <c r="F21">
-        <v>121.961</v>
+        <v>128.38</v>
       </c>
       <c r="G21">
         <v>0.826</v>
@@ -3004,37 +3015,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M21">
-        <v>28.7584038</v>
+        <v>30.272004</v>
       </c>
       <c r="N21">
-        <v>-38.19173713333333</v>
+        <v>-39.70533733333333</v>
       </c>
       <c r="O21">
-        <v>-8.020264797999999</v>
+        <v>-8.33812084</v>
       </c>
       <c r="P21">
-        <v>-30.17147233533333</v>
+        <v>-31.36721649333333</v>
       </c>
       <c r="Q21">
-        <v>43.12852766466666</v>
+        <v>41.93278350666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1084435858983032</v>
+        <v>0.109226630722032</v>
       </c>
       <c r="T21">
-        <v>1.056260853374552</v>
+        <v>1.069464114041734</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.06888421255146293</v>
+        <v>-0.06544000192388978</v>
       </c>
       <c r="W21">
-        <v>0.2520428973196349</v>
+        <v>0.2512307524536532</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3042,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.3280200597688712</v>
+        <v>-0.3116190567804278</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3050,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1376274550683562</v>
+        <v>0.1395274550683562</v>
       </c>
       <c r="C22">
-        <v>201.0141656827628</v>
+        <v>187.934582459395</v>
       </c>
       <c r="D22">
-        <v>328.5681656827628</v>
+        <v>321.907582459395</v>
       </c>
       <c r="E22">
-        <v>-194.02</v>
+        <v>-187.601</v>
       </c>
       <c r="F22">
-        <v>128.38</v>
+        <v>134.799</v>
       </c>
       <c r="G22">
         <v>0.826</v>
@@ -3086,37 +3097,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M22">
-        <v>30.272004</v>
+        <v>31.7856042</v>
       </c>
       <c r="N22">
-        <v>-39.70533733333333</v>
+        <v>-41.21893753333333</v>
       </c>
       <c r="O22">
-        <v>-8.33812084</v>
+        <v>-8.655976881999999</v>
       </c>
       <c r="P22">
-        <v>-31.36721649333333</v>
+        <v>-32.56296065133333</v>
       </c>
       <c r="Q22">
-        <v>41.93278350666667</v>
+        <v>40.73703934866666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.109226630722032</v>
+        <v>0.1100294994653488</v>
       </c>
       <c r="T22">
-        <v>1.069464114041734</v>
+        <v>1.083001634472642</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.06544000192388978</v>
+        <v>-0.0623238113560855</v>
       </c>
       <c r="W22">
-        <v>0.2512307524536532</v>
+        <v>0.250495954717765</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3124,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.3116190567804278</v>
+        <v>-0.2967800540765977</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3132,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1395274550683562</v>
+        <v>0.1414274550683562</v>
       </c>
       <c r="C23">
-        <v>187.9345824593951</v>
+        <v>175.1196744407653</v>
       </c>
       <c r="D23">
-        <v>321.907582459395</v>
+        <v>315.5116744407653</v>
       </c>
       <c r="E23">
-        <v>-187.601</v>
+        <v>-181.182</v>
       </c>
       <c r="F23">
-        <v>134.799</v>
+        <v>141.218</v>
       </c>
       <c r="G23">
         <v>0.826</v>
@@ -3168,37 +3179,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M23">
-        <v>31.78560419999999</v>
+        <v>33.2992044</v>
       </c>
       <c r="N23">
-        <v>-41.21893753333332</v>
+        <v>-42.73253773333333</v>
       </c>
       <c r="O23">
-        <v>-8.655976881999997</v>
+        <v>-8.973832924</v>
       </c>
       <c r="P23">
-        <v>-32.56296065133333</v>
+        <v>-33.75870480933333</v>
       </c>
       <c r="Q23">
-        <v>40.73703934866667</v>
+        <v>39.54129519066667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1100294994653488</v>
+        <v>0.1108529545866995</v>
       </c>
       <c r="T23">
-        <v>1.083001634472642</v>
+        <v>1.096886270812035</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.06232381135608552</v>
+        <v>-0.0594909108398998</v>
       </c>
       <c r="W23">
-        <v>0.250495954717765</v>
+        <v>0.2498279567760484</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3206,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.2967800540765977</v>
+        <v>-0.2832900516185706</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3214,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1414274550683562</v>
+        <v>0.1433274550683563</v>
       </c>
       <c r="C24">
-        <v>175.1196744407653</v>
+        <v>162.5539726631245</v>
       </c>
       <c r="D24">
-        <v>315.5116744407653</v>
+        <v>309.3649726631244</v>
       </c>
       <c r="E24">
-        <v>-181.182</v>
+        <v>-174.763</v>
       </c>
       <c r="F24">
-        <v>141.218</v>
+        <v>147.637</v>
       </c>
       <c r="G24">
         <v>0.826</v>
@@ -3250,37 +3261,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M24">
-        <v>33.2992044</v>
+        <v>34.8128046</v>
       </c>
       <c r="N24">
-        <v>-42.73253773333333</v>
+        <v>-44.24613793333333</v>
       </c>
       <c r="O24">
-        <v>-8.973832924</v>
+        <v>-9.291688965999999</v>
       </c>
       <c r="P24">
-        <v>-33.75870480933333</v>
+        <v>-34.95444896733333</v>
       </c>
       <c r="Q24">
-        <v>39.54129519066667</v>
+        <v>38.34555103266666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1108529545866995</v>
+        <v>0.1116977981527605</v>
       </c>
       <c r="T24">
-        <v>1.096886270812035</v>
+        <v>1.111131547056347</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.0594909108398998</v>
+        <v>-0.0569043494990346</v>
       </c>
       <c r="W24">
-        <v>0.2498279567760484</v>
+        <v>0.2492180456118724</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3288,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.2832900516185706</v>
+        <v>-0.2709730928525458</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3296,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1433274550683563</v>
+        <v>0.1452274550683562</v>
       </c>
       <c r="C25">
-        <v>162.5539726631245</v>
+        <v>150.2231905738029</v>
       </c>
       <c r="D25">
-        <v>309.3649726631244</v>
+        <v>303.4531905738029</v>
       </c>
       <c r="E25">
-        <v>-174.763</v>
+        <v>-168.344</v>
       </c>
       <c r="F25">
-        <v>147.637</v>
+        <v>154.056</v>
       </c>
       <c r="G25">
         <v>0.826</v>
@@ -3332,37 +3343,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M25">
-        <v>34.8128046</v>
+        <v>36.32640480000001</v>
       </c>
       <c r="N25">
-        <v>-44.24613793333333</v>
+        <v>-45.75973813333334</v>
       </c>
       <c r="O25">
-        <v>-9.291688965999999</v>
+        <v>-9.609545008</v>
       </c>
       <c r="P25">
-        <v>-34.95444896733333</v>
+        <v>-36.15019312533334</v>
       </c>
       <c r="Q25">
-        <v>38.34555103266666</v>
+        <v>37.14980687466666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1116977981527605</v>
+        <v>0.1125648744442442</v>
       </c>
       <c r="T25">
-        <v>1.111131547056347</v>
+        <v>1.125751698991299</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.0569043494990346</v>
+        <v>-0.05453333493657481</v>
       </c>
       <c r="W25">
-        <v>0.2492180456118724</v>
+        <v>0.2486589603780444</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3370,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.2709730928525458</v>
+        <v>-0.259682547317023</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3378,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1452274550683562</v>
+        <v>0.1471274550683562</v>
       </c>
       <c r="C26">
-        <v>150.223190573803</v>
+        <v>138.1141131737412</v>
       </c>
       <c r="D26">
-        <v>303.4531905738029</v>
+        <v>297.7631131737411</v>
       </c>
       <c r="E26">
-        <v>-168.344</v>
+        <v>-161.925</v>
       </c>
       <c r="F26">
-        <v>154.056</v>
+        <v>160.475</v>
       </c>
       <c r="G26">
         <v>0.826</v>
@@ -3414,37 +3425,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M26">
-        <v>36.3264048</v>
+        <v>37.840005</v>
       </c>
       <c r="N26">
-        <v>-45.75973813333333</v>
+        <v>-47.27333833333333</v>
       </c>
       <c r="O26">
-        <v>-9.609545008</v>
+        <v>-9.927401049999999</v>
       </c>
       <c r="P26">
-        <v>-36.15019312533333</v>
+        <v>-37.34593728333333</v>
       </c>
       <c r="Q26">
-        <v>37.14980687466667</v>
+        <v>35.95406271666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1125648744442442</v>
+        <v>0.1134550727701674</v>
       </c>
       <c r="T26">
-        <v>1.125751698991299</v>
+        <v>1.140761721644516</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.05453333493657482</v>
+        <v>-0.05235200153911183</v>
       </c>
       <c r="W26">
-        <v>0.2486589603780444</v>
+        <v>0.2481446019629226</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3452,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.259682547317023</v>
+        <v>-0.249295245424342</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3460,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1471274550683562</v>
+        <v>0.1490274550683562</v>
       </c>
       <c r="C27">
-        <v>138.1141131737412</v>
+        <v>126.2144984026468</v>
       </c>
       <c r="D27">
-        <v>297.7631131737411</v>
+        <v>292.2824984026468</v>
       </c>
       <c r="E27">
-        <v>-161.925</v>
+        <v>-155.506</v>
       </c>
       <c r="F27">
-        <v>160.475</v>
+        <v>166.894</v>
       </c>
       <c r="G27">
         <v>0.826</v>
@@ -3496,37 +3507,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M27">
-        <v>37.840005</v>
+        <v>39.3536052</v>
       </c>
       <c r="N27">
-        <v>-47.27333833333333</v>
+        <v>-48.78693853333333</v>
       </c>
       <c r="O27">
-        <v>-9.927401049999999</v>
+        <v>-10.245257092</v>
       </c>
       <c r="P27">
-        <v>-37.34593728333333</v>
+        <v>-38.54168144133334</v>
       </c>
       <c r="Q27">
-        <v>35.95406271666667</v>
+        <v>34.75831855866666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1134550727701674</v>
+        <v>0.1143693305103048</v>
       </c>
       <c r="T27">
-        <v>1.140761721644516</v>
+        <v>1.156177420585658</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.05235200153911183</v>
+        <v>-0.05033846301837675</v>
       </c>
       <c r="W27">
-        <v>0.2481446019629226</v>
+        <v>0.2476698095797333</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3534,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.249295245424342</v>
+        <v>-0.2397069667541749</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3542,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1490274550683562</v>
+        <v>0.1509274550683562</v>
       </c>
       <c r="C28">
-        <v>126.2144984026468</v>
+        <v>114.512989217925</v>
       </c>
       <c r="D28">
-        <v>292.2824984026468</v>
+        <v>286.999989217925</v>
       </c>
       <c r="E28">
-        <v>-155.506</v>
+        <v>-149.087</v>
       </c>
       <c r="F28">
-        <v>166.894</v>
+        <v>173.313</v>
       </c>
       <c r="G28">
         <v>0.826</v>
@@ -3578,37 +3589,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M28">
-        <v>39.3536052</v>
+        <v>40.8672054</v>
       </c>
       <c r="N28">
-        <v>-48.78693853333333</v>
+        <v>-50.30053873333333</v>
       </c>
       <c r="O28">
-        <v>-10.245257092</v>
+        <v>-10.563113134</v>
       </c>
       <c r="P28">
-        <v>-38.54168144133334</v>
+        <v>-39.73742559933333</v>
       </c>
       <c r="Q28">
-        <v>34.75831855866666</v>
+        <v>33.56257440066666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1143693305103048</v>
+        <v>0.1153086364077063</v>
       </c>
       <c r="T28">
-        <v>1.156177420585658</v>
+        <v>1.172015467442996</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.05033846301837675</v>
+        <v>-0.04847407549917761</v>
       </c>
       <c r="W28">
-        <v>0.2476698095797333</v>
+        <v>0.2472301870027061</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3616,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.2397069667541749</v>
+        <v>-0.2308289309484648</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3624,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1509274550683562</v>
+        <v>0.1528274550683562</v>
       </c>
       <c r="C29">
-        <v>114.512989217925</v>
+        <v>102.999035038497</v>
       </c>
       <c r="D29">
-        <v>286.999989217925</v>
+        <v>281.905035038497</v>
       </c>
       <c r="E29">
-        <v>-149.087</v>
+        <v>-142.668</v>
       </c>
       <c r="F29">
-        <v>173.313</v>
+        <v>179.732</v>
       </c>
       <c r="G29">
         <v>0.826</v>
@@ -3660,37 +3671,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M29">
-        <v>40.8672054</v>
+        <v>42.3808056</v>
       </c>
       <c r="N29">
-        <v>-50.30053873333333</v>
+        <v>-51.81413893333333</v>
       </c>
       <c r="O29">
-        <v>-10.563113134</v>
+        <v>-10.880969176</v>
       </c>
       <c r="P29">
-        <v>-39.73742559933333</v>
+        <v>-40.93316975733333</v>
       </c>
       <c r="Q29">
-        <v>33.56257440066666</v>
+        <v>32.36683024266667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1153086364077063</v>
+        <v>0.1162740341355911</v>
       </c>
       <c r="T29">
-        <v>1.172015467442996</v>
+        <v>1.188293460046371</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.04847407549917761</v>
+        <v>-0.04674285851706413</v>
       </c>
       <c r="W29">
-        <v>0.2472301870027061</v>
+        <v>0.2468219660383237</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3698,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.2308289309484648</v>
+        <v>-0.2225850405574483</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3706,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1528274550683562</v>
+        <v>0.1547274550683562</v>
       </c>
       <c r="C30">
-        <v>102.999035038497</v>
+        <v>91.66282141005945</v>
       </c>
       <c r="D30">
-        <v>281.905035038497</v>
+        <v>276.9878214100594</v>
       </c>
       <c r="E30">
-        <v>-142.668</v>
+        <v>-136.249</v>
       </c>
       <c r="F30">
-        <v>179.732</v>
+        <v>186.151</v>
       </c>
       <c r="G30">
         <v>0.826</v>
@@ -3742,37 +3753,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M30">
-        <v>42.3808056</v>
+        <v>43.8944058</v>
       </c>
       <c r="N30">
-        <v>-51.81413893333333</v>
+        <v>-53.32773913333333</v>
       </c>
       <c r="O30">
-        <v>-10.880969176</v>
+        <v>-11.198825218</v>
       </c>
       <c r="P30">
-        <v>-40.93316975733333</v>
+        <v>-42.12891391533333</v>
       </c>
       <c r="Q30">
-        <v>32.36683024266667</v>
+        <v>31.17108608466667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1162740341355911</v>
+        <v>0.1172666261656698</v>
       </c>
       <c r="T30">
-        <v>1.188293460046371</v>
+        <v>1.205029987652658</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.04674285851706413</v>
+        <v>-0.04513103580957916</v>
       </c>
       <c r="W30">
-        <v>0.2468219660383237</v>
+        <v>0.2464418982438988</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3780,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.2225850405574483</v>
+        <v>-0.2149096943313293</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3788,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1547274550683562</v>
+        <v>0.1566274550683562</v>
       </c>
       <c r="C31">
-        <v>91.66282141005954</v>
+        <v>80.49520690515618</v>
       </c>
       <c r="D31">
-        <v>276.9878214100595</v>
+        <v>272.2392069051562</v>
       </c>
       <c r="E31">
-        <v>-136.249</v>
+        <v>-129.83</v>
       </c>
       <c r="F31">
-        <v>186.151</v>
+        <v>192.57</v>
       </c>
       <c r="G31">
         <v>0.826</v>
@@ -3824,37 +3835,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M31">
-        <v>43.89440579999999</v>
+        <v>45.408006</v>
       </c>
       <c r="N31">
-        <v>-53.32773913333332</v>
+        <v>-54.84133933333333</v>
       </c>
       <c r="O31">
-        <v>-11.198825218</v>
+        <v>-11.51668126</v>
       </c>
       <c r="P31">
-        <v>-42.12891391533333</v>
+        <v>-43.32465807333333</v>
       </c>
       <c r="Q31">
-        <v>31.17108608466667</v>
+        <v>29.97534192666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1172666261656698</v>
+        <v>0.1182875779680365</v>
       </c>
       <c r="T31">
-        <v>1.205029987652658</v>
+        <v>1.222244701761981</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.04513103580957917</v>
+        <v>-0.04362666794925985</v>
       </c>
       <c r="W31">
-        <v>0.2464418982438988</v>
+        <v>0.2460871683024355</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3862,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.2149096943313293</v>
+        <v>-0.2077460378536184</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3870,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1566274550683562</v>
+        <v>0.1585274550683562</v>
       </c>
       <c r="C32">
-        <v>80.49520690515618</v>
+        <v>69.48766640447562</v>
       </c>
       <c r="D32">
-        <v>272.2392069051562</v>
+        <v>267.6506664044756</v>
       </c>
       <c r="E32">
-        <v>-129.83</v>
+        <v>-123.411</v>
       </c>
       <c r="F32">
-        <v>192.57</v>
+        <v>198.989</v>
       </c>
       <c r="G32">
         <v>0.826</v>
@@ -3906,37 +3917,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M32">
-        <v>45.408006</v>
+        <v>46.9216062</v>
       </c>
       <c r="N32">
-        <v>-54.84133933333333</v>
+        <v>-56.35493953333333</v>
       </c>
       <c r="O32">
-        <v>-11.51668126</v>
+        <v>-11.834537302</v>
       </c>
       <c r="P32">
-        <v>-43.32465807333333</v>
+        <v>-44.52040223133333</v>
       </c>
       <c r="Q32">
-        <v>29.97534192666667</v>
+        <v>28.77959776866667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1182875779680365</v>
+        <v>0.119338122576269</v>
       </c>
       <c r="T32">
-        <v>1.222244701761981</v>
+        <v>1.239958393091865</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.04362666794925985</v>
+        <v>-0.04221935607992889</v>
       </c>
       <c r="W32">
-        <v>0.2460871683024355</v>
+        <v>0.2457553241636472</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3944,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.2077460378536184</v>
+        <v>-0.2010445527615661</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3952,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1585274550683562</v>
+        <v>0.1604274550683562</v>
       </c>
       <c r="C33">
-        <v>69.48766640447562</v>
+        <v>58.63224001897103</v>
       </c>
       <c r="D33">
-        <v>267.6506664044756</v>
+        <v>263.214240018971</v>
       </c>
       <c r="E33">
-        <v>-123.411</v>
+        <v>-116.992</v>
       </c>
       <c r="F33">
-        <v>198.989</v>
+        <v>205.408</v>
       </c>
       <c r="G33">
         <v>0.826</v>
@@ -3988,37 +3999,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M33">
-        <v>46.9216062</v>
+        <v>48.4352064</v>
       </c>
       <c r="N33">
-        <v>-56.35493953333333</v>
+        <v>-57.86853973333333</v>
       </c>
       <c r="O33">
-        <v>-11.834537302</v>
+        <v>-12.152393344</v>
       </c>
       <c r="P33">
-        <v>-44.52040223133333</v>
+        <v>-45.71614638933333</v>
       </c>
       <c r="Q33">
-        <v>28.77959776866667</v>
+        <v>27.58385361066667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.119338122576269</v>
+        <v>0.1204195655553317</v>
       </c>
       <c r="T33">
-        <v>1.239958393091865</v>
+        <v>1.258193075343216</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.04221935607992889</v>
+        <v>-0.04090000120243112</v>
       </c>
       <c r="W33">
-        <v>0.2457553241636472</v>
+        <v>0.2454442202835333</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4026,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.2010445527615661</v>
+        <v>-0.1947619104877671</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4034,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1604274550683562</v>
+        <v>0.1623274550683562</v>
       </c>
       <c r="C34">
-        <v>58.63224001897103</v>
+        <v>47.92148700898139</v>
       </c>
       <c r="D34">
-        <v>263.214240018971</v>
+        <v>258.9224870089814</v>
       </c>
       <c r="E34">
-        <v>-116.992</v>
+        <v>-110.573</v>
       </c>
       <c r="F34">
-        <v>205.408</v>
+        <v>211.827</v>
       </c>
       <c r="G34">
         <v>0.826</v>
@@ -4070,37 +4081,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M34">
-        <v>48.4352064</v>
+        <v>49.9488066</v>
       </c>
       <c r="N34">
-        <v>-57.86853973333333</v>
+        <v>-59.38213993333333</v>
       </c>
       <c r="O34">
-        <v>-12.152393344</v>
+        <v>-12.470249386</v>
       </c>
       <c r="P34">
-        <v>-45.71614638933333</v>
+        <v>-46.91189054733334</v>
       </c>
       <c r="Q34">
-        <v>27.58385361066667</v>
+        <v>26.38810945266666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1204195655553317</v>
+        <v>0.1215332904143666</v>
       </c>
       <c r="T34">
-        <v>1.258193075343216</v>
+        <v>1.276972076467742</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.04090000120243112</v>
+        <v>-0.03966060722659986</v>
       </c>
       <c r="W34">
-        <v>0.2454442202835333</v>
+        <v>0.2451519711840323</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4108,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.1947619104877671</v>
+        <v>-0.1888600344123803</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4116,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1623274550683562</v>
+        <v>0.1642274550683562</v>
       </c>
       <c r="C35">
-        <v>47.92148700898139</v>
+        <v>37.34844413916619</v>
       </c>
       <c r="D35">
-        <v>258.9224870089814</v>
+        <v>254.7684441391662</v>
       </c>
       <c r="E35">
-        <v>-110.573</v>
+        <v>-104.154</v>
       </c>
       <c r="F35">
-        <v>211.827</v>
+        <v>218.246</v>
       </c>
       <c r="G35">
         <v>0.826</v>
@@ -4152,37 +4163,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M35">
-        <v>49.9488066</v>
+        <v>51.4624068</v>
       </c>
       <c r="N35">
-        <v>-59.38213993333333</v>
+        <v>-60.89574013333333</v>
       </c>
       <c r="O35">
-        <v>-12.470249386</v>
+        <v>-12.788105428</v>
       </c>
       <c r="P35">
-        <v>-46.91189054733334</v>
+        <v>-48.10763470533333</v>
       </c>
       <c r="Q35">
-        <v>26.38810945266666</v>
+        <v>25.19236529466666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1215332904143666</v>
+        <v>0.1226807645115539</v>
       </c>
       <c r="T35">
-        <v>1.276972076467742</v>
+        <v>1.296320138232405</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.03966060722659986</v>
+        <v>-0.03849411877875869</v>
       </c>
       <c r="W35">
-        <v>0.2451519711840323</v>
+        <v>0.2448769132080313</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4190,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.1888600344123803</v>
+        <v>-0.1833053275178986</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4198,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1642274550683562</v>
+        <v>0.1661274550683562</v>
       </c>
       <c r="C36">
-        <v>37.34844413916619</v>
+        <v>26.90658797895378</v>
       </c>
       <c r="D36">
-        <v>254.7684441391662</v>
+        <v>250.7455879789538</v>
       </c>
       <c r="E36">
-        <v>-104.154</v>
+        <v>-97.73499999999996</v>
       </c>
       <c r="F36">
-        <v>218.246</v>
+        <v>224.665</v>
       </c>
       <c r="G36">
         <v>0.826</v>
@@ -4234,37 +4245,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M36">
-        <v>51.4624068</v>
+        <v>52.97600700000001</v>
       </c>
       <c r="N36">
-        <v>-60.89574013333333</v>
+        <v>-62.40934033333334</v>
       </c>
       <c r="O36">
-        <v>-12.788105428</v>
+        <v>-13.10596147</v>
       </c>
       <c r="P36">
-        <v>-48.10763470533333</v>
+        <v>-49.30337886333334</v>
       </c>
       <c r="Q36">
-        <v>25.19236529466666</v>
+        <v>23.99662113666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1226807645115539</v>
+        <v>0.1238635455040394</v>
       </c>
       <c r="T36">
-        <v>1.296320138232405</v>
+        <v>1.316263524974441</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.03849411877875869</v>
+        <v>-0.0373942868136513</v>
       </c>
       <c r="W36">
-        <v>0.2448769132080313</v>
+        <v>0.244617572830659</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4272,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.1833053275178986</v>
+        <v>-0.1780680324459585</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4280,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1661274550683562</v>
+        <v>0.1680274550683562</v>
       </c>
       <c r="C37">
-        <v>26.90658797895378</v>
+        <v>16.58980071917998</v>
       </c>
       <c r="D37">
-        <v>250.7455879789538</v>
+        <v>246.84780071918</v>
       </c>
       <c r="E37">
-        <v>-97.73499999999996</v>
+        <v>-91.31599999999995</v>
       </c>
       <c r="F37">
-        <v>224.665</v>
+        <v>231.084</v>
       </c>
       <c r="G37">
         <v>0.826</v>
@@ -4316,37 +4327,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M37">
-        <v>52.97600700000001</v>
+        <v>54.48960720000001</v>
       </c>
       <c r="N37">
-        <v>-62.40934033333334</v>
+        <v>-63.92294053333334</v>
       </c>
       <c r="O37">
-        <v>-13.10596147</v>
+        <v>-13.423817512</v>
       </c>
       <c r="P37">
-        <v>-49.30337886333334</v>
+        <v>-50.49912302133334</v>
       </c>
       <c r="Q37">
-        <v>23.99662113666666</v>
+        <v>22.80087697866666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1238635455040394</v>
+        <v>0.12508328840254</v>
       </c>
       <c r="T37">
-        <v>1.316263524974441</v>
+        <v>1.336830142552167</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.0373942868136513</v>
+        <v>-0.03635555662438321</v>
       </c>
       <c r="W37">
-        <v>0.244617572830659</v>
+        <v>0.2443726402520296</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4354,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.1780680324459585</v>
+        <v>-0.1731216982113486</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4362,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1680274550683562</v>
+        <v>0.1699274550683562</v>
       </c>
       <c r="C38">
-        <v>16.58980071918009</v>
+        <v>6.392339128163286</v>
       </c>
       <c r="D38">
-        <v>246.8478007191801</v>
+        <v>243.0693391281633</v>
       </c>
       <c r="E38">
-        <v>-91.316</v>
+        <v>-84.89699999999999</v>
       </c>
       <c r="F38">
-        <v>231.084</v>
+        <v>237.503</v>
       </c>
       <c r="G38">
         <v>0.826</v>
@@ -4398,37 +4409,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M38">
-        <v>54.48960719999999</v>
+        <v>56.0032074</v>
       </c>
       <c r="N38">
-        <v>-63.92294053333332</v>
+        <v>-65.43654073333333</v>
       </c>
       <c r="O38">
-        <v>-13.423817512</v>
+        <v>-13.741673554</v>
       </c>
       <c r="P38">
-        <v>-50.49912302133333</v>
+        <v>-51.69486717933333</v>
       </c>
       <c r="Q38">
-        <v>22.80087697866667</v>
+        <v>21.60513282066667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.12508328840254</v>
+        <v>0.1263417532978184</v>
       </c>
       <c r="T38">
-        <v>1.336830142552167</v>
+        <v>1.358049668624424</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.03635555662438322</v>
+        <v>-0.0353729740129134</v>
       </c>
       <c r="W38">
-        <v>0.2443726402520296</v>
+        <v>0.244140947272245</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4436,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.1731216982113486</v>
+        <v>-0.1684427333948257</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4444,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1699274550683562</v>
+        <v>0.1718274550683562</v>
       </c>
       <c r="C39">
-        <v>6.392339128163286</v>
+        <v>-3.691193684095907</v>
       </c>
       <c r="D39">
-        <v>243.0693391281633</v>
+        <v>239.4048063159041</v>
       </c>
       <c r="E39">
-        <v>-84.89699999999999</v>
+        <v>-78.47799999999998</v>
       </c>
       <c r="F39">
-        <v>237.503</v>
+        <v>243.922</v>
       </c>
       <c r="G39">
         <v>0.826</v>
@@ -4480,37 +4491,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M39">
-        <v>56.0032074</v>
+        <v>57.5168076</v>
       </c>
       <c r="N39">
-        <v>-65.43654073333333</v>
+        <v>-66.95014093333333</v>
       </c>
       <c r="O39">
-        <v>-13.741673554</v>
+        <v>-14.059529596</v>
       </c>
       <c r="P39">
-        <v>-51.69486717933333</v>
+        <v>-52.89061133733333</v>
       </c>
       <c r="Q39">
-        <v>21.60513282066667</v>
+        <v>20.40938866266666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1263417532978184</v>
+        <v>0.12764081383488</v>
       </c>
       <c r="T39">
-        <v>1.358049668624424</v>
+        <v>1.379953695537721</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.0353729740129134</v>
+        <v>-0.03444210627573147</v>
       </c>
       <c r="W39">
-        <v>0.244140947272245</v>
+        <v>0.2439214486598175</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4518,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.1684427333948257</v>
+        <v>-0.1640100298844356</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4526,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1718274550683562</v>
+        <v>0.1737274550683562</v>
       </c>
       <c r="C40">
-        <v>-3.691193684095907</v>
+        <v>-13.66587398553838</v>
       </c>
       <c r="D40">
-        <v>239.4048063159041</v>
+        <v>235.8491260144616</v>
       </c>
       <c r="E40">
-        <v>-78.47799999999998</v>
+        <v>-72.05899999999997</v>
       </c>
       <c r="F40">
-        <v>243.922</v>
+        <v>250.341</v>
       </c>
       <c r="G40">
         <v>0.826</v>
@@ -4562,37 +4573,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M40">
-        <v>57.5168076</v>
+        <v>59.03040780000001</v>
       </c>
       <c r="N40">
-        <v>-66.95014093333333</v>
+        <v>-68.46374113333334</v>
       </c>
       <c r="O40">
-        <v>-14.059529596</v>
+        <v>-14.377385638</v>
       </c>
       <c r="P40">
-        <v>-52.89061133733333</v>
+        <v>-54.08635549533334</v>
       </c>
       <c r="Q40">
-        <v>20.40938866266666</v>
+        <v>19.21364450466665</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.12764081383488</v>
+        <v>0.1289824665206977</v>
       </c>
       <c r="T40">
-        <v>1.379953695537721</v>
+        <v>1.402575887267847</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.03444210627573147</v>
+        <v>-0.0335589753455845</v>
       </c>
       <c r="W40">
-        <v>0.2439214486598175</v>
+        <v>0.2437132063864888</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4600,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.1640100298844356</v>
+        <v>-0.1598046445027834</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4608,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1737274550683562</v>
+        <v>0.1756274550683563</v>
       </c>
       <c r="C41">
-        <v>-13.66587398553838</v>
+        <v>-23.5364808832592</v>
       </c>
       <c r="D41">
-        <v>235.8491260144616</v>
+        <v>232.3975191167408</v>
       </c>
       <c r="E41">
-        <v>-72.05899999999997</v>
+        <v>-65.63999999999999</v>
       </c>
       <c r="F41">
-        <v>250.341</v>
+        <v>256.76</v>
       </c>
       <c r="G41">
         <v>0.826</v>
@@ -4644,37 +4655,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M41">
-        <v>59.03040780000001</v>
+        <v>60.544008</v>
       </c>
       <c r="N41">
-        <v>-68.46374113333334</v>
+        <v>-69.97734133333333</v>
       </c>
       <c r="O41">
-        <v>-14.377385638</v>
+        <v>-14.69524168</v>
       </c>
       <c r="P41">
-        <v>-54.08635549533334</v>
+        <v>-55.28209965333333</v>
       </c>
       <c r="Q41">
-        <v>19.21364450466665</v>
+        <v>18.01790034666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1289824665206977</v>
+        <v>0.1303688409627093</v>
       </c>
       <c r="T41">
-        <v>1.402575887267847</v>
+        <v>1.425952152055645</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.0335589753455845</v>
+        <v>-0.03272000096194489</v>
       </c>
       <c r="W41">
-        <v>0.2437132063864888</v>
+        <v>0.2435153762268266</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4682,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.1598046445027834</v>
+        <v>-0.1558095283902139</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4690,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1756274550683563</v>
+        <v>0.1775274550683562</v>
       </c>
       <c r="C42">
-        <v>-23.5364808832592</v>
+        <v>-33.30751775433271</v>
       </c>
       <c r="D42">
-        <v>232.3975191167408</v>
+        <v>229.0454822456673</v>
       </c>
       <c r="E42">
-        <v>-65.63999999999999</v>
+        <v>-59.22099999999995</v>
       </c>
       <c r="F42">
-        <v>256.76</v>
+        <v>263.179</v>
       </c>
       <c r="G42">
         <v>0.826</v>
@@ -4726,37 +4737,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M42">
-        <v>60.544008</v>
+        <v>62.05760820000001</v>
       </c>
       <c r="N42">
-        <v>-69.97734133333333</v>
+        <v>-71.49094153333334</v>
       </c>
       <c r="O42">
-        <v>-14.69524168</v>
+        <v>-15.013097722</v>
       </c>
       <c r="P42">
-        <v>-55.28209965333333</v>
+        <v>-56.47784381133334</v>
       </c>
       <c r="Q42">
-        <v>18.01790034666666</v>
+        <v>16.82215618866665</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1303688409627093</v>
+        <v>0.131802211148518</v>
       </c>
       <c r="T42">
-        <v>1.425952152055645</v>
+        <v>1.450120832598961</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.03272000096194489</v>
+        <v>-0.03192195215799501</v>
       </c>
       <c r="W42">
-        <v>0.2435153762268266</v>
+        <v>0.2433271963188552</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4764,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.1558095283902139</v>
+        <v>-0.1520092959904524</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4772,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1775274550683562</v>
+        <v>0.1794274550683563</v>
       </c>
       <c r="C43">
-        <v>-33.30751775433271</v>
+        <v>-42.98323184833501</v>
       </c>
       <c r="D43">
-        <v>229.0454822456673</v>
+        <v>225.788768151665</v>
       </c>
       <c r="E43">
-        <v>-59.22099999999995</v>
+        <v>-52.80199999999996</v>
       </c>
       <c r="F43">
-        <v>263.179</v>
+        <v>269.598</v>
       </c>
       <c r="G43">
         <v>0.826</v>
@@ -4808,37 +4819,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M43">
-        <v>62.05760820000001</v>
+        <v>63.5712084</v>
       </c>
       <c r="N43">
-        <v>-71.49094153333334</v>
+        <v>-73.00454173333333</v>
       </c>
       <c r="O43">
-        <v>-15.013097722</v>
+        <v>-15.330953764</v>
       </c>
       <c r="P43">
-        <v>-56.47784381133334</v>
+        <v>-57.67358796933333</v>
       </c>
       <c r="Q43">
-        <v>16.82215618866665</v>
+        <v>15.62641203066667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.131802211148518</v>
+        <v>0.1332850078924579</v>
       </c>
       <c r="T43">
-        <v>1.450120832598961</v>
+        <v>1.475122915919633</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.03192195215799501</v>
+        <v>-0.03116190567804275</v>
       </c>
       <c r="W43">
-        <v>0.2433271963188552</v>
+        <v>0.2431479773588825</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4846,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.1520092959904524</v>
+        <v>-0.1483900270382987</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4854,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1794274550683562</v>
+        <v>0.1813274550683562</v>
       </c>
       <c r="C44">
-        <v>-42.98323184833487</v>
+        <v>-52.56763224098447</v>
       </c>
       <c r="D44">
-        <v>225.7887681516651</v>
+        <v>222.6233677590155</v>
       </c>
       <c r="E44">
-        <v>-52.80200000000002</v>
+        <v>-46.38299999999998</v>
       </c>
       <c r="F44">
-        <v>269.598</v>
+        <v>276.017</v>
       </c>
       <c r="G44">
         <v>0.826</v>
@@ -4890,37 +4901,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M44">
-        <v>63.57120839999999</v>
+        <v>65.0848086</v>
       </c>
       <c r="N44">
-        <v>-73.00454173333333</v>
+        <v>-74.51814193333334</v>
       </c>
       <c r="O44">
-        <v>-15.330953764</v>
+        <v>-15.648809806</v>
       </c>
       <c r="P44">
-        <v>-57.67358796933333</v>
+        <v>-58.86933212733334</v>
       </c>
       <c r="Q44">
-        <v>15.62641203066667</v>
+        <v>14.43066787266666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1332850078924579</v>
+        <v>0.1348198325923256</v>
       </c>
       <c r="T44">
-        <v>1.475122915919632</v>
+        <v>1.501002265321731</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.03116190567804276</v>
+        <v>-0.03043721019715804</v>
       </c>
       <c r="W44">
-        <v>0.2431479773588825</v>
+        <v>0.2429770941644898</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4928,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.148390027038299</v>
+        <v>-0.1449390961769432</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4936,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1813274550683562</v>
+        <v>0.1832274550683562</v>
       </c>
       <c r="C45">
-        <v>-52.56763224098447</v>
+        <v>-62.06450629847711</v>
       </c>
       <c r="D45">
-        <v>222.6233677590155</v>
+        <v>219.5454937015229</v>
       </c>
       <c r="E45">
-        <v>-46.38299999999998</v>
+        <v>-39.964</v>
       </c>
       <c r="F45">
-        <v>276.017</v>
+        <v>282.436</v>
       </c>
       <c r="G45">
         <v>0.826</v>
@@ -4972,37 +4983,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M45">
-        <v>65.0848086</v>
+        <v>66.5984088</v>
       </c>
       <c r="N45">
-        <v>-74.51814193333334</v>
+        <v>-76.03174213333332</v>
       </c>
       <c r="O45">
-        <v>-15.648809806</v>
+        <v>-15.966665848</v>
       </c>
       <c r="P45">
-        <v>-58.86933212733334</v>
+        <v>-60.06507628533333</v>
       </c>
       <c r="Q45">
-        <v>14.43066787266666</v>
+        <v>13.23492371466667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1348198325923256</v>
+        <v>0.1364094724600457</v>
       </c>
       <c r="T45">
-        <v>1.501002265321731</v>
+        <v>1.527805877202477</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.03043721019715804</v>
+        <v>-0.0297454554199499</v>
       </c>
       <c r="W45">
-        <v>0.2429770941644898</v>
+        <v>0.2428139783880242</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5010,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.1449390961769432</v>
+        <v>-0.1416450258092852</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5018,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1832274550683562</v>
+        <v>0.1851274550683562</v>
       </c>
       <c r="C46">
-        <v>-62.06450629847711</v>
+        <v>-71.47743479468227</v>
       </c>
       <c r="D46">
-        <v>219.5454937015229</v>
+        <v>216.5515652053178</v>
       </c>
       <c r="E46">
-        <v>-39.964</v>
+        <v>-33.54499999999996</v>
       </c>
       <c r="F46">
-        <v>282.436</v>
+        <v>288.855</v>
       </c>
       <c r="G46">
         <v>0.826</v>
@@ -5054,37 +5065,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M46">
-        <v>66.5984088</v>
+        <v>68.112009</v>
       </c>
       <c r="N46">
-        <v>-76.03174213333332</v>
+        <v>-77.54534233333334</v>
       </c>
       <c r="O46">
-        <v>-15.966665848</v>
+        <v>-16.28452189</v>
       </c>
       <c r="P46">
-        <v>-60.06507628533333</v>
+        <v>-61.26082044333334</v>
       </c>
       <c r="Q46">
-        <v>13.23492371466667</v>
+        <v>12.03917955666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1364094724600457</v>
+        <v>0.1380569174138647</v>
       </c>
       <c r="T46">
-        <v>1.527805877202477</v>
+        <v>1.555584165878885</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.0297454554199499</v>
+        <v>-0.02908444529950657</v>
       </c>
       <c r="W46">
-        <v>0.2428139783880242</v>
+        <v>0.2426581122016236</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5092,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.1416450258092852</v>
+        <v>-0.138497358569079</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5100,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1851274550683562</v>
+        <v>0.1870274550683562</v>
       </c>
       <c r="C47">
-        <v>-71.47743479468227</v>
+        <v>-80.80980580806596</v>
       </c>
       <c r="D47">
-        <v>216.5515652053178</v>
+        <v>213.638194191934</v>
       </c>
       <c r="E47">
-        <v>-33.54499999999996</v>
+        <v>-27.12599999999998</v>
       </c>
       <c r="F47">
-        <v>288.855</v>
+        <v>295.274</v>
       </c>
       <c r="G47">
         <v>0.826</v>
@@ -5136,37 +5147,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M47">
-        <v>68.112009</v>
+        <v>69.6256092</v>
       </c>
       <c r="N47">
-        <v>-77.54534233333334</v>
+        <v>-79.05894253333332</v>
       </c>
       <c r="O47">
-        <v>-16.28452189</v>
+        <v>-16.602377932</v>
       </c>
       <c r="P47">
-        <v>-61.26082044333334</v>
+        <v>-62.45656460133333</v>
       </c>
       <c r="Q47">
-        <v>12.03917955666666</v>
+        <v>10.84343539866667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1380569174138647</v>
+        <v>0.1397653788474548</v>
       </c>
       <c r="T47">
-        <v>1.555584165878885</v>
+        <v>1.584391280061828</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.02908444529950657</v>
+        <v>-0.0284521747495173</v>
       </c>
       <c r="W47">
-        <v>0.2426581122016236</v>
+        <v>0.2425090228059362</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5174,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.138497358569079</v>
+        <v>-0.1354865464262727</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5182,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1870274550683562</v>
+        <v>0.1889274550683562</v>
       </c>
       <c r="C48">
-        <v>-80.80980580806596</v>
+        <v>-90.06482751173428</v>
       </c>
       <c r="D48">
-        <v>213.638194191934</v>
+        <v>210.8021724882657</v>
       </c>
       <c r="E48">
-        <v>-27.12599999999998</v>
+        <v>-20.70699999999999</v>
       </c>
       <c r="F48">
-        <v>295.274</v>
+        <v>301.693</v>
       </c>
       <c r="G48">
         <v>0.826</v>
@@ -5218,37 +5229,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M48">
-        <v>69.6256092</v>
+        <v>71.1392094</v>
       </c>
       <c r="N48">
-        <v>-79.05894253333332</v>
+        <v>-80.57254273333334</v>
       </c>
       <c r="O48">
-        <v>-16.602377932</v>
+        <v>-16.920233974</v>
       </c>
       <c r="P48">
-        <v>-62.45656460133333</v>
+        <v>-63.65230875933334</v>
       </c>
       <c r="Q48">
-        <v>10.84343539866667</v>
+        <v>9.64769124066666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1397653788474548</v>
+        <v>0.1415383105238218</v>
       </c>
       <c r="T48">
-        <v>1.584391280061828</v>
+        <v>1.614285455157334</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.0284521747495173</v>
+        <v>-0.0278468093293148</v>
       </c>
       <c r="W48">
-        <v>0.2425090228059362</v>
+        <v>0.2423662776398524</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5256,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.1354865464262727</v>
+        <v>-0.1326038539491181</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5264,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1889274550683562</v>
+        <v>0.1908274550683562</v>
       </c>
       <c r="C49">
-        <v>-90.06482751173428</v>
+        <v>-99.24553995810479</v>
       </c>
       <c r="D49">
-        <v>210.8021724882657</v>
+        <v>208.0404600418952</v>
       </c>
       <c r="E49">
-        <v>-20.70699999999999</v>
+        <v>-14.28799999999995</v>
       </c>
       <c r="F49">
-        <v>301.693</v>
+        <v>308.112</v>
       </c>
       <c r="G49">
         <v>0.826</v>
@@ -5300,37 +5311,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M49">
-        <v>71.1392094</v>
+        <v>72.65280960000001</v>
       </c>
       <c r="N49">
-        <v>-80.57254273333334</v>
+        <v>-82.08614293333335</v>
       </c>
       <c r="O49">
-        <v>-16.920233974</v>
+        <v>-17.238090016</v>
       </c>
       <c r="P49">
-        <v>-63.65230875933334</v>
+        <v>-64.84805291733335</v>
       </c>
       <c r="Q49">
-        <v>9.64769124066666</v>
+        <v>8.451947082666649</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1415383105238218</v>
+        <v>0.1433794318800492</v>
       </c>
       <c r="T49">
-        <v>1.614285455157334</v>
+        <v>1.645329406218052</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.0278468093293148</v>
+        <v>-0.0272666674682874</v>
       </c>
       <c r="W49">
-        <v>0.2423662776398524</v>
+        <v>0.2422294801890222</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5338,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.1326038539491181</v>
+        <v>-0.1298412736585115</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5346,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1908274550683562</v>
+        <v>0.1927274550683562</v>
       </c>
       <c r="C50">
-        <v>-99.24553995810467</v>
+        <v>-108.3548259492131</v>
       </c>
       <c r="D50">
-        <v>208.0404600418953</v>
+        <v>205.350174050787</v>
       </c>
       <c r="E50">
-        <v>-14.28800000000001</v>
+        <v>-7.868999999999971</v>
       </c>
       <c r="F50">
-        <v>308.112</v>
+        <v>314.531</v>
       </c>
       <c r="G50">
         <v>0.826</v>
@@ -5382,37 +5393,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M50">
-        <v>72.6528096</v>
+        <v>74.16640980000001</v>
       </c>
       <c r="N50">
-        <v>-82.08614293333332</v>
+        <v>-83.59974313333333</v>
       </c>
       <c r="O50">
-        <v>-17.238090016</v>
+        <v>-17.555946058</v>
       </c>
       <c r="P50">
-        <v>-64.84805291733332</v>
+        <v>-66.04379707533333</v>
       </c>
       <c r="Q50">
-        <v>8.451947082666678</v>
+        <v>7.256202924666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1433794318800492</v>
+        <v>0.1452927540737756</v>
       </c>
       <c r="T50">
-        <v>1.645329406218051</v>
+        <v>1.677590767124288</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.02726666746828741</v>
+        <v>-0.02671020486689379</v>
       </c>
       <c r="W50">
-        <v>0.2422294801890222</v>
+        <v>0.2420982663076136</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5420,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.1298412736585113</v>
+        <v>-0.1271914517471131</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5428,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1927274550683562</v>
+        <v>0.1946274550683562</v>
       </c>
       <c r="C51">
-        <v>-108.3548259492131</v>
+        <v>-117.3954210743685</v>
       </c>
       <c r="D51">
-        <v>205.350174050787</v>
+        <v>202.7285789256315</v>
       </c>
       <c r="E51">
-        <v>-7.868999999999971</v>
+        <v>-1.449999999999989</v>
       </c>
       <c r="F51">
-        <v>314.531</v>
+        <v>320.95</v>
       </c>
       <c r="G51">
         <v>0.826</v>
@@ -5464,37 +5475,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M51">
-        <v>74.16640980000001</v>
+        <v>75.68001</v>
       </c>
       <c r="N51">
-        <v>-83.59974313333333</v>
+        <v>-85.11334333333332</v>
       </c>
       <c r="O51">
-        <v>-17.555946058</v>
+        <v>-17.8738021</v>
       </c>
       <c r="P51">
-        <v>-66.04379707533333</v>
+        <v>-67.23954123333333</v>
       </c>
       <c r="Q51">
-        <v>7.256202924666667</v>
+        <v>6.06045876666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1452927540737756</v>
+        <v>0.1472826091552512</v>
       </c>
       <c r="T51">
-        <v>1.677590767124288</v>
+        <v>1.711142582466774</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.02671020486689379</v>
+        <v>-0.02617600076955592</v>
       </c>
       <c r="W51">
-        <v>0.2420982663076136</v>
+        <v>0.2419723009814613</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5502,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.1271914517471131</v>
+        <v>-0.1246476227121709</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5510,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1946274550683562</v>
+        <v>0.1965274550683562</v>
       </c>
       <c r="C52">
-        <v>-117.3954210743685</v>
+        <v>-126.3699229886283</v>
       </c>
       <c r="D52">
-        <v>202.7285789256315</v>
+        <v>200.1730770113716</v>
       </c>
       <c r="E52">
-        <v>-1.449999999999989</v>
+        <v>4.968999999999994</v>
       </c>
       <c r="F52">
-        <v>320.95</v>
+        <v>327.369</v>
       </c>
       <c r="G52">
         <v>0.826</v>
@@ -5546,37 +5557,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M52">
-        <v>75.68001</v>
+        <v>77.19361019999999</v>
       </c>
       <c r="N52">
-        <v>-85.11334333333332</v>
+        <v>-86.62694353333333</v>
       </c>
       <c r="O52">
-        <v>-17.8738021</v>
+        <v>-18.191658142</v>
       </c>
       <c r="P52">
-        <v>-67.23954123333333</v>
+        <v>-68.43528539133334</v>
       </c>
       <c r="Q52">
-        <v>6.06045876666667</v>
+        <v>4.86471460866666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1472826091552512</v>
+        <v>0.1493536828114808</v>
       </c>
       <c r="T52">
-        <v>1.711142582466774</v>
+        <v>1.746063859659974</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.02617600076955592</v>
+        <v>-0.0256627458525058</v>
       </c>
       <c r="W52">
-        <v>0.2419723009814613</v>
+        <v>0.2418512754720209</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5584,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.1246476227121709</v>
+        <v>-0.1222035516785991</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5592,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1965274550683562</v>
+        <v>0.1984274550683562</v>
       </c>
       <c r="C53">
-        <v>-126.3699229886283</v>
+        <v>-135.2807999982481</v>
       </c>
       <c r="D53">
-        <v>200.1730770113716</v>
+        <v>197.6812000017519</v>
       </c>
       <c r="E53">
-        <v>4.968999999999994</v>
+        <v>11.38800000000003</v>
       </c>
       <c r="F53">
-        <v>327.369</v>
+        <v>333.788</v>
       </c>
       <c r="G53">
         <v>0.826</v>
@@ -5628,37 +5639,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M53">
-        <v>77.19361019999999</v>
+        <v>78.70721040000001</v>
       </c>
       <c r="N53">
-        <v>-86.62694353333333</v>
+        <v>-88.14054373333335</v>
       </c>
       <c r="O53">
-        <v>-18.191658142</v>
+        <v>-18.509514184</v>
       </c>
       <c r="P53">
-        <v>-68.43528539133334</v>
+        <v>-69.63102954933335</v>
       </c>
       <c r="Q53">
-        <v>4.86471460866666</v>
+        <v>3.668970450666649</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1493536828114808</v>
+        <v>0.1515110512033866</v>
       </c>
       <c r="T53">
-        <v>1.746063859659974</v>
+        <v>1.782440190069556</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.0256627458525058</v>
+        <v>-0.02516923150918838</v>
       </c>
       <c r="W53">
-        <v>0.2418512754720209</v>
+        <v>0.2417349047898666</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5666,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.1222035516785991</v>
+        <v>-0.1198534833770877</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5674,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1984274550683562</v>
+        <v>0.2003274550683563</v>
       </c>
       <c r="C54">
-        <v>-135.2807999982481</v>
+        <v>-144.1303990127546</v>
       </c>
       <c r="D54">
-        <v>197.6812000017519</v>
+        <v>195.2506009872454</v>
       </c>
       <c r="E54">
-        <v>11.38800000000003</v>
+        <v>17.80700000000002</v>
       </c>
       <c r="F54">
-        <v>333.788</v>
+        <v>340.207</v>
       </c>
       <c r="G54">
         <v>0.826</v>
@@ -5710,37 +5721,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M54">
-        <v>78.70721040000001</v>
+        <v>80.22081060000001</v>
       </c>
       <c r="N54">
-        <v>-88.14054373333335</v>
+        <v>-89.65414393333333</v>
       </c>
       <c r="O54">
-        <v>-18.509514184</v>
+        <v>-18.827370226</v>
       </c>
       <c r="P54">
-        <v>-69.63102954933335</v>
+        <v>-70.82677370733333</v>
       </c>
       <c r="Q54">
-        <v>3.668970450666649</v>
+        <v>2.473226292666666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1515110512033866</v>
+        <v>0.1537602225055864</v>
       </c>
       <c r="T54">
-        <v>1.782440190069556</v>
+        <v>1.820364449432738</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.02516923150918838</v>
+        <v>-0.02469434034863765</v>
       </c>
       <c r="W54">
-        <v>0.2417349047898666</v>
+        <v>0.2416229254542088</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5748,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.1198534833770877</v>
+        <v>-0.1175920968982744</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5756,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2003274550683563</v>
+        <v>0.2022274550683562</v>
       </c>
       <c r="C55">
-        <v>-144.1303990127546</v>
+        <v>-152.9209529174937</v>
       </c>
       <c r="D55">
-        <v>195.2506009872454</v>
+        <v>192.8790470825063</v>
       </c>
       <c r="E55">
-        <v>17.80700000000002</v>
+        <v>24.22600000000006</v>
       </c>
       <c r="F55">
-        <v>340.207</v>
+        <v>346.626</v>
       </c>
       <c r="G55">
         <v>0.826</v>
@@ -5792,37 +5803,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M55">
-        <v>80.22081060000001</v>
+        <v>81.73441080000001</v>
       </c>
       <c r="N55">
-        <v>-89.65414393333333</v>
+        <v>-91.16774413333334</v>
       </c>
       <c r="O55">
-        <v>-18.827370226</v>
+        <v>-19.145226268</v>
       </c>
       <c r="P55">
-        <v>-70.82677370733333</v>
+        <v>-72.02251786533334</v>
       </c>
       <c r="Q55">
-        <v>2.473226292666666</v>
+        <v>1.277482134666656</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1537602225055864</v>
+        <v>0.1561071838644034</v>
       </c>
       <c r="T55">
-        <v>1.820364449432738</v>
+        <v>1.859937589637798</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.02469434034863765</v>
+        <v>-0.02423703774958881</v>
       </c>
       <c r="W55">
-        <v>0.2416229254542088</v>
+        <v>0.2415150935013531</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5830,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.1175920968982744</v>
+        <v>-0.1154144654742324</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5838,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2022274550683562</v>
+        <v>0.2041274550683563</v>
       </c>
       <c r="C56">
-        <v>-152.9209529174937</v>
+        <v>-161.6545874153358</v>
       </c>
       <c r="D56">
-        <v>192.8790470825063</v>
+        <v>190.5644125846642</v>
       </c>
       <c r="E56">
-        <v>24.22600000000006</v>
+        <v>30.64500000000004</v>
       </c>
       <c r="F56">
-        <v>346.626</v>
+        <v>353.045</v>
       </c>
       <c r="G56">
         <v>0.826</v>
@@ -5874,37 +5885,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M56">
-        <v>81.73441080000001</v>
+        <v>83.24801100000001</v>
       </c>
       <c r="N56">
-        <v>-91.16774413333334</v>
+        <v>-92.68134433333333</v>
       </c>
       <c r="O56">
-        <v>-19.145226268</v>
+        <v>-19.46308231</v>
       </c>
       <c r="P56">
-        <v>-72.02251786533334</v>
+        <v>-73.21826202333332</v>
       </c>
       <c r="Q56">
-        <v>1.277482134666656</v>
+        <v>0.08173797666667326</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1561071838644034</v>
+        <v>0.1585584546169458</v>
       </c>
       <c r="T56">
-        <v>1.859937589637798</v>
+        <v>1.901269536074193</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.02423703774958881</v>
+        <v>-0.02379636433595992</v>
       </c>
       <c r="W56">
-        <v>0.2415150935013531</v>
+        <v>0.2414111827104194</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5912,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.1154144654742324</v>
+        <v>-0.1133160206474282</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5920,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2041274550683563</v>
+        <v>0.2060274550683562</v>
       </c>
       <c r="C57">
-        <v>-161.6545874153358</v>
+        <v>-170.3333273816006</v>
       </c>
       <c r="D57">
-        <v>190.5644125846642</v>
+        <v>188.3046726183994</v>
       </c>
       <c r="E57">
-        <v>30.64500000000004</v>
+        <v>37.06400000000002</v>
       </c>
       <c r="F57">
-        <v>353.045</v>
+        <v>359.464</v>
       </c>
       <c r="G57">
         <v>0.826</v>
@@ -5956,37 +5967,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M57">
-        <v>83.24801100000001</v>
+        <v>84.7616112</v>
       </c>
       <c r="N57">
-        <v>-92.68134433333333</v>
+        <v>-94.19494453333334</v>
       </c>
       <c r="O57">
-        <v>-19.46308231</v>
+        <v>-19.780938352</v>
       </c>
       <c r="P57">
-        <v>-73.21826202333332</v>
+        <v>-74.41400618133335</v>
       </c>
       <c r="Q57">
-        <v>0.08173797666667326</v>
+        <v>-1.114006181333352</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1585584546169458</v>
+        <v>0.1611211467673309</v>
       </c>
       <c r="T57">
-        <v>1.901269536074193</v>
+        <v>1.944480207348607</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.02379636433595992</v>
+        <v>-0.02337142925853206</v>
       </c>
       <c r="W57">
-        <v>0.2414111827104194</v>
+        <v>0.2413109830191619</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5994,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.1133160206474282</v>
+        <v>-0.1112925202787243</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6002,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2060274550683562</v>
+        <v>0.2079274550683562</v>
       </c>
       <c r="C58">
-        <v>-170.3333273816006</v>
+        <v>-178.9591027721358</v>
       </c>
       <c r="D58">
-        <v>188.3046726183994</v>
+        <v>186.0978972278642</v>
       </c>
       <c r="E58">
-        <v>37.06400000000002</v>
+        <v>43.48300000000006</v>
       </c>
       <c r="F58">
-        <v>359.464</v>
+        <v>365.883</v>
       </c>
       <c r="G58">
         <v>0.826</v>
@@ -6038,37 +6049,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M58">
-        <v>84.7616112</v>
+        <v>86.27521140000002</v>
       </c>
       <c r="N58">
-        <v>-94.19494453333334</v>
+        <v>-95.70854473333335</v>
       </c>
       <c r="O58">
-        <v>-19.780938352</v>
+        <v>-20.098794394</v>
       </c>
       <c r="P58">
-        <v>-74.41400618133335</v>
+        <v>-75.60975033933335</v>
       </c>
       <c r="Q58">
-        <v>-1.114006181333352</v>
+        <v>-2.309750339333348</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1611211467673309</v>
+        <v>0.1638030339014548</v>
       </c>
       <c r="T58">
-        <v>1.944480207348607</v>
+        <v>1.989700677286946</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.02337142925853206</v>
+        <v>-0.02296140418382097</v>
       </c>
       <c r="W58">
-        <v>0.2413109830191619</v>
+        <v>0.241214299106545</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6076,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.1112925202787243</v>
+        <v>-0.1093400199229571</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6084,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2079274550683562</v>
+        <v>0.2098274550683563</v>
       </c>
       <c r="C59">
-        <v>-178.9591027721358</v>
+        <v>-187.5337541207811</v>
       </c>
       <c r="D59">
-        <v>186.0978972278642</v>
+        <v>183.9422458792189</v>
       </c>
       <c r="E59">
-        <v>43.48300000000006</v>
+        <v>49.90200000000004</v>
       </c>
       <c r="F59">
-        <v>365.883</v>
+        <v>372.302</v>
       </c>
       <c r="G59">
         <v>0.826</v>
@@ -6120,37 +6131,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M59">
-        <v>86.27521140000002</v>
+        <v>87.7888116</v>
       </c>
       <c r="N59">
-        <v>-95.70854473333335</v>
+        <v>-97.22214493333334</v>
       </c>
       <c r="O59">
-        <v>-20.098794394</v>
+        <v>-20.416650436</v>
       </c>
       <c r="P59">
-        <v>-75.60975033933335</v>
+        <v>-76.80549449733334</v>
       </c>
       <c r="Q59">
-        <v>-2.309750339333348</v>
+        <v>-3.505494497333345</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1638030339014548</v>
+        <v>0.1666126299467276</v>
       </c>
       <c r="T59">
-        <v>1.989700677286946</v>
+        <v>2.037074502936636</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.02296140418382097</v>
+        <v>-0.02256551790478958</v>
       </c>
       <c r="W59">
-        <v>0.241214299106545</v>
+        <v>0.2411209491219494</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6158,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.1093400199229571</v>
+        <v>-0.1074548471656647</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6166,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2098274550683562</v>
+        <v>0.2117274550683562</v>
       </c>
       <c r="C60">
-        <v>-187.533754120781</v>
+        <v>-196.0590376591293</v>
       </c>
       <c r="D60">
-        <v>183.942245879219</v>
+        <v>181.8359623408706</v>
       </c>
       <c r="E60">
-        <v>49.90199999999999</v>
+        <v>56.32099999999997</v>
       </c>
       <c r="F60">
-        <v>372.302</v>
+        <v>378.7209999999999</v>
       </c>
       <c r="G60">
         <v>0.826</v>
@@ -6202,37 +6213,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M60">
-        <v>87.78881159999999</v>
+        <v>89.30241179999999</v>
       </c>
       <c r="N60">
-        <v>-97.22214493333331</v>
+        <v>-98.73574513333332</v>
       </c>
       <c r="O60">
-        <v>-20.41665043599999</v>
+        <v>-20.734506478</v>
       </c>
       <c r="P60">
-        <v>-76.80549449733331</v>
+        <v>-78.00123865533332</v>
       </c>
       <c r="Q60">
-        <v>-3.505494497333316</v>
+        <v>-4.701238655333327</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1666126299467275</v>
+        <v>0.1695592794576234</v>
       </c>
       <c r="T60">
-        <v>2.037074502936635</v>
+        <v>2.0867592469107</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.02256551790478958</v>
+        <v>-0.02218305149962366</v>
       </c>
       <c r="W60">
-        <v>0.2411209491219494</v>
+        <v>0.2410307635436113</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6240,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.1074548471656647</v>
+        <v>-0.1056335785696365</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6248,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2117274550683562</v>
+        <v>0.2136274550683562</v>
       </c>
       <c r="C61">
-        <v>-196.0590376591293</v>
+        <v>-204.5366300885202</v>
       </c>
       <c r="D61">
-        <v>181.8359623408706</v>
+        <v>179.7773699114798</v>
       </c>
       <c r="E61">
-        <v>56.32099999999997</v>
+        <v>62.74000000000001</v>
       </c>
       <c r="F61">
-        <v>378.7209999999999</v>
+        <v>385.14</v>
       </c>
       <c r="G61">
         <v>0.826</v>
@@ -6284,37 +6295,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M61">
-        <v>89.30241179999999</v>
+        <v>90.816012</v>
       </c>
       <c r="N61">
-        <v>-98.73574513333332</v>
+        <v>-100.2493453333333</v>
       </c>
       <c r="O61">
-        <v>-20.734506478</v>
+        <v>-21.05236252</v>
       </c>
       <c r="P61">
-        <v>-78.00123865533332</v>
+        <v>-79.19698281333334</v>
       </c>
       <c r="Q61">
-        <v>-4.701238655333327</v>
+        <v>-5.896982813333338</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1695592794576234</v>
+        <v>0.172653261444064</v>
       </c>
       <c r="T61">
-        <v>2.0867592469107</v>
+        <v>2.138928228083467</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.02218305149962366</v>
+        <v>-0.02181333397462993</v>
       </c>
       <c r="W61">
-        <v>0.2410307635436113</v>
+        <v>0.2409435841512178</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6322,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.1056335785696365</v>
+        <v>-0.1038730189268093</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6330,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2136274550683562</v>
+        <v>0.2155274550683562</v>
       </c>
       <c r="C62">
-        <v>-204.5366300885202</v>
+        <v>-212.9681330315134</v>
       </c>
       <c r="D62">
-        <v>179.7773699114798</v>
+        <v>177.7648669684866</v>
       </c>
       <c r="E62">
-        <v>62.74000000000001</v>
+        <v>69.15899999999999</v>
       </c>
       <c r="F62">
-        <v>385.14</v>
+        <v>391.559</v>
       </c>
       <c r="G62">
         <v>0.826</v>
@@ -6366,37 +6377,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M62">
-        <v>90.816012</v>
+        <v>92.3296122</v>
       </c>
       <c r="N62">
-        <v>-100.2493453333333</v>
+        <v>-101.7629455333333</v>
       </c>
       <c r="O62">
-        <v>-21.05236252</v>
+        <v>-21.370218562</v>
       </c>
       <c r="P62">
-        <v>-79.19698281333334</v>
+        <v>-80.39272697133333</v>
       </c>
       <c r="Q62">
-        <v>-5.896982813333338</v>
+        <v>-7.092726971333335</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.172653261444064</v>
+        <v>0.1759059091733989</v>
       </c>
       <c r="T62">
-        <v>2.138928228083467</v>
+        <v>2.193772541624069</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.02181333397462993</v>
+        <v>-0.02145573833570157</v>
       </c>
       <c r="W62">
-        <v>0.2409435841512178</v>
+        <v>0.2408592630995584</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6404,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.1038730189268093</v>
+        <v>-0.1021701825509598</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6412,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2155274550683562</v>
+        <v>0.2174274550683563</v>
       </c>
       <c r="C63">
-        <v>-212.9681330315134</v>
+        <v>-221.3550771876836</v>
       </c>
       <c r="D63">
-        <v>177.7648669684866</v>
+        <v>175.7969228123164</v>
       </c>
       <c r="E63">
-        <v>69.15899999999999</v>
+        <v>75.57800000000003</v>
       </c>
       <c r="F63">
-        <v>391.559</v>
+        <v>397.978</v>
       </c>
       <c r="G63">
         <v>0.826</v>
@@ -6448,37 +6459,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M63">
-        <v>92.3296122</v>
+        <v>93.8432124</v>
       </c>
       <c r="N63">
-        <v>-101.7629455333333</v>
+        <v>-103.2765457333333</v>
       </c>
       <c r="O63">
-        <v>-21.370218562</v>
+        <v>-21.688074604</v>
       </c>
       <c r="P63">
-        <v>-80.39272697133333</v>
+        <v>-81.58847112933333</v>
       </c>
       <c r="Q63">
-        <v>-7.092726971333335</v>
+        <v>-8.288471129333331</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1759059091733989</v>
+        <v>0.1793297488884884</v>
       </c>
       <c r="T63">
-        <v>2.193772541624069</v>
+        <v>2.251503397982597</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.02145573833570157</v>
+        <v>-0.02110967803996444</v>
       </c>
       <c r="W63">
-        <v>0.2408592630995584</v>
+        <v>0.2407776620818236</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6486,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.1021701825509598</v>
+        <v>-0.1005222763807831</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6494,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2174274550683563</v>
+        <v>0.2193274550683562</v>
       </c>
       <c r="C64">
-        <v>-221.3550771876836</v>
+        <v>-229.6989262163967</v>
       </c>
       <c r="D64">
-        <v>175.7969228123164</v>
+        <v>173.8720737836033</v>
       </c>
       <c r="E64">
-        <v>75.57800000000003</v>
+        <v>81.99700000000001</v>
       </c>
       <c r="F64">
-        <v>397.978</v>
+        <v>404.397</v>
       </c>
       <c r="G64">
         <v>0.826</v>
@@ -6530,37 +6541,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M64">
-        <v>93.8432124</v>
+        <v>95.3568126</v>
       </c>
       <c r="N64">
-        <v>-103.2765457333333</v>
+        <v>-104.7901459333333</v>
       </c>
       <c r="O64">
-        <v>-21.688074604</v>
+        <v>-22.005930646</v>
       </c>
       <c r="P64">
-        <v>-81.58847112933333</v>
+        <v>-82.78421528733332</v>
       </c>
       <c r="Q64">
-        <v>-8.288471129333331</v>
+        <v>-9.484215287333328</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1793297488884884</v>
+        <v>0.1829386610206097</v>
       </c>
       <c r="T64">
-        <v>2.251503397982597</v>
+        <v>2.312354841171316</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.02110967803996444</v>
+        <v>-0.02077460378536184</v>
       </c>
       <c r="W64">
-        <v>0.2407776620818236</v>
+        <v>0.2406986515725883</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6568,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.1005222763807831</v>
+        <v>-0.09892668469219923</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6576,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2193274550683562</v>
+        <v>0.2212274550683562</v>
       </c>
       <c r="C65">
-        <v>-229.6989262163967</v>
+        <v>-238.0010803672686</v>
       </c>
       <c r="D65">
-        <v>173.8720737836033</v>
+        <v>171.9889196327314</v>
       </c>
       <c r="E65">
-        <v>81.99700000000001</v>
+        <v>88.416</v>
       </c>
       <c r="F65">
-        <v>404.397</v>
+        <v>410.816</v>
       </c>
       <c r="G65">
         <v>0.826</v>
@@ -6612,37 +6623,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M65">
-        <v>95.3568126</v>
+        <v>96.8704128</v>
       </c>
       <c r="N65">
-        <v>-104.7901459333333</v>
+        <v>-106.3037461333333</v>
       </c>
       <c r="O65">
-        <v>-22.005930646</v>
+        <v>-22.323786688</v>
       </c>
       <c r="P65">
-        <v>-82.78421528733332</v>
+        <v>-83.97995944533334</v>
       </c>
       <c r="Q65">
-        <v>-9.484215287333328</v>
+        <v>-10.67995944533334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1829386610206097</v>
+        <v>0.1867480682711822</v>
       </c>
       <c r="T65">
-        <v>2.312354841171316</v>
+        <v>2.376586920092742</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.02077460378536184</v>
+        <v>-0.02045000060121556</v>
       </c>
       <c r="W65">
-        <v>0.2406986515725883</v>
+        <v>0.2406221101417667</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6650,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.09892668469219923</v>
+        <v>-0.09738095524388379</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6658,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2212274550683562</v>
+        <v>0.2231274550683562</v>
       </c>
       <c r="C66">
-        <v>-238.0010803672686</v>
+        <v>-246.2628798772273</v>
       </c>
       <c r="D66">
-        <v>171.9889196327314</v>
+        <v>170.1461201227727</v>
       </c>
       <c r="E66">
-        <v>88.416</v>
+        <v>94.83500000000004</v>
       </c>
       <c r="F66">
-        <v>410.816</v>
+        <v>417.235</v>
       </c>
       <c r="G66">
         <v>0.826</v>
@@ -6694,37 +6705,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M66">
-        <v>96.8704128</v>
+        <v>98.38401300000001</v>
       </c>
       <c r="N66">
-        <v>-106.3037461333333</v>
+        <v>-107.8173463333333</v>
       </c>
       <c r="O66">
-        <v>-22.323786688</v>
+        <v>-22.64164273</v>
       </c>
       <c r="P66">
-        <v>-83.97995944533334</v>
+        <v>-85.17570360333335</v>
       </c>
       <c r="Q66">
-        <v>-10.67995944533334</v>
+        <v>-11.87570360333335</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1867480682711822</v>
+        <v>0.1907751559360731</v>
       </c>
       <c r="T66">
-        <v>2.376586920092742</v>
+        <v>2.444489403523963</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.02045000060121556</v>
+        <v>-0.0201353852073507</v>
       </c>
       <c r="W66">
-        <v>0.2406221101417667</v>
+        <v>0.2405479238318933</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6732,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.09738095524388379</v>
+        <v>-0.09588278670167005</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6740,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2231274550683562</v>
+        <v>0.2250274550683562</v>
       </c>
       <c r="C67">
-        <v>-246.2628798772273</v>
+        <v>-254.4856081515029</v>
       </c>
       <c r="D67">
-        <v>170.1461201227727</v>
+        <v>168.3423918484971</v>
       </c>
       <c r="E67">
-        <v>94.83500000000004</v>
+        <v>101.254</v>
       </c>
       <c r="F67">
-        <v>417.235</v>
+        <v>423.654</v>
       </c>
       <c r="G67">
         <v>0.826</v>
@@ -6776,37 +6787,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M67">
-        <v>98.38401300000001</v>
+        <v>99.89761320000001</v>
       </c>
       <c r="N67">
-        <v>-107.8173463333333</v>
+        <v>-109.3309465333333</v>
       </c>
       <c r="O67">
-        <v>-22.64164273</v>
+        <v>-22.959498772</v>
       </c>
       <c r="P67">
-        <v>-85.17570360333335</v>
+        <v>-86.37144776133333</v>
       </c>
       <c r="Q67">
-        <v>-11.87570360333335</v>
+        <v>-13.07144776133333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1907751559360731</v>
+        <v>0.1950391311106635</v>
       </c>
       <c r="T67">
-        <v>2.444489403523963</v>
+        <v>2.516386150686432</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.0201353852073507</v>
+        <v>-0.01983030361329993</v>
       </c>
       <c r="W67">
-        <v>0.2405479238318933</v>
+        <v>0.2404759855920161</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6814,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.09588278670167005</v>
+        <v>-0.09443001720619004</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6822,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2250274550683562</v>
+        <v>0.2269274550683563</v>
       </c>
       <c r="C68">
-        <v>-254.4856081515029</v>
+        <v>-262.6704947444077</v>
       </c>
       <c r="D68">
-        <v>168.3423918484971</v>
+        <v>166.5765052555924</v>
       </c>
       <c r="E68">
-        <v>101.254</v>
+        <v>107.6730000000001</v>
       </c>
       <c r="F68">
-        <v>423.654</v>
+        <v>430.073</v>
       </c>
       <c r="G68">
         <v>0.826</v>
@@ -6858,37 +6869,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M68">
-        <v>99.89761320000001</v>
+        <v>101.4112134</v>
       </c>
       <c r="N68">
-        <v>-109.3309465333333</v>
+        <v>-110.8445467333333</v>
       </c>
       <c r="O68">
-        <v>-22.959498772</v>
+        <v>-23.277354814</v>
       </c>
       <c r="P68">
-        <v>-86.37144776133333</v>
+        <v>-87.56719191933334</v>
       </c>
       <c r="Q68">
-        <v>-13.07144776133333</v>
+        <v>-14.26719191933334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1950391311106635</v>
+        <v>0.1995615290231079</v>
       </c>
       <c r="T68">
-        <v>2.516386150686432</v>
+        <v>2.59264027646481</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.01983030361329993</v>
+        <v>-0.01953432893250441</v>
       </c>
       <c r="W68">
-        <v>0.2404759855920161</v>
+        <v>0.2404061947622846</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6896,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.09443001720619004</v>
+        <v>-0.09302061396430683</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6904,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2269274550683563</v>
+        <v>0.2288274550683563</v>
       </c>
       <c r="C69">
-        <v>-262.6704947444077</v>
+        <v>-270.8187181544552</v>
       </c>
       <c r="D69">
-        <v>166.5765052555924</v>
+        <v>164.8472818455448</v>
       </c>
       <c r="E69">
-        <v>107.6730000000001</v>
+        <v>114.092</v>
       </c>
       <c r="F69">
-        <v>430.073</v>
+        <v>436.492</v>
       </c>
       <c r="G69">
         <v>0.826</v>
@@ -6940,37 +6951,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M69">
-        <v>101.4112134</v>
+        <v>102.9248136</v>
       </c>
       <c r="N69">
-        <v>-110.8445467333333</v>
+        <v>-112.3581469333333</v>
       </c>
       <c r="O69">
-        <v>-23.277354814</v>
+        <v>-23.595210856</v>
       </c>
       <c r="P69">
-        <v>-87.56719191933334</v>
+        <v>-88.76293607733334</v>
       </c>
       <c r="Q69">
-        <v>-14.26719191933334</v>
+        <v>-15.46293607733334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1995615290231079</v>
+        <v>0.20436657680508</v>
       </c>
       <c r="T69">
-        <v>2.59264027646481</v>
+        <v>2.673660285104335</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.01953432893250441</v>
+        <v>-0.01924705938937935</v>
       </c>
       <c r="W69">
-        <v>0.2404061947622846</v>
+        <v>0.2403384566040157</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6978,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.09302061396430683</v>
+        <v>-0.0916526637589492</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6986,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2288274550683563</v>
+        <v>0.2307274550683563</v>
       </c>
       <c r="C70">
-        <v>-270.8187181544552</v>
+        <v>-278.9314084471742</v>
       </c>
       <c r="D70">
-        <v>164.8472818455448</v>
+        <v>163.1535915528257</v>
       </c>
       <c r="E70">
-        <v>114.092</v>
+        <v>120.511</v>
       </c>
       <c r="F70">
-        <v>436.492</v>
+        <v>442.911</v>
       </c>
       <c r="G70">
         <v>0.826</v>
@@ -7022,37 +7033,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M70">
-        <v>102.9248136</v>
+        <v>104.4384138</v>
       </c>
       <c r="N70">
-        <v>-112.3581469333333</v>
+        <v>-113.8717471333333</v>
       </c>
       <c r="O70">
-        <v>-23.595210856</v>
+        <v>-23.913066898</v>
       </c>
       <c r="P70">
-        <v>-88.76293607733334</v>
+        <v>-89.95868023533335</v>
       </c>
       <c r="Q70">
-        <v>-15.46293607733334</v>
+        <v>-16.65868023533335</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.20436657680508</v>
+        <v>0.20948162766976</v>
       </c>
       <c r="T70">
-        <v>2.673660285104335</v>
+        <v>2.759907391075442</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.01924705938937935</v>
+        <v>-0.01896811649967819</v>
       </c>
       <c r="W70">
-        <v>0.2403384566040157</v>
+        <v>0.2402726818706241</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7060,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.0916526637589492</v>
+        <v>-0.090324364284182</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7068,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2307274550683563</v>
+        <v>0.2326274550683562</v>
       </c>
       <c r="C71">
-        <v>-278.9314084471742</v>
+        <v>-287.0096497178803</v>
       </c>
       <c r="D71">
-        <v>163.1535915528257</v>
+        <v>161.4943502821198</v>
       </c>
       <c r="E71">
-        <v>120.511</v>
+        <v>126.9300000000001</v>
       </c>
       <c r="F71">
-        <v>442.911</v>
+        <v>449.33</v>
       </c>
       <c r="G71">
         <v>0.826</v>
@@ -7104,37 +7115,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M71">
-        <v>104.4384138</v>
+        <v>105.952014</v>
       </c>
       <c r="N71">
-        <v>-113.8717471333333</v>
+        <v>-115.3853473333334</v>
       </c>
       <c r="O71">
-        <v>-23.913066898</v>
+        <v>-24.23092294</v>
       </c>
       <c r="P71">
-        <v>-89.95868023533335</v>
+        <v>-91.15442439333336</v>
       </c>
       <c r="Q71">
-        <v>-16.65868023533335</v>
+        <v>-17.85442439333336</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.20948162766976</v>
+        <v>0.2149376819254186</v>
       </c>
       <c r="T71">
-        <v>2.759907391075442</v>
+        <v>2.85190430411129</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.01896811649967819</v>
+        <v>-0.01869714340682565</v>
       </c>
       <c r="W71">
-        <v>0.2402726818706241</v>
+        <v>0.2402087864153295</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7142,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.090324364284182</v>
+        <v>-0.08903401622297946</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7150,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2326274550683562</v>
+        <v>0.2345274550683563</v>
       </c>
       <c r="C72">
-        <v>-287.0096497178803</v>
+        <v>-295.0544824056834</v>
       </c>
       <c r="D72">
-        <v>161.4943502821198</v>
+        <v>159.8685175943166</v>
       </c>
       <c r="E72">
-        <v>126.9300000000001</v>
+        <v>133.349</v>
       </c>
       <c r="F72">
-        <v>449.33</v>
+        <v>455.749</v>
       </c>
       <c r="G72">
         <v>0.826</v>
@@ -7186,37 +7197,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M72">
-        <v>105.952014</v>
+        <v>107.4656142</v>
       </c>
       <c r="N72">
-        <v>-115.3853473333334</v>
+        <v>-116.8989475333333</v>
       </c>
       <c r="O72">
-        <v>-24.23092294</v>
+        <v>-24.548778982</v>
       </c>
       <c r="P72">
-        <v>-91.15442439333336</v>
+        <v>-92.35016855133334</v>
       </c>
       <c r="Q72">
-        <v>-17.85442439333336</v>
+        <v>-19.05016855133334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2149376819254186</v>
+        <v>0.2207700157849159</v>
       </c>
       <c r="T72">
-        <v>2.85190430411129</v>
+        <v>2.950245831839266</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.01869714340682565</v>
+        <v>-0.01843380335884219</v>
       </c>
       <c r="W72">
-        <v>0.2402087864153295</v>
+        <v>0.240146690832015</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7224,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.08903401622297946</v>
+        <v>-0.08778001599448659</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7232,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2345274550683562</v>
+        <v>0.2364274550683562</v>
       </c>
       <c r="C73">
-        <v>-295.0544824056832</v>
+        <v>-303.0669054691149</v>
       </c>
       <c r="D73">
-        <v>159.8685175943168</v>
+        <v>158.275094530885</v>
       </c>
       <c r="E73">
-        <v>133.349</v>
+        <v>139.768</v>
       </c>
       <c r="F73">
-        <v>455.749</v>
+        <v>462.1679999999999</v>
       </c>
       <c r="G73">
         <v>0.826</v>
@@ -7268,37 +7279,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M73">
-        <v>107.4656142</v>
+        <v>108.9792144</v>
       </c>
       <c r="N73">
-        <v>-116.8989475333333</v>
+        <v>-118.4125477333333</v>
       </c>
       <c r="O73">
-        <v>-24.54877898199999</v>
+        <v>-24.866635024</v>
       </c>
       <c r="P73">
-        <v>-92.35016855133333</v>
+        <v>-93.54591270933332</v>
       </c>
       <c r="Q73">
-        <v>-19.05016855133333</v>
+        <v>-20.24591270933333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2207700157849158</v>
+        <v>0.2270189449200914</v>
       </c>
       <c r="T73">
-        <v>2.950245831839265</v>
+        <v>3.055611754404953</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.01843380335884219</v>
+        <v>-0.01817777831219161</v>
       </c>
       <c r="W73">
-        <v>0.240146690832015</v>
+        <v>0.2400863201260148</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7306,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.08778001599448659</v>
+        <v>-0.08656084910567441</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7314,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2364274550683562</v>
+        <v>0.2383274550683562</v>
       </c>
       <c r="C74">
-        <v>-303.0669054691149</v>
+        <v>-311.0478784329289</v>
       </c>
       <c r="D74">
-        <v>158.275094530885</v>
+        <v>156.7131215670711</v>
       </c>
       <c r="E74">
-        <v>139.768</v>
+        <v>146.187</v>
       </c>
       <c r="F74">
-        <v>462.1679999999999</v>
+        <v>468.587</v>
       </c>
       <c r="G74">
         <v>0.826</v>
@@ -7350,37 +7361,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M74">
-        <v>108.9792144</v>
+        <v>110.4928146</v>
       </c>
       <c r="N74">
-        <v>-118.4125477333333</v>
+        <v>-119.9261479333333</v>
       </c>
       <c r="O74">
-        <v>-24.866635024</v>
+        <v>-25.184491066</v>
       </c>
       <c r="P74">
-        <v>-93.54591270933332</v>
+        <v>-94.74165686733335</v>
       </c>
       <c r="Q74">
-        <v>-20.24591270933333</v>
+        <v>-21.44165686733335</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2270189449200914</v>
+        <v>0.2337307576949096</v>
       </c>
       <c r="T74">
-        <v>3.055611754404953</v>
+        <v>3.168782560123655</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.01817777831219161</v>
+        <v>-0.01792876765038076</v>
       </c>
       <c r="W74">
-        <v>0.2400863201260148</v>
+        <v>0.2400276034119598</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7388,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.08656084910567441</v>
+        <v>-0.08537508404943228</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7396,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2383274550683562</v>
+        <v>0.2402274550683562</v>
       </c>
       <c r="C75">
-        <v>-311.0478784329289</v>
+        <v>-318.9983233148915</v>
       </c>
       <c r="D75">
-        <v>156.7131215670711</v>
+        <v>155.1816766851085</v>
       </c>
       <c r="E75">
-        <v>146.187</v>
+        <v>152.606</v>
       </c>
       <c r="F75">
-        <v>468.587</v>
+        <v>475.006</v>
       </c>
       <c r="G75">
         <v>0.826</v>
@@ -7432,37 +7443,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M75">
-        <v>110.4928146</v>
+        <v>112.0064148</v>
       </c>
       <c r="N75">
-        <v>-119.9261479333333</v>
+        <v>-121.4397481333333</v>
       </c>
       <c r="O75">
-        <v>-25.184491066</v>
+        <v>-25.502347108</v>
       </c>
       <c r="P75">
-        <v>-94.74165686733335</v>
+        <v>-95.93740102533333</v>
       </c>
       <c r="Q75">
-        <v>-21.44165686733335</v>
+        <v>-22.63740102533333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2337307576949096</v>
+        <v>0.2409588637600984</v>
       </c>
       <c r="T75">
-        <v>3.168782560123655</v>
+        <v>3.290658812436103</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.01792876765038076</v>
+        <v>-0.0176864870064567</v>
       </c>
       <c r="W75">
-        <v>0.2400276034119598</v>
+        <v>0.2399704736361225</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7470,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.08537508404943228</v>
+        <v>-0.08422136669741276</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7478,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2402274550683562</v>
+        <v>0.2421274550683562</v>
       </c>
       <c r="C76">
-        <v>-318.9983233148915</v>
+        <v>-326.9191264406898</v>
       </c>
       <c r="D76">
-        <v>155.1816766851085</v>
+        <v>153.6798735593102</v>
       </c>
       <c r="E76">
-        <v>152.606</v>
+        <v>159.025</v>
       </c>
       <c r="F76">
-        <v>475.006</v>
+        <v>481.425</v>
       </c>
       <c r="G76">
         <v>0.826</v>
@@ -7514,37 +7525,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M76">
-        <v>112.0064148</v>
+        <v>113.520015</v>
       </c>
       <c r="N76">
-        <v>-121.4397481333333</v>
+        <v>-122.9533483333333</v>
       </c>
       <c r="O76">
-        <v>-25.502347108</v>
+        <v>-25.82020315</v>
       </c>
       <c r="P76">
-        <v>-95.93740102533333</v>
+        <v>-97.13314518333334</v>
       </c>
       <c r="Q76">
-        <v>-22.63740102533333</v>
+        <v>-23.83314518333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2409588637600984</v>
+        <v>0.2487652183105024</v>
       </c>
       <c r="T76">
-        <v>3.290658812436103</v>
+        <v>3.422285164933548</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.0176864870064567</v>
+        <v>-0.01745066717970394</v>
       </c>
       <c r="W76">
-        <v>0.2399704736361225</v>
+        <v>0.2399148673209742</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7552,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.08422136669741276</v>
+        <v>-0.08309841514144733</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7560,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2421274550683562</v>
+        <v>0.2440274550683562</v>
       </c>
       <c r="C77">
-        <v>-326.9191264406898</v>
+        <v>-334.8111401544663</v>
       </c>
       <c r="D77">
-        <v>153.6798735593102</v>
+        <v>152.2068598455337</v>
       </c>
       <c r="E77">
-        <v>159.025</v>
+        <v>165.444</v>
       </c>
       <c r="F77">
-        <v>481.425</v>
+        <v>487.844</v>
       </c>
       <c r="G77">
         <v>0.826</v>
@@ -7596,37 +7607,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M77">
-        <v>113.520015</v>
+        <v>115.0336152</v>
       </c>
       <c r="N77">
-        <v>-122.9533483333333</v>
+        <v>-124.4669485333333</v>
       </c>
       <c r="O77">
-        <v>-25.82020315</v>
+        <v>-26.138059192</v>
       </c>
       <c r="P77">
-        <v>-97.13314518333334</v>
+        <v>-98.32888934133332</v>
       </c>
       <c r="Q77">
-        <v>-23.83314518333334</v>
+        <v>-25.02888934133333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2487652183105024</v>
+        <v>0.2572221024067732</v>
       </c>
       <c r="T77">
-        <v>3.422285164933548</v>
+        <v>3.564880380139112</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.01745066717970394</v>
+        <v>-0.01722105313786573</v>
       </c>
       <c r="W77">
-        <v>0.2399148673209742</v>
+        <v>0.2398607243299088</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7634,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.08309841514144733</v>
+        <v>-0.08200501494221779</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7642,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2440274550683562</v>
+        <v>0.2459274550683563</v>
       </c>
       <c r="C78">
-        <v>-334.8111401544663</v>
+        <v>-342.6751844319131</v>
       </c>
       <c r="D78">
-        <v>152.2068598455337</v>
+        <v>150.7618155680869</v>
       </c>
       <c r="E78">
-        <v>165.444</v>
+        <v>171.863</v>
       </c>
       <c r="F78">
-        <v>487.844</v>
+        <v>494.263</v>
       </c>
       <c r="G78">
         <v>0.826</v>
@@ -7678,37 +7689,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M78">
-        <v>115.0336152</v>
+        <v>116.5472154</v>
       </c>
       <c r="N78">
-        <v>-124.4669485333333</v>
+        <v>-125.9805487333333</v>
       </c>
       <c r="O78">
-        <v>-26.138059192</v>
+        <v>-26.455915234</v>
       </c>
       <c r="P78">
-        <v>-98.32888934133332</v>
+        <v>-99.52463349933333</v>
       </c>
       <c r="Q78">
-        <v>-25.02888934133333</v>
+        <v>-26.22463349933334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2572221024067732</v>
+        <v>0.2664143677288069</v>
       </c>
       <c r="T78">
-        <v>3.564880380139112</v>
+        <v>3.719875179275596</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.01722105313786573</v>
+        <v>-0.01699740309711423</v>
       </c>
       <c r="W78">
-        <v>0.2398607243299088</v>
+        <v>0.2398079876502996</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7716,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.08200501494221779</v>
+        <v>-0.08094001474816315</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7724,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2459274550683563</v>
+        <v>0.2478274550683562</v>
       </c>
       <c r="C79">
-        <v>-342.6751844319131</v>
+        <v>-350.5120484023446</v>
       </c>
       <c r="D79">
-        <v>150.7618155680869</v>
+        <v>149.3439515976555</v>
       </c>
       <c r="E79">
-        <v>171.863</v>
+        <v>178.282</v>
       </c>
       <c r="F79">
-        <v>494.263</v>
+        <v>500.682</v>
       </c>
       <c r="G79">
         <v>0.826</v>
@@ -7760,37 +7771,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M79">
-        <v>116.5472154</v>
+        <v>118.0608156</v>
       </c>
       <c r="N79">
-        <v>-125.9805487333333</v>
+        <v>-127.4941489333333</v>
       </c>
       <c r="O79">
-        <v>-26.455915234</v>
+        <v>-26.773771276</v>
       </c>
       <c r="P79">
-        <v>-99.52463349933333</v>
+        <v>-100.7203776573333</v>
       </c>
       <c r="Q79">
-        <v>-26.22463349933334</v>
+        <v>-27.42037765733335</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2664143677288069</v>
+        <v>0.2764422935346618</v>
       </c>
       <c r="T79">
-        <v>3.719875179275596</v>
+        <v>3.888960414697213</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.01699740309711423</v>
+        <v>-0.01677948767279225</v>
       </c>
       <c r="W79">
-        <v>0.2398079876502996</v>
+        <v>0.2397566031932444</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7798,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.08094001474816315</v>
+        <v>-0.07990232225139171</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7806,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2478274550683562</v>
+        <v>0.2497274550683563</v>
       </c>
       <c r="C80">
-        <v>-350.5120484023446</v>
+        <v>-358.3224917856811</v>
       </c>
       <c r="D80">
-        <v>149.3439515976555</v>
+        <v>147.9525082143189</v>
       </c>
       <c r="E80">
-        <v>178.282</v>
+        <v>184.701</v>
       </c>
       <c r="F80">
-        <v>500.682</v>
+        <v>507.101</v>
       </c>
       <c r="G80">
         <v>0.826</v>
@@ -7842,37 +7853,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M80">
-        <v>118.0608156</v>
+        <v>119.5744158</v>
       </c>
       <c r="N80">
-        <v>-127.4941489333333</v>
+        <v>-129.0077491333333</v>
       </c>
       <c r="O80">
-        <v>-26.773771276</v>
+        <v>-27.091627318</v>
       </c>
       <c r="P80">
-        <v>-100.7203776573333</v>
+        <v>-101.9161218153333</v>
       </c>
       <c r="Q80">
-        <v>-27.42037765733335</v>
+        <v>-28.61612181533333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2764422935346618</v>
+        <v>0.2874252598934552</v>
       </c>
       <c r="T80">
-        <v>3.888960414697213</v>
+        <v>4.074149005873272</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.01677948767279225</v>
+        <v>-0.01656708909465564</v>
       </c>
       <c r="W80">
-        <v>0.2397566031932444</v>
+        <v>0.2397065196085198</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7880,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.07990232225139171</v>
+        <v>-0.07889090045074099</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7888,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2497274550683563</v>
+        <v>0.2516274550683563</v>
       </c>
       <c r="C81">
-        <v>-358.3224917856811</v>
+        <v>-366.1072462498455</v>
       </c>
       <c r="D81">
-        <v>147.9525082143189</v>
+        <v>146.5867537501545</v>
       </c>
       <c r="E81">
-        <v>184.701</v>
+        <v>191.12</v>
       </c>
       <c r="F81">
-        <v>507.101</v>
+        <v>513.52</v>
       </c>
       <c r="G81">
         <v>0.826</v>
@@ -7924,37 +7935,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M81">
-        <v>119.5744158</v>
+        <v>121.088016</v>
       </c>
       <c r="N81">
-        <v>-129.0077491333333</v>
+        <v>-130.5213493333333</v>
       </c>
       <c r="O81">
-        <v>-27.091627318</v>
+        <v>-27.40948336</v>
       </c>
       <c r="P81">
-        <v>-101.9161218153333</v>
+        <v>-103.1118659733333</v>
       </c>
       <c r="Q81">
-        <v>-28.61612181533333</v>
+        <v>-29.81186597333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2874252598934552</v>
+        <v>0.299506522888128</v>
       </c>
       <c r="T81">
-        <v>4.074149005873272</v>
+        <v>4.277856456166935</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.01656708909465564</v>
+        <v>-0.01636000048097245</v>
       </c>
       <c r="W81">
-        <v>0.2397065196085198</v>
+        <v>0.2396576881134133</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7962,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.07889090045074099</v>
+        <v>-0.07790476419510672</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7970,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2516274550683563</v>
+        <v>0.2535274550683563</v>
       </c>
       <c r="C82">
-        <v>-366.1072462498455</v>
+        <v>-373.8670166936641</v>
       </c>
       <c r="D82">
-        <v>146.5867537501545</v>
+        <v>145.2459833063359</v>
       </c>
       <c r="E82">
-        <v>191.12</v>
+        <v>197.539</v>
       </c>
       <c r="F82">
-        <v>513.52</v>
+        <v>519.939</v>
       </c>
       <c r="G82">
         <v>0.826</v>
@@ -8006,37 +8017,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M82">
-        <v>121.088016</v>
+        <v>122.6016162</v>
       </c>
       <c r="N82">
-        <v>-130.5213493333333</v>
+        <v>-132.0349495333333</v>
       </c>
       <c r="O82">
-        <v>-27.40948336</v>
+        <v>-27.727339402</v>
       </c>
       <c r="P82">
-        <v>-103.1118659733333</v>
+        <v>-104.3076101313333</v>
       </c>
       <c r="Q82">
-        <v>-29.81186597333333</v>
+        <v>-31.00761013133334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.299506522888128</v>
+        <v>0.3128594977769768</v>
       </c>
       <c r="T82">
-        <v>4.277856456166935</v>
+        <v>4.503006795965195</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.01636000048097245</v>
+        <v>-0.01615802516639254</v>
       </c>
       <c r="W82">
-        <v>0.2396576881134133</v>
+        <v>0.2396100623342354</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8044,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.07790476419510672</v>
+        <v>-0.0769429769828216</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8052,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2535274550683563</v>
+        <v>0.2554274550683563</v>
       </c>
       <c r="C83">
-        <v>-373.8670166936641</v>
+        <v>-381.6024824600021</v>
       </c>
       <c r="D83">
-        <v>145.2459833063359</v>
+        <v>143.929517539998</v>
       </c>
       <c r="E83">
-        <v>197.539</v>
+        <v>203.9580000000001</v>
       </c>
       <c r="F83">
-        <v>519.939</v>
+        <v>526.3580000000001</v>
       </c>
       <c r="G83">
         <v>0.826</v>
@@ -8088,37 +8099,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M83">
-        <v>122.6016162</v>
+        <v>124.1152164</v>
       </c>
       <c r="N83">
-        <v>-132.0349495333333</v>
+        <v>-133.5485497333333</v>
       </c>
       <c r="O83">
-        <v>-27.727339402</v>
+        <v>-28.045195444</v>
       </c>
       <c r="P83">
-        <v>-104.3076101313333</v>
+        <v>-105.5033542893333</v>
       </c>
       <c r="Q83">
-        <v>-31.00761013133334</v>
+        <v>-32.20335428933335</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3128594977769768</v>
+        <v>0.3276961365423645</v>
       </c>
       <c r="T83">
-        <v>4.503006795965195</v>
+        <v>4.753173840185484</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.01615802516639254</v>
+        <v>-0.0159609760789975</v>
       </c>
       <c r="W83">
-        <v>0.2396100623342354</v>
+        <v>0.2395635981594277</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8126,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.0769429769828216</v>
+        <v>-0.0760046479952261</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8134,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2554274550683563</v>
+        <v>0.2573274550683563</v>
       </c>
       <c r="C84">
-        <v>-381.6024824600021</v>
+        <v>-389.3142984835184</v>
       </c>
       <c r="D84">
-        <v>143.929517539998</v>
+        <v>142.6367015164816</v>
       </c>
       <c r="E84">
-        <v>203.9580000000001</v>
+        <v>210.3770000000001</v>
       </c>
       <c r="F84">
-        <v>526.3580000000001</v>
+        <v>532.777</v>
       </c>
       <c r="G84">
         <v>0.826</v>
@@ -8170,37 +8181,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M84">
-        <v>124.1152164</v>
+        <v>125.6288166</v>
       </c>
       <c r="N84">
-        <v>-133.5485497333333</v>
+        <v>-135.0621499333334</v>
       </c>
       <c r="O84">
-        <v>-28.045195444</v>
+        <v>-28.363051486</v>
       </c>
       <c r="P84">
-        <v>-105.5033542893333</v>
+        <v>-106.6990984473334</v>
       </c>
       <c r="Q84">
-        <v>-32.20335428933335</v>
+        <v>-33.39909844733336</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3276961365423645</v>
+        <v>0.3442782622213271</v>
       </c>
       <c r="T84">
-        <v>4.753173840185484</v>
+        <v>5.032772301372867</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.0159609760789975</v>
+        <v>-0.01576867516238308</v>
       </c>
       <c r="W84">
-        <v>0.2395635981594277</v>
+        <v>0.23951825360329</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8208,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.0760046479952261</v>
+        <v>-0.07508892934468148</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8216,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2573274550683563</v>
+        <v>0.2592274550683563</v>
       </c>
       <c r="C85">
-        <v>-389.3142984835184</v>
+        <v>-397.0030963771142</v>
       </c>
       <c r="D85">
-        <v>142.6367015164816</v>
+        <v>141.3669036228858</v>
       </c>
       <c r="E85">
-        <v>210.3770000000001</v>
+        <v>216.796</v>
       </c>
       <c r="F85">
-        <v>532.777</v>
+        <v>539.196</v>
       </c>
       <c r="G85">
         <v>0.826</v>
@@ -8252,37 +8263,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M85">
-        <v>125.6288166</v>
+        <v>127.1424168</v>
       </c>
       <c r="N85">
-        <v>-135.0621499333334</v>
+        <v>-136.5757501333333</v>
       </c>
       <c r="O85">
-        <v>-28.363051486</v>
+        <v>-28.680907528</v>
       </c>
       <c r="P85">
-        <v>-106.6990984473334</v>
+        <v>-107.8948426053333</v>
       </c>
       <c r="Q85">
-        <v>-33.39909844733336</v>
+        <v>-34.59484260533334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3442782622213271</v>
+        <v>0.3629331536101601</v>
       </c>
       <c r="T85">
-        <v>5.032772301372867</v>
+        <v>5.347320570208671</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.01576867516238308</v>
+        <v>-0.01558095283902138</v>
       </c>
       <c r="W85">
-        <v>0.23951825360329</v>
+        <v>0.2394739886794413</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8290,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.07508892934468148</v>
+        <v>-0.07419501351914937</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8298,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2592274550683562</v>
+        <v>0.2611274550683562</v>
       </c>
       <c r="C86">
-        <v>-397.003096377114</v>
+        <v>-404.669485460862</v>
       </c>
       <c r="D86">
-        <v>141.3669036228859</v>
+        <v>140.119514539138</v>
       </c>
       <c r="E86">
-        <v>216.7959999999999</v>
+        <v>223.215</v>
       </c>
       <c r="F86">
-        <v>539.1959999999999</v>
+        <v>545.615</v>
       </c>
       <c r="G86">
         <v>0.826</v>
@@ -8334,37 +8345,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M86">
-        <v>127.1424168</v>
+        <v>128.656017</v>
       </c>
       <c r="N86">
-        <v>-136.5757501333333</v>
+        <v>-138.0893503333334</v>
       </c>
       <c r="O86">
-        <v>-28.680907528</v>
+        <v>-28.99876357</v>
       </c>
       <c r="P86">
-        <v>-107.8948426053333</v>
+        <v>-109.0905867633333</v>
       </c>
       <c r="Q86">
-        <v>-34.59484260533333</v>
+        <v>-35.79058676333335</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3629331536101599</v>
+        <v>0.3840753638508372</v>
       </c>
       <c r="T86">
-        <v>5.347320570208668</v>
+        <v>5.703808608222579</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.01558095283902138</v>
+        <v>-0.01539764751150348</v>
       </c>
       <c r="W86">
-        <v>0.2394739886794413</v>
+        <v>0.2394307652832125</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8372,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.07419501351914959</v>
+        <v>-0.07332213100715945</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8380,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2611274550683562</v>
+        <v>0.2630274550683562</v>
       </c>
       <c r="C87">
-        <v>-404.669485460862</v>
+        <v>-412.3140537369374</v>
       </c>
       <c r="D87">
-        <v>140.119514539138</v>
+        <v>138.8939462630626</v>
       </c>
       <c r="E87">
-        <v>223.215</v>
+        <v>229.634</v>
       </c>
       <c r="F87">
-        <v>545.615</v>
+        <v>552.034</v>
       </c>
       <c r="G87">
         <v>0.826</v>
@@ -8416,37 +8427,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M87">
-        <v>128.656017</v>
+        <v>130.1696172</v>
       </c>
       <c r="N87">
-        <v>-138.0893503333334</v>
+        <v>-139.6029505333333</v>
       </c>
       <c r="O87">
-        <v>-28.99876357</v>
+        <v>-29.316619612</v>
       </c>
       <c r="P87">
-        <v>-109.0905867633333</v>
+        <v>-110.2863309213333</v>
       </c>
       <c r="Q87">
-        <v>-35.79058676333335</v>
+        <v>-36.98633092133335</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3840753638508372</v>
+        <v>0.4082378898401827</v>
       </c>
       <c r="T87">
-        <v>5.703808608222579</v>
+        <v>6.111223508809906</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.01539764751150348</v>
+        <v>-0.01521860509857902</v>
       </c>
       <c r="W87">
-        <v>0.2394307652832125</v>
+        <v>0.2393885470822449</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8454,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.07332213100715945</v>
+        <v>-0.07246954808847161</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8462,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2630274550683562</v>
+        <v>0.2649274550683562</v>
       </c>
       <c r="C88">
-        <v>-412.3140537369374</v>
+        <v>-419.9373688138295</v>
       </c>
       <c r="D88">
-        <v>138.8939462630626</v>
+        <v>137.6896311861705</v>
       </c>
       <c r="E88">
-        <v>229.634</v>
+        <v>236.053</v>
       </c>
       <c r="F88">
-        <v>552.034</v>
+        <v>558.453</v>
       </c>
       <c r="G88">
         <v>0.826</v>
@@ -8498,37 +8509,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M88">
-        <v>130.1696172</v>
+        <v>131.6832174</v>
       </c>
       <c r="N88">
-        <v>-139.6029505333333</v>
+        <v>-141.1165507333333</v>
       </c>
       <c r="O88">
-        <v>-29.316619612</v>
+        <v>-29.634475654</v>
       </c>
       <c r="P88">
-        <v>-110.2863309213333</v>
+        <v>-111.4820750793333</v>
       </c>
       <c r="Q88">
-        <v>-36.98633092133335</v>
+        <v>-38.18207507933333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4082378898401827</v>
+        <v>0.4361177275201968</v>
       </c>
       <c r="T88">
-        <v>6.111223508809906</v>
+        <v>6.581317624872207</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.01521860509857902</v>
+        <v>-0.01504367860319306</v>
       </c>
       <c r="W88">
-        <v>0.2393885470822449</v>
+        <v>0.239347299414633</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8536,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.07246954808847161</v>
+        <v>-0.07163656477710978</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8544,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2649274550683562</v>
+        <v>0.2668274550683563</v>
       </c>
       <c r="C89">
-        <v>-419.9373688138295</v>
+        <v>-427.5399787828843</v>
       </c>
       <c r="D89">
-        <v>137.6896311861705</v>
+        <v>136.5060212171157</v>
       </c>
       <c r="E89">
-        <v>236.053</v>
+        <v>242.472</v>
       </c>
       <c r="F89">
-        <v>558.453</v>
+        <v>564.872</v>
       </c>
       <c r="G89">
         <v>0.826</v>
@@ -8580,37 +8591,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M89">
-        <v>131.6832174</v>
+        <v>133.1968176</v>
       </c>
       <c r="N89">
-        <v>-141.1165507333333</v>
+        <v>-142.6301509333333</v>
       </c>
       <c r="O89">
-        <v>-29.634475654</v>
+        <v>-29.952331696</v>
       </c>
       <c r="P89">
-        <v>-111.4820750793333</v>
+        <v>-112.6778192373333</v>
       </c>
       <c r="Q89">
-        <v>-38.18207507933333</v>
+        <v>-39.37781923733334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4361177275201968</v>
+        <v>0.4686442048135465</v>
       </c>
       <c r="T89">
-        <v>6.581317624872207</v>
+        <v>7.129760760278224</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.01504367860319306</v>
+        <v>-0.01487272770997495</v>
       </c>
       <c r="W89">
-        <v>0.239347299414633</v>
+        <v>0.2393069891940121</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8618,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.07163656477710978</v>
+        <v>-0.0708225129046427</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8626,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2668274550683563</v>
+        <v>0.2687274550683562</v>
       </c>
       <c r="C90">
-        <v>-427.5399787828843</v>
+        <v>-435.1224130500228</v>
       </c>
       <c r="D90">
-        <v>136.5060212171157</v>
+        <v>135.3425869499771</v>
       </c>
       <c r="E90">
-        <v>242.472</v>
+        <v>248.891</v>
       </c>
       <c r="F90">
-        <v>564.872</v>
+        <v>571.2909999999999</v>
       </c>
       <c r="G90">
         <v>0.826</v>
@@ -8662,37 +8673,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M90">
-        <v>133.1968176</v>
+        <v>134.7104178</v>
       </c>
       <c r="N90">
-        <v>-142.6301509333333</v>
+        <v>-144.1437511333333</v>
       </c>
       <c r="O90">
-        <v>-29.952331696</v>
+        <v>-30.270187738</v>
       </c>
       <c r="P90">
-        <v>-112.6778192373333</v>
+        <v>-113.8735633953333</v>
       </c>
       <c r="Q90">
-        <v>-39.37781923733334</v>
+        <v>-40.57356339533332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4686442048135465</v>
+        <v>0.5070845870693235</v>
       </c>
       <c r="T90">
-        <v>7.129760760278224</v>
+        <v>7.777920829394427</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.01487272770997495</v>
+        <v>-0.01470561840986287</v>
       </c>
       <c r="W90">
-        <v>0.2393069891940121</v>
+        <v>0.2392675848210457</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8700,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.0708225129046427</v>
+        <v>-0.07002675433268046</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8708,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2687274550683562</v>
+        <v>0.2706274550683563</v>
       </c>
       <c r="C91">
-        <v>-435.1224130500228</v>
+        <v>-442.685183125287</v>
       </c>
       <c r="D91">
-        <v>135.3425869499771</v>
+        <v>134.198816874713</v>
       </c>
       <c r="E91">
-        <v>248.891</v>
+        <v>255.3100000000001</v>
       </c>
       <c r="F91">
-        <v>571.2909999999999</v>
+        <v>577.71</v>
       </c>
       <c r="G91">
         <v>0.826</v>
@@ -8744,37 +8755,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M91">
-        <v>134.7104178</v>
+        <v>136.224018</v>
       </c>
       <c r="N91">
-        <v>-144.1437511333333</v>
+        <v>-145.6573513333333</v>
       </c>
       <c r="O91">
-        <v>-30.270187738</v>
+        <v>-30.58804378</v>
       </c>
       <c r="P91">
-        <v>-113.8735633953333</v>
+        <v>-115.0693075533333</v>
       </c>
       <c r="Q91">
-        <v>-40.57356339533332</v>
+        <v>-41.76930755333335</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5070845870693235</v>
+        <v>0.5532130457762559</v>
       </c>
       <c r="T91">
-        <v>7.777920829394427</v>
+        <v>8.55571291233387</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.01470561840986287</v>
+        <v>-0.01454222264975328</v>
       </c>
       <c r="W91">
-        <v>0.2392675848210457</v>
+        <v>0.2392290561008119</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8782,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.07002675433268046</v>
+        <v>-0.06924867928453948</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8790,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2706274550683563</v>
+        <v>0.2725274550683562</v>
       </c>
       <c r="C92">
-        <v>-442.685183125287</v>
+        <v>-450.2287833726857</v>
       </c>
       <c r="D92">
-        <v>134.198816874713</v>
+        <v>133.0742166273144</v>
       </c>
       <c r="E92">
-        <v>255.3100000000001</v>
+        <v>261.729</v>
       </c>
       <c r="F92">
-        <v>577.71</v>
+        <v>584.129</v>
       </c>
       <c r="G92">
         <v>0.826</v>
@@ -8826,37 +8837,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M92">
-        <v>136.224018</v>
+        <v>137.7376182</v>
       </c>
       <c r="N92">
-        <v>-145.6573513333333</v>
+        <v>-147.1709515333334</v>
       </c>
       <c r="O92">
-        <v>-30.58804378</v>
+        <v>-30.905899822</v>
       </c>
       <c r="P92">
-        <v>-115.0693075533333</v>
+        <v>-116.2650517113333</v>
       </c>
       <c r="Q92">
-        <v>-41.76930755333335</v>
+        <v>-42.96505171133334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5532130457762559</v>
+        <v>0.6095922730847289</v>
       </c>
       <c r="T92">
-        <v>8.55571291233387</v>
+        <v>9.506347680370968</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.01454222264975328</v>
+        <v>-0.0143824180052505</v>
       </c>
       <c r="W92">
-        <v>0.2392290561008119</v>
+        <v>0.2391913741656381</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8864,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.06924867928453948</v>
+        <v>-0.06848770478690724</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8872,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2725274550683562</v>
+        <v>0.2744274550683563</v>
       </c>
       <c r="C93">
-        <v>-450.2287833726857</v>
+        <v>-457.7536917226531</v>
       </c>
       <c r="D93">
-        <v>133.0742166273144</v>
+        <v>131.9683082773469</v>
       </c>
       <c r="E93">
-        <v>261.729</v>
+        <v>268.148</v>
       </c>
       <c r="F93">
-        <v>584.129</v>
+        <v>590.548</v>
       </c>
       <c r="G93">
         <v>0.826</v>
@@ -8908,37 +8919,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M93">
-        <v>137.7376182</v>
+        <v>139.2512184</v>
       </c>
       <c r="N93">
-        <v>-147.1709515333334</v>
+        <v>-148.6845517333333</v>
       </c>
       <c r="O93">
-        <v>-30.905899822</v>
+        <v>-31.223755864</v>
       </c>
       <c r="P93">
-        <v>-116.2650517113333</v>
+        <v>-117.4607958693333</v>
       </c>
       <c r="Q93">
-        <v>-42.96505171133334</v>
+        <v>-44.16079586933334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6095922730847289</v>
+        <v>0.6800663072203201</v>
       </c>
       <c r="T93">
-        <v>9.506347680370968</v>
+        <v>10.69464114041734</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.0143824180052505</v>
+        <v>-0.01422608737475865</v>
       </c>
       <c r="W93">
-        <v>0.2391913741656381</v>
+        <v>0.2391545114029681</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8946,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.06848770478690724</v>
+        <v>-0.06774327321313645</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8954,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2744274550683563</v>
+        <v>0.2763274550683562</v>
       </c>
       <c r="C94">
-        <v>-457.7536917226531</v>
+        <v>-465.2603703492731</v>
       </c>
       <c r="D94">
-        <v>131.9683082773469</v>
+        <v>130.8806296507269</v>
       </c>
       <c r="E94">
-        <v>268.148</v>
+        <v>274.567</v>
       </c>
       <c r="F94">
-        <v>590.548</v>
+        <v>596.967</v>
       </c>
       <c r="G94">
         <v>0.826</v>
@@ -8990,37 +9001,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M94">
-        <v>139.2512184</v>
+        <v>140.7648186</v>
       </c>
       <c r="N94">
-        <v>-148.6845517333333</v>
+        <v>-150.1981519333333</v>
       </c>
       <c r="O94">
-        <v>-31.223755864</v>
+        <v>-31.541611906</v>
       </c>
       <c r="P94">
-        <v>-117.4607958693333</v>
+        <v>-118.6565400273333</v>
       </c>
       <c r="Q94">
-        <v>-44.16079586933334</v>
+        <v>-45.35654002733335</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6800663072203201</v>
+        <v>0.7706757796803659</v>
       </c>
       <c r="T94">
-        <v>10.69464114041734</v>
+        <v>12.22244701761982</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.01422608737475865</v>
+        <v>-0.01407311869330963</v>
       </c>
       <c r="W94">
-        <v>0.2391545114029681</v>
+        <v>0.2391184413878824</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9028,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.06774327321313645</v>
+        <v>-0.06701485092052217</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9036,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2763274550683562</v>
+        <v>0.2782274550683562</v>
       </c>
       <c r="C95">
-        <v>-465.2603703492731</v>
+        <v>-472.7492663142882</v>
       </c>
       <c r="D95">
-        <v>130.8806296507269</v>
+        <v>129.8107336857117</v>
       </c>
       <c r="E95">
-        <v>274.567</v>
+        <v>280.986</v>
       </c>
       <c r="F95">
-        <v>596.967</v>
+        <v>603.386</v>
       </c>
       <c r="G95">
         <v>0.826</v>
@@ -9072,37 +9083,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M95">
-        <v>140.7648186</v>
+        <v>142.2784188</v>
       </c>
       <c r="N95">
-        <v>-150.1981519333333</v>
+        <v>-151.7117521333333</v>
       </c>
       <c r="O95">
-        <v>-31.541611906</v>
+        <v>-31.859467948</v>
       </c>
       <c r="P95">
-        <v>-118.6565400273333</v>
+        <v>-119.8522841853333</v>
       </c>
       <c r="Q95">
-        <v>-45.35654002733335</v>
+        <v>-46.55228418533333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7706757796803659</v>
+        <v>0.8914884096270937</v>
       </c>
       <c r="T95">
-        <v>12.22244701761982</v>
+        <v>14.25952152055646</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.01407311869330963</v>
+        <v>-0.0139234046646574</v>
       </c>
       <c r="W95">
-        <v>0.2391184413878824</v>
+        <v>0.2390831388199262</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9110,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.06701485092052217</v>
+        <v>-0.06630192697455906</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9118,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2782274550683562</v>
+        <v>0.2801274550683562</v>
       </c>
       <c r="C96">
-        <v>-472.7492663142882</v>
+        <v>-480.2208121797778</v>
       </c>
       <c r="D96">
-        <v>129.8107336857117</v>
+        <v>128.7581878202223</v>
       </c>
       <c r="E96">
-        <v>280.986</v>
+        <v>287.4050000000001</v>
       </c>
       <c r="F96">
-        <v>603.386</v>
+        <v>609.8050000000001</v>
       </c>
       <c r="G96">
         <v>0.826</v>
@@ -9154,37 +9165,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M96">
-        <v>142.2784188</v>
+        <v>143.792019</v>
       </c>
       <c r="N96">
-        <v>-151.7117521333333</v>
+        <v>-153.2253523333333</v>
       </c>
       <c r="O96">
-        <v>-31.859467948</v>
+        <v>-32.17732399</v>
       </c>
       <c r="P96">
-        <v>-119.8522841853333</v>
+        <v>-121.0480283433333</v>
       </c>
       <c r="Q96">
-        <v>-46.55228418533333</v>
+        <v>-47.74802834333335</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8914884096270937</v>
+        <v>1.060626091552513</v>
       </c>
       <c r="T96">
-        <v>14.25952152055646</v>
+        <v>17.11142582466776</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.0139234046646574</v>
+        <v>-0.01377684251029259</v>
       </c>
       <c r="W96">
-        <v>0.2390831388199262</v>
+        <v>0.239048579463927</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9192,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.06630192697455906</v>
+        <v>-0.06560401195377419</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9200,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2801274550683562</v>
+        <v>0.2820274550683562</v>
       </c>
       <c r="C97">
-        <v>-480.2208121797778</v>
+        <v>-487.6754265912679</v>
       </c>
       <c r="D97">
-        <v>128.7581878202223</v>
+        <v>127.7225734087322</v>
       </c>
       <c r="E97">
-        <v>287.4050000000001</v>
+        <v>293.8240000000001</v>
       </c>
       <c r="F97">
-        <v>609.8050000000001</v>
+        <v>616.224</v>
       </c>
       <c r="G97">
         <v>0.826</v>
@@ -9236,37 +9247,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M97">
-        <v>143.792019</v>
+        <v>145.3056192</v>
       </c>
       <c r="N97">
-        <v>-153.2253523333333</v>
+        <v>-154.7389525333334</v>
       </c>
       <c r="O97">
-        <v>-32.17732399</v>
+        <v>-32.49518003200001</v>
       </c>
       <c r="P97">
-        <v>-121.0480283433333</v>
+        <v>-122.2437725013334</v>
       </c>
       <c r="Q97">
-        <v>-47.74802834333335</v>
+        <v>-48.94377250133336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.060626091552513</v>
+        <v>1.314332614440642</v>
       </c>
       <c r="T97">
-        <v>17.11142582466776</v>
+        <v>21.38928228083471</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.01377684251029259</v>
+        <v>-0.0136333337341437</v>
       </c>
       <c r="W97">
-        <v>0.239048579463927</v>
+        <v>0.2390147400945111</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9274,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.06560401195377419</v>
+        <v>-0.06492063682925586</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9282,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2820274550683562</v>
+        <v>0.2839274550683562</v>
       </c>
       <c r="C98">
-        <v>-487.6754265912678</v>
+        <v>-495.1135148329278</v>
       </c>
       <c r="D98">
-        <v>127.7225734087322</v>
+        <v>126.7034851670722</v>
       </c>
       <c r="E98">
-        <v>293.824</v>
+        <v>300.2429999999999</v>
       </c>
       <c r="F98">
-        <v>616.2239999999999</v>
+        <v>622.6429999999999</v>
       </c>
       <c r="G98">
         <v>0.826</v>
@@ -9318,37 +9329,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M98">
-        <v>145.3056192</v>
+        <v>146.8192194</v>
       </c>
       <c r="N98">
-        <v>-154.7389525333333</v>
+        <v>-156.2525527333333</v>
       </c>
       <c r="O98">
-        <v>-32.495180032</v>
+        <v>-32.813036074</v>
       </c>
       <c r="P98">
-        <v>-122.2437725013333</v>
+        <v>-123.4395166593333</v>
       </c>
       <c r="Q98">
-        <v>-48.94377250133333</v>
+        <v>-50.13951665933332</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.314332614440638</v>
+        <v>1.737176819254185</v>
       </c>
       <c r="T98">
-        <v>21.38928228083465</v>
+        <v>28.51904304111287</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.01363333373414371</v>
+        <v>-0.01349278390183295</v>
       </c>
       <c r="W98">
-        <v>0.2390147400945111</v>
+        <v>0.2389815984440522</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9356,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.06492063682925586</v>
+        <v>-0.06425135191349018</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9364,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2839274550683562</v>
+        <v>0.2858274550683562</v>
       </c>
       <c r="C99">
-        <v>-495.1135148329278</v>
+        <v>-502.5354693563963</v>
       </c>
       <c r="D99">
-        <v>126.7034851670722</v>
+        <v>125.7005306436037</v>
       </c>
       <c r="E99">
-        <v>300.2429999999999</v>
+        <v>306.662</v>
       </c>
       <c r="F99">
-        <v>622.6429999999999</v>
+        <v>629.062</v>
       </c>
       <c r="G99">
         <v>0.826</v>
@@ -9400,37 +9411,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M99">
-        <v>146.8192194</v>
+        <v>148.3328196</v>
       </c>
       <c r="N99">
-        <v>-156.2525527333333</v>
+        <v>-157.7661529333334</v>
       </c>
       <c r="O99">
-        <v>-32.813036074</v>
+        <v>-33.13089211600001</v>
       </c>
       <c r="P99">
-        <v>-123.4395166593333</v>
+        <v>-124.6352608173333</v>
       </c>
       <c r="Q99">
-        <v>-50.13951665933332</v>
+        <v>-51.33526081733335</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.737176819254185</v>
+        <v>2.582865228881277</v>
       </c>
       <c r="T99">
-        <v>28.51904304111287</v>
+        <v>42.77856456166931</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.01349278390183295</v>
+        <v>-0.01335510243344689</v>
       </c>
       <c r="W99">
-        <v>0.2389815984440522</v>
+        <v>0.2389491331538068</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9438,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.06425135191349018</v>
+        <v>-0.06359572587355666</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9446,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2858274550683562</v>
+        <v>0.2877274550683562</v>
       </c>
       <c r="C100">
-        <v>-502.5354693563963</v>
+        <v>-509.9416702846885</v>
       </c>
       <c r="D100">
-        <v>125.7005306436037</v>
+        <v>124.7133297153115</v>
       </c>
       <c r="E100">
-        <v>306.662</v>
+        <v>313.081</v>
       </c>
       <c r="F100">
-        <v>629.062</v>
+        <v>635.481</v>
       </c>
       <c r="G100">
         <v>0.826</v>
@@ -9482,37 +9493,37 @@
         <v>-9.43333333333333</v>
       </c>
       <c r="M100">
-        <v>148.3328196</v>
+        <v>149.8464198</v>
       </c>
       <c r="N100">
-        <v>-157.7661529333334</v>
+        <v>-159.2797531333333</v>
       </c>
       <c r="O100">
-        <v>-33.13089211600001</v>
+        <v>-33.448748158</v>
       </c>
       <c r="P100">
-        <v>-124.6352608173333</v>
+        <v>-125.8310049753333</v>
       </c>
       <c r="Q100">
-        <v>-51.33526081733335</v>
+        <v>-52.53100497533335</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.582865228881277</v>
+        <v>5.119930457762553</v>
       </c>
       <c r="T100">
-        <v>42.77856456166931</v>
+        <v>85.55712912333861</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.01335510243344689</v>
+        <v>-0.01322020240886662</v>
       </c>
       <c r="W100">
-        <v>0.2389491331538068</v>
+        <v>0.2389173237280107</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9520,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.06359572587355666</v>
+        <v>-0.06295334480412684</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2877274550683562</v>
-      </c>
-      <c r="C101">
-        <v>-509.9416702846885</v>
-      </c>
-      <c r="D101">
-        <v>124.7133297153115</v>
-      </c>
-      <c r="E101">
-        <v>313.081</v>
-      </c>
-      <c r="F101">
-        <v>635.481</v>
-      </c>
-      <c r="G101">
-        <v>0.826</v>
-      </c>
-      <c r="H101">
-        <v>319.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>63.86666666666667</v>
-      </c>
-      <c r="K101">
-        <v>73.3</v>
-      </c>
-      <c r="L101">
-        <v>-9.43333333333333</v>
-      </c>
-      <c r="M101">
-        <v>149.8464198</v>
-      </c>
-      <c r="N101">
-        <v>-159.2797531333333</v>
-      </c>
-      <c r="O101">
-        <v>-33.448748158</v>
-      </c>
-      <c r="P101">
-        <v>-125.8310049753333</v>
-      </c>
-      <c r="Q101">
-        <v>-52.53100497533335</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.119930457762553</v>
-      </c>
-      <c r="T101">
-        <v>85.55712912333861</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.01322020240886662</v>
-      </c>
-      <c r="W101">
-        <v>0.2389173237280107</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.06295334480412684</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
